--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354017</t>
+          <t>2026-03-02T04:10:34.094704</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354033</t>
+          <t>2026-03-02T04:10:34.094719</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354037</t>
+          <t>2026-03-02T04:10:34.094723</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354040</t>
+          <t>2026-03-02T04:10:34.094727</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354044</t>
+          <t>2026-03-02T04:10:34.094730</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354047</t>
+          <t>2026-03-02T04:10:34.094733</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354050</t>
+          <t>2026-03-02T04:10:34.094736</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354054</t>
+          <t>2026-03-02T04:10:34.094740</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354057</t>
+          <t>2026-03-02T04:10:34.094743</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354063</t>
+          <t>2026-03-02T04:10:34.094749</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354066</t>
+          <t>2026-03-02T04:10:34.094752</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354069</t>
+          <t>2026-03-02T04:10:34.094755</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354072</t>
+          <t>2026-03-02T04:10:34.094758</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354075</t>
+          <t>2026-03-02T04:10:34.094761</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354077</t>
+          <t>2026-03-02T04:10:34.094763</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354080</t>
+          <t>2026-03-02T04:10:34.094766</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354083</t>
+          <t>2026-03-02T04:10:34.094769</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354086</t>
+          <t>2026-03-02T04:10:34.094772</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354089</t>
+          <t>2026-03-02T04:10:34.094775</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354094</t>
+          <t>2026-03-02T04:10:34.094780</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354097</t>
+          <t>2026-03-02T04:10:34.094782</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354100</t>
+          <t>2026-03-02T04:10:34.094785</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354102</t>
+          <t>2026-03-02T04:10:34.094788</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354105</t>
+          <t>2026-03-02T04:10:34.094790</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354108</t>
+          <t>2026-03-02T04:10:34.094793</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354111</t>
+          <t>2026-03-02T04:10:34.094796</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354114</t>
+          <t>2026-03-02T04:10:34.094799</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354116</t>
+          <t>2026-03-02T04:10:34.094801</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354119</t>
+          <t>2026-03-02T04:10:34.094804</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354124</t>
+          <t>2026-03-02T04:10:34.094811</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354127</t>
+          <t>2026-03-02T04:10:34.094814</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354130</t>
+          <t>2026-03-02T04:10:34.094817</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354133</t>
+          <t>2026-03-02T04:10:34.094819</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354136</t>
+          <t>2026-03-02T04:10:34.094822</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354140</t>
+          <t>2026-03-02T04:10:34.094825</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354143</t>
+          <t>2026-03-02T04:10:34.094828</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354146</t>
+          <t>2026-03-02T04:10:34.094830</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1306.00</t>
+          <t>1312.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354149</t>
+          <t>2026-03-02T04:10:34.094833</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1315.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354152</t>
+          <t>2026-03-02T04:10:34.094836</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1423.00</t>
+          <t>1304.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1423</v>
+        <v>1304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354154</t>
+          <t>2026-03-02T04:10:34.094838</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1425.00</t>
+          <t>1306.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1425</v>
+        <v>1306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354157</t>
+          <t>2026-03-02T04:10:34.094841</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1418</v>
+        <v>1300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354160</t>
+          <t>2026-03-02T04:10:34.094844</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094704</t>
+          <t>2026-03-03T04:11:29.852609</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094719</t>
+          <t>2026-03-03T04:11:29.852624</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094723</t>
+          <t>2026-03-03T04:11:29.852628</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094727</t>
+          <t>2026-03-03T04:11:29.852631</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094730</t>
+          <t>2026-03-03T04:11:29.852634</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094733</t>
+          <t>2026-03-03T04:11:29.852637</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094736</t>
+          <t>2026-03-03T04:11:29.852640</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094740</t>
+          <t>2026-03-03T04:11:29.852644</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094743</t>
+          <t>2026-03-03T04:11:29.852646</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094749</t>
+          <t>2026-03-03T04:11:29.852651</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094752</t>
+          <t>2026-03-03T04:11:29.852654</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094755</t>
+          <t>2026-03-03T04:11:29.852657</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094758</t>
+          <t>2026-03-03T04:11:29.852660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094761</t>
+          <t>2026-03-03T04:11:29.852662</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094763</t>
+          <t>2026-03-03T04:11:29.852665</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094766</t>
+          <t>2026-03-03T04:11:29.852668</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094769</t>
+          <t>2026-03-03T04:11:29.852671</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094772</t>
+          <t>2026-03-03T04:11:29.852673</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094775</t>
+          <t>2026-03-03T04:11:29.852676</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094780</t>
+          <t>2026-03-03T04:11:29.852681</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094782</t>
+          <t>2026-03-03T04:11:29.852683</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094785</t>
+          <t>2026-03-03T04:11:29.852686</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094788</t>
+          <t>2026-03-03T04:11:29.852689</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094790</t>
+          <t>2026-03-03T04:11:29.852692</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094793</t>
+          <t>2026-03-03T04:11:29.852694</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094796</t>
+          <t>2026-03-03T04:11:29.852697</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094799</t>
+          <t>2026-03-03T04:11:29.852700</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094801</t>
+          <t>2026-03-03T04:11:29.852703</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094804</t>
+          <t>2026-03-03T04:11:29.852705</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094811</t>
+          <t>2026-03-03T04:11:29.852709</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094814</t>
+          <t>2026-03-03T04:11:29.852712</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094817</t>
+          <t>2026-03-03T04:11:29.852715</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094819</t>
+          <t>2026-03-03T04:11:29.852718</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094822</t>
+          <t>2026-03-03T04:11:29.852720</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094825</t>
+          <t>2026-03-03T04:11:29.852723</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094828</t>
+          <t>2026-03-03T04:11:29.852726</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094830</t>
+          <t>2026-03-03T04:11:29.852728</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094833</t>
+          <t>2026-03-03T04:11:29.852731</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094836</t>
+          <t>2026-03-03T04:11:29.852734</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094838</t>
+          <t>2026-03-03T04:11:29.852738</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1306.00</t>
+          <t>1312.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094841</t>
+          <t>2026-03-03T04:11:29.852741</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1315.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094844</t>
+          <t>2026-03-03T04:11:29.852744</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852609</t>
+          <t>2026-03-04T04:05:06.836062</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852624</t>
+          <t>2026-03-04T04:05:06.836075</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852628</t>
+          <t>2026-03-04T04:05:06.836079</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852631</t>
+          <t>2026-03-04T04:05:06.836083</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852634</t>
+          <t>2026-03-04T04:05:06.836086</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852637</t>
+          <t>2026-03-04T04:05:06.836089</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852640</t>
+          <t>2026-03-04T04:05:06.836092</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852644</t>
+          <t>2026-03-04T04:05:06.836096</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852646</t>
+          <t>2026-03-04T04:05:06.836099</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852651</t>
+          <t>2026-03-04T04:05:06.836105</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852654</t>
+          <t>2026-03-04T04:05:06.836108</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852657</t>
+          <t>2026-03-04T04:05:06.836111</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852660</t>
+          <t>2026-03-04T04:05:06.836114</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852662</t>
+          <t>2026-03-04T04:05:06.836117</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852665</t>
+          <t>2026-03-04T04:05:06.836119</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852668</t>
+          <t>2026-03-04T04:05:06.836122</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852671</t>
+          <t>2026-03-04T04:05:06.836125</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852673</t>
+          <t>2026-03-04T04:05:06.836128</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852676</t>
+          <t>2026-03-04T04:05:06.836130</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852681</t>
+          <t>2026-03-04T04:05:06.836135</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852683</t>
+          <t>2026-03-04T04:05:06.836138</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852686</t>
+          <t>2026-03-04T04:05:06.836141</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852689</t>
+          <t>2026-03-04T04:05:06.836143</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852692</t>
+          <t>2026-03-04T04:05:06.836146</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852694</t>
+          <t>2026-03-04T04:05:06.836149</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852697</t>
+          <t>2026-03-04T04:05:06.836152</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852700</t>
+          <t>2026-03-04T04:05:06.836154</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852703</t>
+          <t>2026-03-04T04:05:06.836157</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852705</t>
+          <t>2026-03-04T04:05:06.836160</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852709</t>
+          <t>2026-03-04T04:05:06.836165</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852712</t>
+          <t>2026-03-04T04:05:06.836168</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852715</t>
+          <t>2026-03-04T04:05:06.836170</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852718</t>
+          <t>2026-03-04T04:05:06.836173</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852720</t>
+          <t>2026-03-04T04:05:06.836176</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852723</t>
+          <t>2026-03-04T04:05:06.836179</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852726</t>
+          <t>2026-03-04T04:05:06.836181</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852728</t>
+          <t>2026-03-04T04:05:06.836184</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852731</t>
+          <t>2026-03-04T04:05:06.836187</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852734</t>
+          <t>2026-03-04T04:05:06.836190</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852738</t>
+          <t>2026-03-04T04:05:06.836192</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852741</t>
+          <t>2026-03-04T04:05:06.836195</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852744</t>
+          <t>2026-03-04T04:05:06.836198</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836062</t>
+          <t>2026-03-05T04:09:02.075980</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836075</t>
+          <t>2026-03-05T04:09:02.075995</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836079</t>
+          <t>2026-03-05T04:09:02.075999</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836083</t>
+          <t>2026-03-05T04:09:02.076002</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836086</t>
+          <t>2026-03-05T04:09:02.076005</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836089</t>
+          <t>2026-03-05T04:09:02.076009</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836092</t>
+          <t>2026-03-05T04:09:02.076012</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836096</t>
+          <t>2026-03-05T04:09:02.076015</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836099</t>
+          <t>2026-03-05T04:09:02.076018</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836105</t>
+          <t>2026-03-05T04:09:02.076024</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836108</t>
+          <t>2026-03-05T04:09:02.076027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836111</t>
+          <t>2026-03-05T04:09:02.076030</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836114</t>
+          <t>2026-03-05T04:09:02.076033</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836117</t>
+          <t>2026-03-05T04:09:02.076036</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836119</t>
+          <t>2026-03-05T04:09:02.076039</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836122</t>
+          <t>2026-03-05T04:09:02.076042</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836125</t>
+          <t>2026-03-05T04:09:02.076044</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836128</t>
+          <t>2026-03-05T04:09:02.076047</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836130</t>
+          <t>2026-03-05T04:09:02.076050</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836135</t>
+          <t>2026-03-05T04:09:02.076055</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836138</t>
+          <t>2026-03-05T04:09:02.076058</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836141</t>
+          <t>2026-03-05T04:09:02.076061</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836143</t>
+          <t>2026-03-05T04:09:02.076064</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836146</t>
+          <t>2026-03-05T04:09:02.076067</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836149</t>
+          <t>2026-03-05T04:09:02.076069</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836152</t>
+          <t>2026-03-05T04:09:02.076072</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836154</t>
+          <t>2026-03-05T04:09:02.076075</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836157</t>
+          <t>2026-03-05T04:09:02.076078</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836160</t>
+          <t>2026-03-05T04:09:02.076081</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836165</t>
+          <t>2026-03-05T04:09:02.076086</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836168</t>
+          <t>2026-03-05T04:09:02.076088</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836170</t>
+          <t>2026-03-05T04:09:02.076091</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836173</t>
+          <t>2026-03-05T04:09:02.076094</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836176</t>
+          <t>2026-03-05T04:09:02.076097</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836179</t>
+          <t>2026-03-05T04:09:02.076099</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836181</t>
+          <t>2026-03-05T04:09:02.076102</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836184</t>
+          <t>2026-03-05T04:09:02.076105</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836187</t>
+          <t>2026-03-05T04:09:02.076108</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836190</t>
+          <t>2026-03-05T04:09:02.076110</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836192</t>
+          <t>2026-03-05T04:09:02.076113</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836195</t>
+          <t>2026-03-05T04:09:02.076116</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836198</t>
+          <t>2026-03-05T04:09:02.076119</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.075980</t>
+          <t>2026-03-06T04:06:04.365846</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.075995</t>
+          <t>2026-03-06T04:06:04.365859</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.075999</t>
+          <t>2026-03-06T04:06:04.365864</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076002</t>
+          <t>2026-03-06T04:06:04.365867</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076005</t>
+          <t>2026-03-06T04:06:04.365870</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076009</t>
+          <t>2026-03-06T04:06:04.365873</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076012</t>
+          <t>2026-03-06T04:06:04.365877</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076015</t>
+          <t>2026-03-06T04:06:04.365880</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076018</t>
+          <t>2026-03-06T04:06:04.365883</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076024</t>
+          <t>2026-03-06T04:06:04.365890</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076027</t>
+          <t>2026-03-06T04:06:04.365892</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076030</t>
+          <t>2026-03-06T04:06:04.365895</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076033</t>
+          <t>2026-03-06T04:06:04.365898</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076036</t>
+          <t>2026-03-06T04:06:04.365901</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076039</t>
+          <t>2026-03-06T04:06:04.365904</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076042</t>
+          <t>2026-03-06T04:06:04.365907</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076044</t>
+          <t>2026-03-06T04:06:04.365909</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076047</t>
+          <t>2026-03-06T04:06:04.365912</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076050</t>
+          <t>2026-03-06T04:06:04.365915</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076055</t>
+          <t>2026-03-06T04:06:04.365920</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076058</t>
+          <t>2026-03-06T04:06:04.365923</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076061</t>
+          <t>2026-03-06T04:06:04.365926</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076064</t>
+          <t>2026-03-06T04:06:04.365928</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076067</t>
+          <t>2026-03-06T04:06:04.365931</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076069</t>
+          <t>2026-03-06T04:06:04.365934</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076072</t>
+          <t>2026-03-06T04:06:04.365937</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076075</t>
+          <t>2026-03-06T04:06:04.365939</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076078</t>
+          <t>2026-03-06T04:06:04.365942</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076081</t>
+          <t>2026-03-06T04:06:04.365945</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076086</t>
+          <t>2026-03-06T04:06:04.365950</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076088</t>
+          <t>2026-03-06T04:06:04.365952</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076091</t>
+          <t>2026-03-06T04:06:04.365955</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076094</t>
+          <t>2026-03-06T04:06:04.365958</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076097</t>
+          <t>2026-03-06T04:06:04.365961</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076099</t>
+          <t>2026-03-06T04:06:04.365963</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076102</t>
+          <t>2026-03-06T04:06:04.365966</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076105</t>
+          <t>2026-03-06T04:06:04.365969</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076108</t>
+          <t>2026-03-06T04:06:04.365972</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076110</t>
+          <t>2026-03-06T04:06:04.365974</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076113</t>
+          <t>2026-03-06T04:06:04.365977</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076116</t>
+          <t>2026-03-06T04:06:04.365980</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076119</t>
+          <t>2026-03-06T04:06:04.365983</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365846</t>
+          <t>2026-03-07T03:57:00.438508</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365859</t>
+          <t>2026-03-07T03:57:00.438519</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365864</t>
+          <t>2026-03-07T03:57:00.438524</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365867</t>
+          <t>2026-03-07T03:57:00.438527</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365870</t>
+          <t>2026-03-07T03:57:00.438530</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365873</t>
+          <t>2026-03-07T03:57:00.438533</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365877</t>
+          <t>2026-03-07T03:57:00.438536</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365880</t>
+          <t>2026-03-07T03:57:00.438543</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365883</t>
+          <t>2026-03-07T03:57:00.438546</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365890</t>
+          <t>2026-03-07T03:57:00.438549</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365892</t>
+          <t>2026-03-07T03:57:00.438552</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365895</t>
+          <t>2026-03-07T03:57:00.438555</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365898</t>
+          <t>2026-03-07T03:57:00.438558</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365901</t>
+          <t>2026-03-07T03:57:00.438561</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365904</t>
+          <t>2026-03-07T03:57:00.438563</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365907</t>
+          <t>2026-03-07T03:57:00.438566</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365909</t>
+          <t>2026-03-07T03:57:00.438569</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365912</t>
+          <t>2026-03-07T03:57:00.438573</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365915</t>
+          <t>2026-03-07T03:57:00.438576</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365920</t>
+          <t>2026-03-07T03:57:00.438579</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365923</t>
+          <t>2026-03-07T03:57:00.438582</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365926</t>
+          <t>2026-03-07T03:57:00.438584</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365928</t>
+          <t>2026-03-07T03:57:00.438587</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365931</t>
+          <t>2026-03-07T03:57:00.438590</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365934</t>
+          <t>2026-03-07T03:57:00.438593</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365937</t>
+          <t>2026-03-07T03:57:00.438595</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365939</t>
+          <t>2026-03-07T03:57:00.438598</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365942</t>
+          <t>2026-03-07T03:57:00.438603</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365945</t>
+          <t>2026-03-07T03:57:00.438606</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365950</t>
+          <t>2026-03-07T03:57:00.438608</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365952</t>
+          <t>2026-03-07T03:57:00.438611</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365955</t>
+          <t>2026-03-07T03:57:00.438614</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365958</t>
+          <t>2026-03-07T03:57:00.438617</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365961</t>
+          <t>2026-03-07T03:57:00.438619</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365963</t>
+          <t>2026-03-07T03:57:00.438622</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365966</t>
+          <t>2026-03-07T03:57:00.438625</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365969</t>
+          <t>2026-03-07T03:57:00.438628</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365972</t>
+          <t>2026-03-07T03:57:00.438631</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,202 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365974</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>六福</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:04.365977</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>周大福</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1299.00</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:04.365980</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:04.365983</t>
+          <t>2026-03-07T03:57:00.438633</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438508</t>
+          <t>2026-03-08T04:07:50.583982</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438519</t>
+          <t>2026-03-08T04:07:50.583996</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438524</t>
+          <t>2026-03-08T04:07:50.584001</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438527</t>
+          <t>2026-03-08T04:07:50.584004</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438530</t>
+          <t>2026-03-08T04:07:50.584007</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438533</t>
+          <t>2026-03-08T04:07:50.584010</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438536</t>
+          <t>2026-03-08T04:07:50.584013</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438543</t>
+          <t>2026-03-08T04:07:50.584020</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438546</t>
+          <t>2026-03-08T04:07:50.584024</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438549</t>
+          <t>2026-03-08T04:07:50.584027</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438552</t>
+          <t>2026-03-08T04:07:50.584030</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438555</t>
+          <t>2026-03-08T04:07:50.584033</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438558</t>
+          <t>2026-03-08T04:07:50.584036</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438561</t>
+          <t>2026-03-08T04:07:50.584038</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438563</t>
+          <t>2026-03-08T04:07:50.584041</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438566</t>
+          <t>2026-03-08T04:07:50.584044</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438569</t>
+          <t>2026-03-08T04:07:50.584046</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438573</t>
+          <t>2026-03-08T04:07:50.584052</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438576</t>
+          <t>2026-03-08T04:07:50.584055</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438579</t>
+          <t>2026-03-08T04:07:50.584057</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438582</t>
+          <t>2026-03-08T04:07:50.584060</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438584</t>
+          <t>2026-03-08T04:07:50.584063</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438587</t>
+          <t>2026-03-08T04:07:50.584065</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438590</t>
+          <t>2026-03-08T04:07:50.584068</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438593</t>
+          <t>2026-03-08T04:07:50.584071</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438595</t>
+          <t>2026-03-08T04:07:50.584074</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438598</t>
+          <t>2026-03-08T04:07:50.584077</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438603</t>
+          <t>2026-03-08T04:07:50.584082</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438606</t>
+          <t>2026-03-08T04:07:50.584084</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438608</t>
+          <t>2026-03-08T04:07:50.584087</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438611</t>
+          <t>2026-03-08T04:07:50.584090</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438614</t>
+          <t>2026-03-08T04:07:50.584092</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438617</t>
+          <t>2026-03-08T04:07:50.584095</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438619</t>
+          <t>2026-03-08T04:07:50.584098</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438622</t>
+          <t>2026-03-08T04:07:50.584101</t>
         </is>
       </c>
     </row>
@@ -2819,202 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438625</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:00.438628</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>六福</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:00.438631</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>周大福</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1299.00</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:00.438633</t>
+          <t>2026-03-08T04:07:50.584104</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.583982</t>
+          <t>2026-03-09T04:13:10.124860</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.583996</t>
+          <t>2026-03-09T04:13:10.124875</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584001</t>
+          <t>2026-03-09T04:13:10.124879</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584004</t>
+          <t>2026-03-09T04:13:10.124882</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584007</t>
+          <t>2026-03-09T04:13:10.124885</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584010</t>
+          <t>2026-03-09T04:13:10.124889</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584013</t>
+          <t>2026-03-09T04:13:10.124892</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584020</t>
+          <t>2026-03-09T04:13:10.124899</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584024</t>
+          <t>2026-03-09T04:13:10.124902</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584027</t>
+          <t>2026-03-09T04:13:10.124905</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584030</t>
+          <t>2026-03-09T04:13:10.124908</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584033</t>
+          <t>2026-03-09T04:13:10.124911</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584036</t>
+          <t>2026-03-09T04:13:10.124914</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584038</t>
+          <t>2026-03-09T04:13:10.124917</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584041</t>
+          <t>2026-03-09T04:13:10.124919</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584044</t>
+          <t>2026-03-09T04:13:10.124922</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584046</t>
+          <t>2026-03-09T04:13:10.124925</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584052</t>
+          <t>2026-03-09T04:13:10.124930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584055</t>
+          <t>2026-03-09T04:13:10.124933</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584057</t>
+          <t>2026-03-09T04:13:10.124935</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584060</t>
+          <t>2026-03-09T04:13:10.124938</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584063</t>
+          <t>2026-03-09T04:13:10.124941</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584065</t>
+          <t>2026-03-09T04:13:10.124944</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584068</t>
+          <t>2026-03-09T04:13:10.124946</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584071</t>
+          <t>2026-03-09T04:13:10.124949</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584074</t>
+          <t>2026-03-09T04:13:10.124952</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584077</t>
+          <t>2026-03-09T04:13:10.124955</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584082</t>
+          <t>2026-03-09T04:13:10.124960</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584084</t>
+          <t>2026-03-09T04:13:10.124962</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584087</t>
+          <t>2026-03-09T04:13:10.124965</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584090</t>
+          <t>2026-03-09T04:13:10.124968</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584092</t>
+          <t>2026-03-09T04:13:10.124971</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584095</t>
+          <t>2026-03-09T04:13:10.124973</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584098</t>
+          <t>2026-03-09T04:13:10.124976</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584101</t>
+          <t>2026-03-09T04:13:10.124979</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584104</t>
+          <t>2026-03-09T04:13:10.124982</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124860</t>
+          <t>2026-03-10T04:05:19.857120</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124875</t>
+          <t>2026-03-10T04:05:19.857134</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124879</t>
+          <t>2026-03-10T04:05:19.857138</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124882</t>
+          <t>2026-03-10T04:05:19.857142</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124885</t>
+          <t>2026-03-10T04:05:19.857145</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124889</t>
+          <t>2026-03-10T04:05:19.857148</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124892</t>
+          <t>2026-03-10T04:05:19.857151</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124899</t>
+          <t>2026-03-10T04:05:19.857158</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124902</t>
+          <t>2026-03-10T04:05:19.857161</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124905</t>
+          <t>2026-03-10T04:05:19.857164</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124908</t>
+          <t>2026-03-10T04:05:19.857167</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124911</t>
+          <t>2026-03-10T04:05:19.857170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124914</t>
+          <t>2026-03-10T04:05:19.857173</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124917</t>
+          <t>2026-03-10T04:05:19.857176</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124919</t>
+          <t>2026-03-10T04:05:19.857179</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124922</t>
+          <t>2026-03-10T04:05:19.857181</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124925</t>
+          <t>2026-03-10T04:05:19.857184</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124930</t>
+          <t>2026-03-10T04:05:19.857189</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124933</t>
+          <t>2026-03-10T04:05:19.857192</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124935</t>
+          <t>2026-03-10T04:05:19.857195</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124938</t>
+          <t>2026-03-10T04:05:19.857197</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124941</t>
+          <t>2026-03-10T04:05:19.857200</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124944</t>
+          <t>2026-03-10T04:05:19.857203</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124946</t>
+          <t>2026-03-10T04:05:19.857206</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124949</t>
+          <t>2026-03-10T04:05:19.857208</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124952</t>
+          <t>2026-03-10T04:05:19.857211</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124955</t>
+          <t>2026-03-10T04:05:19.857214</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124960</t>
+          <t>2026-03-10T04:05:19.857219</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124962</t>
+          <t>2026-03-10T04:05:19.857222</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124965</t>
+          <t>2026-03-10T04:05:19.857224</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124968</t>
+          <t>2026-03-10T04:05:19.857227</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124971</t>
+          <t>2026-03-10T04:05:19.857230</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124973</t>
+          <t>2026-03-10T04:05:19.857233</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124976</t>
+          <t>2026-03-10T04:05:19.857235</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124979</t>
+          <t>2026-03-10T04:05:19.857238</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124982</t>
+          <t>2026-03-10T04:05:19.857241</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857120</t>
+          <t>2026-03-11T04:06:20.499363</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857134</t>
+          <t>2026-03-11T04:06:20.499377</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857138</t>
+          <t>2026-03-11T04:06:20.499382</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857142</t>
+          <t>2026-03-11T04:06:20.499385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857145</t>
+          <t>2026-03-11T04:06:20.499388</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857148</t>
+          <t>2026-03-11T04:06:20.499391</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857151</t>
+          <t>2026-03-11T04:06:20.499394</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857158</t>
+          <t>2026-03-11T04:06:20.499401</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857161</t>
+          <t>2026-03-11T04:06:20.499405</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857164</t>
+          <t>2026-03-11T04:06:20.499408</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857167</t>
+          <t>2026-03-11T04:06:20.499410</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857170</t>
+          <t>2026-03-11T04:06:20.499413</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857173</t>
+          <t>2026-03-11T04:06:20.499416</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857176</t>
+          <t>2026-03-11T04:06:20.499419</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857179</t>
+          <t>2026-03-11T04:06:20.499422</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857181</t>
+          <t>2026-03-11T04:06:20.499425</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857184</t>
+          <t>2026-03-11T04:06:20.499427</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857189</t>
+          <t>2026-03-11T04:06:20.499433</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857192</t>
+          <t>2026-03-11T04:06:20.499435</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857195</t>
+          <t>2026-03-11T04:06:20.499438</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857197</t>
+          <t>2026-03-11T04:06:20.499441</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857200</t>
+          <t>2026-03-11T04:06:20.499444</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857203</t>
+          <t>2026-03-11T04:06:20.499446</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857206</t>
+          <t>2026-03-11T04:06:20.499449</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857208</t>
+          <t>2026-03-11T04:06:20.499452</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857211</t>
+          <t>2026-03-11T04:06:20.499455</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857214</t>
+          <t>2026-03-11T04:06:20.499458</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857219</t>
+          <t>2026-03-11T04:06:20.499462</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857222</t>
+          <t>2026-03-11T04:06:20.499465</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857224</t>
+          <t>2026-03-11T04:06:20.499468</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857227</t>
+          <t>2026-03-11T04:06:20.499470</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857230</t>
+          <t>2026-03-11T04:06:20.499473</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857233</t>
+          <t>2026-03-11T04:06:20.499476</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857235</t>
+          <t>2026-03-11T04:06:20.499479</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857238</t>
+          <t>2026-03-11T04:06:20.499481</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857241</t>
+          <t>2026-03-11T04:06:20.499484</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499363</t>
+          <t>2026-03-12T04:10:06.569143</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499377</t>
+          <t>2026-03-12T04:10:06.569164</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499382</t>
+          <t>2026-03-12T04:10:06.569170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499385</t>
+          <t>2026-03-12T04:10:06.569173</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499388</t>
+          <t>2026-03-12T04:10:06.569176</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499391</t>
+          <t>2026-03-12T04:10:06.569180</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499394</t>
+          <t>2026-03-12T04:10:06.569183</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499401</t>
+          <t>2026-03-12T04:10:06.569190</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499405</t>
+          <t>2026-03-12T04:10:06.569193</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499408</t>
+          <t>2026-03-12T04:10:06.569196</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499410</t>
+          <t>2026-03-12T04:10:06.569199</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499413</t>
+          <t>2026-03-12T04:10:06.569202</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499416</t>
+          <t>2026-03-12T04:10:06.569205</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499419</t>
+          <t>2026-03-12T04:10:06.569208</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499422</t>
+          <t>2026-03-12T04:10:06.569211</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499425</t>
+          <t>2026-03-12T04:10:06.569213</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499427</t>
+          <t>2026-03-12T04:10:06.569216</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499433</t>
+          <t>2026-03-12T04:10:06.569221</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499435</t>
+          <t>2026-03-12T04:10:06.569224</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499438</t>
+          <t>2026-03-12T04:10:06.569227</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499441</t>
+          <t>2026-03-12T04:10:06.569230</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499444</t>
+          <t>2026-03-12T04:10:06.569232</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499446</t>
+          <t>2026-03-12T04:10:06.569235</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499449</t>
+          <t>2026-03-12T04:10:06.569238</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499452</t>
+          <t>2026-03-12T04:10:06.569240</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499455</t>
+          <t>2026-03-12T04:10:06.569243</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499458</t>
+          <t>2026-03-12T04:10:06.569246</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499462</t>
+          <t>2026-03-12T04:10:06.569253</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499465</t>
+          <t>2026-03-12T04:10:06.569257</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499468</t>
+          <t>2026-03-12T04:10:06.569260</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499470</t>
+          <t>2026-03-12T04:10:06.569264</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499473</t>
+          <t>2026-03-12T04:10:06.569267</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499476</t>
+          <t>2026-03-12T04:10:06.569270</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499479</t>
+          <t>2026-03-12T04:10:06.569272</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499481</t>
+          <t>2026-03-12T04:10:06.569275</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499484</t>
+          <t>2026-03-12T04:10:06.569278</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569143</t>
+          <t>2026-03-13T04:08:47.727099</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569164</t>
+          <t>2026-03-13T04:08:47.727128</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569170</t>
+          <t>2026-03-13T04:08:47.727135</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569173</t>
+          <t>2026-03-13T04:08:47.727141</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569176</t>
+          <t>2026-03-13T04:08:47.727147</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569180</t>
+          <t>2026-03-13T04:08:47.727153</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569183</t>
+          <t>2026-03-13T04:08:47.727159</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569190</t>
+          <t>2026-03-13T04:08:47.727171</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569193</t>
+          <t>2026-03-13T04:08:47.727177</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569196</t>
+          <t>2026-03-13T04:08:47.727183</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569199</t>
+          <t>2026-03-13T04:08:47.727189</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569202</t>
+          <t>2026-03-13T04:08:47.727195</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569205</t>
+          <t>2026-03-13T04:08:47.727201</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569208</t>
+          <t>2026-03-13T04:08:47.727206</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569211</t>
+          <t>2026-03-13T04:08:47.727212</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569213</t>
+          <t>2026-03-13T04:08:47.727217</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569216</t>
+          <t>2026-03-13T04:08:47.727223</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569221</t>
+          <t>2026-03-13T04:08:47.727231</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569224</t>
+          <t>2026-03-13T04:08:47.727237</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569227</t>
+          <t>2026-03-13T04:08:47.727243</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569230</t>
+          <t>2026-03-13T04:08:47.727248</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569232</t>
+          <t>2026-03-13T04:08:47.727253</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569235</t>
+          <t>2026-03-13T04:08:47.727257</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569238</t>
+          <t>2026-03-13T04:08:47.727262</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569240</t>
+          <t>2026-03-13T04:08:47.727266</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1428</v>
+        <v>1452</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569243</t>
+          <t>2026-03-13T04:08:47.727271</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569246</t>
+          <t>2026-03-13T04:08:47.727277</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569253</t>
+          <t>2026-03-13T04:08:47.727283</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569257</t>
+          <t>2026-03-13T04:08:47.727286</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569260</t>
+          <t>2026-03-13T04:08:47.727289</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569264</t>
+          <t>2026-03-13T04:08:47.727292</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569267</t>
+          <t>2026-03-13T04:08:47.727294</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569270</t>
+          <t>2026-03-13T04:08:47.727297</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569272</t>
+          <t>2026-03-13T04:08:47.727300</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,72 +2754,267 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569275</t>
+          <t>2026-03-13T04:08:47.727303</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:47.727306</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:47.727308</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:47.727311</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>周大福</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>1380.00</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E40" t="n">
         <v>1380</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>涨</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-03-12T04:10:06.569278</t>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:47.727315</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727099</t>
+          <t>2026-03-14T04:07:11.012501</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727128</t>
+          <t>2026-03-14T04:07:11.012514</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727135</t>
+          <t>2026-03-14T04:07:11.012519</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727141</t>
+          <t>2026-03-14T04:07:11.012522</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727147</t>
+          <t>2026-03-14T04:07:11.012525</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727153</t>
+          <t>2026-03-14T04:07:11.012528</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727159</t>
+          <t>2026-03-14T04:07:11.012531</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727171</t>
+          <t>2026-03-14T04:07:11.012535</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727177</t>
+          <t>2026-03-14T04:07:11.012538</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727183</t>
+          <t>2026-03-14T04:07:11.012544</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727189</t>
+          <t>2026-03-14T04:07:11.012547</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727195</t>
+          <t>2026-03-14T04:07:11.012550</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727201</t>
+          <t>2026-03-14T04:07:11.012553</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727206</t>
+          <t>2026-03-14T04:07:11.012556</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727212</t>
+          <t>2026-03-14T04:07:11.012559</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727217</t>
+          <t>2026-03-14T04:07:11.012562</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727223</t>
+          <t>2026-03-14T04:07:11.012565</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727231</t>
+          <t>2026-03-14T04:07:11.012567</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727237</t>
+          <t>2026-03-14T04:07:11.012570</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727243</t>
+          <t>2026-03-14T04:07:11.012575</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727248</t>
+          <t>2026-03-14T04:07:11.012578</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727253</t>
+          <t>2026-03-14T04:07:11.012581</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727257</t>
+          <t>2026-03-14T04:07:11.012584</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727262</t>
+          <t>2026-03-14T04:07:11.012587</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727266</t>
+          <t>2026-03-14T04:07:11.012589</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727271</t>
+          <t>2026-03-14T04:07:11.012592</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727277</t>
+          <t>2026-03-14T04:07:11.012595</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727283</t>
+          <t>2026-03-14T04:07:11.012598</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727286</t>
+          <t>2026-03-14T04:07:11.012601</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727289</t>
+          <t>2026-03-14T04:07:11.012605</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727292</t>
+          <t>2026-03-14T04:07:11.012608</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727294</t>
+          <t>2026-03-14T04:07:11.012611</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727297</t>
+          <t>2026-03-14T04:07:11.012614</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727300</t>
+          <t>2026-03-14T04:07:11.012617</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727303</t>
+          <t>2026-03-14T04:07:11.012619</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727306</t>
+          <t>2026-03-14T04:07:11.012622</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727308</t>
+          <t>2026-03-14T04:07:11.012625</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727311</t>
+          <t>2026-03-14T04:07:11.012628</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727315</t>
+          <t>2026-03-14T04:07:11.012630</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012501</t>
+          <t>2026-03-15T04:29:47.143189</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012514</t>
+          <t>2026-03-15T04:29:47.143226</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012519</t>
+          <t>2026-03-15T04:29:47.143231</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012522</t>
+          <t>2026-03-15T04:29:47.143234</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012525</t>
+          <t>2026-03-15T04:29:47.143237</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012528</t>
+          <t>2026-03-15T04:29:47.143241</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012531</t>
+          <t>2026-03-15T04:29:47.143244</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012535</t>
+          <t>2026-03-15T04:29:47.143251</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012538</t>
+          <t>2026-03-15T04:29:47.143254</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012544</t>
+          <t>2026-03-15T04:29:47.143258</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012547</t>
+          <t>2026-03-15T04:29:47.143260</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012550</t>
+          <t>2026-03-15T04:29:47.143264</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012553</t>
+          <t>2026-03-15T04:29:47.143266</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012556</t>
+          <t>2026-03-15T04:29:47.143269</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012559</t>
+          <t>2026-03-15T04:29:47.143272</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012562</t>
+          <t>2026-03-15T04:29:47.143275</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012565</t>
+          <t>2026-03-15T04:29:47.143277</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012567</t>
+          <t>2026-03-15T04:29:47.143282</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012570</t>
+          <t>2026-03-15T04:29:47.143285</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012575</t>
+          <t>2026-03-15T04:29:47.143288</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012578</t>
+          <t>2026-03-15T04:29:47.143291</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012581</t>
+          <t>2026-03-15T04:29:47.143294</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012584</t>
+          <t>2026-03-15T04:29:47.143296</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012587</t>
+          <t>2026-03-15T04:29:47.143299</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012589</t>
+          <t>2026-03-15T04:29:47.143302</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012592</t>
+          <t>2026-03-15T04:29:47.143305</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012595</t>
+          <t>2026-03-15T04:29:47.143307</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012598</t>
+          <t>2026-03-15T04:29:47.143312</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012601</t>
+          <t>2026-03-15T04:29:47.143315</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012605</t>
+          <t>2026-03-15T04:29:47.143318</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012608</t>
+          <t>2026-03-15T04:29:47.143321</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012611</t>
+          <t>2026-03-15T04:29:47.143324</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012614</t>
+          <t>2026-03-15T04:29:47.143327</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012617</t>
+          <t>2026-03-15T04:29:47.143330</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012619</t>
+          <t>2026-03-15T04:29:47.143333</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012622</t>
+          <t>2026-03-15T04:29:47.143335</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012625</t>
+          <t>2026-03-15T04:29:47.143338</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012628</t>
+          <t>2026-03-15T04:29:47.143341</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012630</t>
+          <t>2026-03-15T04:29:47.143344</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143189</t>
+          <t>2026-03-16T04:36:48.961972</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143226</t>
+          <t>2026-03-16T04:36:48.961987</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143231</t>
+          <t>2026-03-16T04:36:48.961991</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143234</t>
+          <t>2026-03-16T04:36:48.961995</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143237</t>
+          <t>2026-03-16T04:36:48.961998</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143241</t>
+          <t>2026-03-16T04:36:48.962001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143244</t>
+          <t>2026-03-16T04:36:48.962004</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143251</t>
+          <t>2026-03-16T04:36:48.962008</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143254</t>
+          <t>2026-03-16T04:36:48.962015</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143258</t>
+          <t>2026-03-16T04:36:48.962018</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143260</t>
+          <t>2026-03-16T04:36:48.962021</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143264</t>
+          <t>2026-03-16T04:36:48.962024</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143266</t>
+          <t>2026-03-16T04:36:48.962028</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143269</t>
+          <t>2026-03-16T04:36:48.962031</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143272</t>
+          <t>2026-03-16T04:36:48.962033</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143275</t>
+          <t>2026-03-16T04:36:48.962037</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143277</t>
+          <t>2026-03-16T04:36:48.962039</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143282</t>
+          <t>2026-03-16T04:36:48.962043</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143285</t>
+          <t>2026-03-16T04:36:48.962048</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143288</t>
+          <t>2026-03-16T04:36:48.962051</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143291</t>
+          <t>2026-03-16T04:36:48.962054</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143294</t>
+          <t>2026-03-16T04:36:48.962057</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143296</t>
+          <t>2026-03-16T04:36:48.962060</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143299</t>
+          <t>2026-03-16T04:36:48.962063</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143302</t>
+          <t>2026-03-16T04:36:48.962066</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143305</t>
+          <t>2026-03-16T04:36:48.962069</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143307</t>
+          <t>2026-03-16T04:36:48.962072</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143312</t>
+          <t>2026-03-16T04:36:48.962075</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143315</t>
+          <t>2026-03-16T04:36:48.962080</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143318</t>
+          <t>2026-03-16T04:36:48.962083</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143321</t>
+          <t>2026-03-16T04:36:48.962086</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143324</t>
+          <t>2026-03-16T04:36:48.962089</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143327</t>
+          <t>2026-03-16T04:36:48.962092</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143330</t>
+          <t>2026-03-16T04:36:48.962095</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143333</t>
+          <t>2026-03-16T04:36:48.962098</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143335</t>
+          <t>2026-03-16T04:36:48.962101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143338</t>
+          <t>2026-03-16T04:36:48.962104</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143341</t>
+          <t>2026-03-16T04:36:48.962107</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3014,7 +3014,202 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143344</t>
+          <t>2026-03-16T04:36:48.962112</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:48.962115</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1380.00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:48.962118</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:48.962121</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961972</t>
+          <t>2026-03-17T04:14:32.873151</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961987</t>
+          <t>2026-03-17T04:14:32.873167</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961991</t>
+          <t>2026-03-17T04:14:32.873172</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961995</t>
+          <t>2026-03-17T04:14:32.873175</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961998</t>
+          <t>2026-03-17T04:14:32.873179</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962001</t>
+          <t>2026-03-17T04:14:32.873182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962004</t>
+          <t>2026-03-17T04:14:32.873185</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962008</t>
+          <t>2026-03-17T04:14:32.873189</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962015</t>
+          <t>2026-03-17T04:14:32.873192</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962018</t>
+          <t>2026-03-17T04:14:32.873195</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962021</t>
+          <t>2026-03-17T04:14:32.873201</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962024</t>
+          <t>2026-03-17T04:14:32.873204</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962028</t>
+          <t>2026-03-17T04:14:32.873207</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962031</t>
+          <t>2026-03-17T04:14:32.873210</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962033</t>
+          <t>2026-03-17T04:14:32.873213</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962037</t>
+          <t>2026-03-17T04:14:32.873216</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962039</t>
+          <t>2026-03-17T04:14:32.873219</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962043</t>
+          <t>2026-03-17T04:14:32.873222</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962048</t>
+          <t>2026-03-17T04:14:32.873225</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962051</t>
+          <t>2026-03-17T04:14:32.873227</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962054</t>
+          <t>2026-03-17T04:14:32.873232</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962057</t>
+          <t>2026-03-17T04:14:32.873235</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962060</t>
+          <t>2026-03-17T04:14:32.873238</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962063</t>
+          <t>2026-03-17T04:14:32.873241</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962066</t>
+          <t>2026-03-17T04:14:32.873244</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962069</t>
+          <t>2026-03-17T04:14:32.873247</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962072</t>
+          <t>2026-03-17T04:14:32.873250</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1452</v>
+        <v>1400</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962075</t>
+          <t>2026-03-17T04:14:32.873253</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962080</t>
+          <t>2026-03-17T04:14:32.873255</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962083</t>
+          <t>2026-03-17T04:14:32.873258</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962086</t>
+          <t>2026-03-17T04:14:32.873263</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962089</t>
+          <t>2026-03-17T04:14:32.873266</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962092</t>
+          <t>2026-03-17T04:14:32.873269</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962095</t>
+          <t>2026-03-17T04:14:32.873274</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1380</v>
+        <v>1433</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962098</t>
+          <t>2026-03-17T04:14:32.873277</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1384</v>
+        <v>1428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962101</t>
+          <t>2026-03-17T04:14:32.873280</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962104</t>
+          <t>2026-03-17T04:14:32.873283</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962107</t>
+          <t>2026-03-17T04:14:32.873285</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962112</t>
+          <t>2026-03-17T04:14:32.873288</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962115</t>
+          <t>2026-03-17T04:14:32.873291</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,72 +3144,267 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962118</t>
+          <t>2026-03-17T04:14:32.873296</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:32.873299</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>周生生</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>1377.00</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>1377</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>跌</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-16T04:36:48.962121</t>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:32.873302</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:32.873305</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1380.00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:32.873308</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873151</t>
+          <t>2026-03-18T04:22:02.688081</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873167</t>
+          <t>2026-03-18T04:22:02.688096</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873172</t>
+          <t>2026-03-18T04:22:02.688101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873175</t>
+          <t>2026-03-18T04:22:02.688104</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873179</t>
+          <t>2026-03-18T04:22:02.688108</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873182</t>
+          <t>2026-03-18T04:22:02.688111</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873185</t>
+          <t>2026-03-18T04:22:02.688114</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873189</t>
+          <t>2026-03-18T04:22:02.688118</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873192</t>
+          <t>2026-03-18T04:22:02.688121</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873195</t>
+          <t>2026-03-18T04:22:02.688124</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873201</t>
+          <t>2026-03-18T04:22:02.688131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873204</t>
+          <t>2026-03-18T04:22:02.688134</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873207</t>
+          <t>2026-03-18T04:22:02.688137</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873210</t>
+          <t>2026-03-18T04:22:02.688140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873213</t>
+          <t>2026-03-18T04:22:02.688143</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873216</t>
+          <t>2026-03-18T04:22:02.688160</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873219</t>
+          <t>2026-03-18T04:22:02.688164</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873222</t>
+          <t>2026-03-18T04:22:02.688167</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873225</t>
+          <t>2026-03-18T04:22:02.688170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1376</v>
+        <v>1390</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873227</t>
+          <t>2026-03-18T04:22:02.688173</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873232</t>
+          <t>2026-03-18T04:22:02.688178</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873235</t>
+          <t>2026-03-18T04:22:02.688181</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873238</t>
+          <t>2026-03-18T04:22:02.688184</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873241</t>
+          <t>2026-03-18T04:22:02.688187</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873244</t>
+          <t>2026-03-18T04:22:02.688190</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873247</t>
+          <t>2026-03-18T04:22:02.688193</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873250</t>
+          <t>2026-03-18T04:22:02.688196</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873253</t>
+          <t>2026-03-18T04:22:02.688199</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873255</t>
+          <t>2026-03-18T04:22:02.688202</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873258</t>
+          <t>2026-03-18T04:22:02.688205</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1452</v>
+        <v>1400</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873263</t>
+          <t>2026-03-18T04:22:02.688210</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873266</t>
+          <t>2026-03-18T04:22:02.688213</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873269</t>
+          <t>2026-03-18T04:22:02.688218</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873274</t>
+          <t>2026-03-18T04:22:02.688221</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873277</t>
+          <t>2026-03-18T04:22:02.688224</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873280</t>
+          <t>2026-03-18T04:22:02.688227</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873283</t>
+          <t>2026-03-18T04:22:02.688229</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1386</v>
+        <v>1428</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873285</t>
+          <t>2026-03-18T04:22:02.688232</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873288</t>
+          <t>2026-03-18T04:22:02.688235</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873291</t>
+          <t>2026-03-18T04:22:02.688238</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873296</t>
+          <t>2026-03-18T04:22:02.688243</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873299</t>
+          <t>2026-03-18T04:22:02.688246</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873302</t>
+          <t>2026-03-18T04:22:02.688249</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,72 +3339,267 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873305</t>
+          <t>2026-03-18T04:22:02.688252</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:02.688255</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>周大福</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>1380.00</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>1380</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>涨</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-03-17T04:14:32.873308</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:02.688258</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:02.688261</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:02.688263</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1358</v>
+        <v>1316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688081</t>
+          <t>2026-03-19T04:21:07.605930</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688096</t>
+          <t>2026-03-19T04:21:07.605946</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688101</t>
+          <t>2026-03-19T04:21:07.605951</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688104</t>
+          <t>2026-03-19T04:21:07.605954</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688108</t>
+          <t>2026-03-19T04:21:07.605958</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688111</t>
+          <t>2026-03-19T04:21:07.605961</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688114</t>
+          <t>2026-03-19T04:21:07.605964</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688118</t>
+          <t>2026-03-19T04:21:07.605970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688121</t>
+          <t>2026-03-19T04:21:07.605973</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688124</t>
+          <t>2026-03-19T04:21:07.605977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688131</t>
+          <t>2026-03-19T04:21:07.605982</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688134</t>
+          <t>2026-03-19T04:21:07.605985</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688137</t>
+          <t>2026-03-19T04:21:07.605988</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688140</t>
+          <t>2026-03-19T04:21:07.605991</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688143</t>
+          <t>2026-03-19T04:21:07.605994</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688160</t>
+          <t>2026-03-19T04:21:07.605997</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688164</t>
+          <t>2026-03-19T04:21:07.606000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688167</t>
+          <t>2026-03-19T04:21:07.606003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688170</t>
+          <t>2026-03-19T04:21:07.606006</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688173</t>
+          <t>2026-03-19T04:21:07.606009</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688178</t>
+          <t>2026-03-19T04:21:07.606014</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688181</t>
+          <t>2026-03-19T04:21:07.606017</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688184</t>
+          <t>2026-03-19T04:21:07.606020</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688187</t>
+          <t>2026-03-19T04:21:07.606023</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688190</t>
+          <t>2026-03-19T04:21:07.606026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688193</t>
+          <t>2026-03-19T04:21:07.606029</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688196</t>
+          <t>2026-03-19T04:21:07.606032</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688199</t>
+          <t>2026-03-19T04:21:07.606035</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688202</t>
+          <t>2026-03-19T04:21:07.606038</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688205</t>
+          <t>2026-03-19T04:21:07.606041</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688210</t>
+          <t>2026-03-19T04:21:07.606043</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688213</t>
+          <t>2026-03-19T04:21:07.606046</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688218</t>
+          <t>2026-03-19T04:21:07.606049</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688221</t>
+          <t>2026-03-19T04:21:07.606052</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688224</t>
+          <t>2026-03-19T04:21:07.606055</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688227</t>
+          <t>2026-03-19T04:21:07.606058</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688229</t>
+          <t>2026-03-19T04:21:07.606061</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688232</t>
+          <t>2026-03-19T04:21:07.606064</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688235</t>
+          <t>2026-03-19T04:21:07.606066</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688238</t>
+          <t>2026-03-19T04:21:07.606069</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688243</t>
+          <t>2026-03-19T04:21:07.606074</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688246</t>
+          <t>2026-03-19T04:21:07.606077</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688249</t>
+          <t>2026-03-19T04:21:07.606080</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688252</t>
+          <t>2026-03-19T04:21:07.606083</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688255</t>
+          <t>2026-03-19T04:21:07.606086</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688258</t>
+          <t>2026-03-19T04:21:07.606089</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,72 +3534,202 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688261</t>
+          <t>2026-03-19T04:21:07.606092</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:07.606094</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>周生生</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>1377.00</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E50" t="n">
         <v>1377</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>跌</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-03-18T04:22:02.688263</t>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:07.606097</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:07.606100</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1316</v>
+        <v>1268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605930</t>
+          <t>2026-03-20T04:10:43.744684</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605946</t>
+          <t>2026-03-20T04:10:43.744699</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1310</v>
+        <v>1269</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605951</t>
+          <t>2026-03-20T04:10:43.744704</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605954</t>
+          <t>2026-03-20T04:10:43.744707</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605958</t>
+          <t>2026-03-20T04:10:43.744710</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605961</t>
+          <t>2026-03-20T04:10:43.744713</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605964</t>
+          <t>2026-03-20T04:10:43.744717</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605970</t>
+          <t>2026-03-20T04:10:43.744721</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605973</t>
+          <t>2026-03-20T04:10:43.744724</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605977</t>
+          <t>2026-03-20T04:10:43.744727</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605982</t>
+          <t>2026-03-20T04:10:43.744733</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605985</t>
+          <t>2026-03-20T04:10:43.744736</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605988</t>
+          <t>2026-03-20T04:10:43.744739</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605991</t>
+          <t>2026-03-20T04:10:43.744742</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605994</t>
+          <t>2026-03-20T04:10:43.744745</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605997</t>
+          <t>2026-03-20T04:10:43.744748</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606000</t>
+          <t>2026-03-20T04:10:43.744751</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606003</t>
+          <t>2026-03-20T04:10:43.744754</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606006</t>
+          <t>2026-03-20T04:10:43.744757</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606009</t>
+          <t>2026-03-20T04:10:43.744760</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606014</t>
+          <t>2026-03-20T04:10:43.744765</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606017</t>
+          <t>2026-03-20T04:10:43.744768</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606020</t>
+          <t>2026-03-20T04:10:43.744771</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606023</t>
+          <t>2026-03-20T04:10:43.744774</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606026</t>
+          <t>2026-03-20T04:10:43.744777</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606029</t>
+          <t>2026-03-20T04:10:43.744779</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606032</t>
+          <t>2026-03-20T04:10:43.744782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606035</t>
+          <t>2026-03-20T04:10:43.744785</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606038</t>
+          <t>2026-03-20T04:10:43.744788</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606041</t>
+          <t>2026-03-20T04:10:43.744791</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606043</t>
+          <t>2026-03-20T04:10:43.744794</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606046</t>
+          <t>2026-03-20T04:10:43.744797</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606049</t>
+          <t>2026-03-20T04:10:43.744799</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606052</t>
+          <t>2026-03-20T04:10:43.744802</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606055</t>
+          <t>2026-03-20T04:10:43.744805</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606058</t>
+          <t>2026-03-20T04:10:43.744808</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606061</t>
+          <t>2026-03-20T04:10:43.744811</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606064</t>
+          <t>2026-03-20T04:10:43.744814</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606066</t>
+          <t>2026-03-20T04:10:43.744816</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606069</t>
+          <t>2026-03-20T04:10:43.744819</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606074</t>
+          <t>2026-03-20T04:10:43.744824</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606077</t>
+          <t>2026-03-20T04:10:43.744827</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606080</t>
+          <t>2026-03-20T04:10:43.744830</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606083</t>
+          <t>2026-03-20T04:10:43.744833</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1384</v>
+        <v>1428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606086</t>
+          <t>2026-03-20T04:10:43.744836</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606089</t>
+          <t>2026-03-20T04:10:43.744839</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606092</t>
+          <t>2026-03-20T04:10:43.744841</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606094</t>
+          <t>2026-03-20T04:10:43.744844</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606097</t>
+          <t>2026-03-20T04:10:43.744847</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606100</t>
+          <t>2026-03-20T04:10:43.744850</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744684</t>
+          <t>2026-03-21T04:01:59.791242</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744699</t>
+          <t>2026-03-21T04:01:59.791257</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744704</t>
+          <t>2026-03-21T04:01:59.791262</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744707</t>
+          <t>2026-03-21T04:01:59.791265</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744710</t>
+          <t>2026-03-21T04:01:59.791268</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744713</t>
+          <t>2026-03-21T04:01:59.791272</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744717</t>
+          <t>2026-03-21T04:01:59.791275</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744721</t>
+          <t>2026-03-21T04:01:59.791278</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744724</t>
+          <t>2026-03-21T04:01:59.791281</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744727</t>
+          <t>2026-03-21T04:01:59.791284</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744733</t>
+          <t>2026-03-21T04:01:59.791290</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744736</t>
+          <t>2026-03-21T04:01:59.791293</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744739</t>
+          <t>2026-03-21T04:01:59.791296</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744742</t>
+          <t>2026-03-21T04:01:59.791299</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744745</t>
+          <t>2026-03-21T04:01:59.791302</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744748</t>
+          <t>2026-03-21T04:01:59.791305</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744751</t>
+          <t>2026-03-21T04:01:59.791308</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744754</t>
+          <t>2026-03-21T04:01:59.791313</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744757</t>
+          <t>2026-03-21T04:01:59.791316</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744760</t>
+          <t>2026-03-21T04:01:59.791319</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744765</t>
+          <t>2026-03-21T04:01:59.791324</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744768</t>
+          <t>2026-03-21T04:01:59.791327</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744771</t>
+          <t>2026-03-21T04:01:59.791329</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744774</t>
+          <t>2026-03-21T04:01:59.791332</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744777</t>
+          <t>2026-03-21T04:01:59.791335</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744779</t>
+          <t>2026-03-21T04:01:59.791338</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744782</t>
+          <t>2026-03-21T04:01:59.791343</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744785</t>
+          <t>2026-03-21T04:01:59.791346</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744788</t>
+          <t>2026-03-21T04:01:59.791349</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744791</t>
+          <t>2026-03-21T04:01:59.791352</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744794</t>
+          <t>2026-03-21T04:01:59.791355</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744797</t>
+          <t>2026-03-21T04:01:59.791358</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744799</t>
+          <t>2026-03-21T04:01:59.791361</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744802</t>
+          <t>2026-03-21T04:01:59.791364</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744805</t>
+          <t>2026-03-21T04:01:59.791368</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744808</t>
+          <t>2026-03-21T04:01:59.791371</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744811</t>
+          <t>2026-03-21T04:01:59.791374</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744814</t>
+          <t>2026-03-21T04:01:59.791377</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744816</t>
+          <t>2026-03-21T04:01:59.791380</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744819</t>
+          <t>2026-03-21T04:01:59.791382</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744824</t>
+          <t>2026-03-21T04:01:59.791387</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744827</t>
+          <t>2026-03-21T04:01:59.791390</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744830</t>
+          <t>2026-03-21T04:01:59.791393</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744833</t>
+          <t>2026-03-21T04:01:59.791396</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744836</t>
+          <t>2026-03-21T04:01:59.791399</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744839</t>
+          <t>2026-03-21T04:01:59.791402</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744841</t>
+          <t>2026-03-21T04:01:59.791405</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744844</t>
+          <t>2026-03-21T04:01:59.791407</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744847</t>
+          <t>2026-03-21T04:01:59.791410</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744850</t>
+          <t>2026-03-21T04:01:59.791413</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791242</t>
+          <t>2026-03-22T04:16:38.321038</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791257</t>
+          <t>2026-03-22T04:16:38.321052</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791262</t>
+          <t>2026-03-22T04:16:38.321056</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791265</t>
+          <t>2026-03-22T04:16:38.321060</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791268</t>
+          <t>2026-03-22T04:16:38.321063</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791272</t>
+          <t>2026-03-22T04:16:38.321066</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791275</t>
+          <t>2026-03-22T04:16:38.321069</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791278</t>
+          <t>2026-03-22T04:16:38.321073</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791281</t>
+          <t>2026-03-22T04:16:38.321076</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791284</t>
+          <t>2026-03-22T04:16:38.321079</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791290</t>
+          <t>2026-03-22T04:16:38.321085</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791293</t>
+          <t>2026-03-22T04:16:38.321088</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791296</t>
+          <t>2026-03-22T04:16:38.321091</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791299</t>
+          <t>2026-03-22T04:16:38.321094</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791302</t>
+          <t>2026-03-22T04:16:38.321097</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791305</t>
+          <t>2026-03-22T04:16:38.321099</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791308</t>
+          <t>2026-03-22T04:16:38.321102</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791313</t>
+          <t>2026-03-22T04:16:38.321105</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791316</t>
+          <t>2026-03-22T04:16:38.321108</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791319</t>
+          <t>2026-03-22T04:16:38.321111</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791324</t>
+          <t>2026-03-22T04:16:38.321116</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791327</t>
+          <t>2026-03-22T04:16:38.321119</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791329</t>
+          <t>2026-03-22T04:16:38.321122</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791332</t>
+          <t>2026-03-22T04:16:38.321124</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791335</t>
+          <t>2026-03-22T04:16:38.321127</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791338</t>
+          <t>2026-03-22T04:16:38.321130</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791343</t>
+          <t>2026-03-22T04:16:38.321133</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791346</t>
+          <t>2026-03-22T04:16:38.321136</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791349</t>
+          <t>2026-03-22T04:16:38.321139</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791352</t>
+          <t>2026-03-22T04:16:38.321142</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791355</t>
+          <t>2026-03-22T04:16:38.321144</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791358</t>
+          <t>2026-03-22T04:16:38.321147</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791361</t>
+          <t>2026-03-22T04:16:38.321150</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791364</t>
+          <t>2026-03-22T04:16:38.321153</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791368</t>
+          <t>2026-03-22T04:16:38.321156</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791371</t>
+          <t>2026-03-22T04:16:38.321158</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791374</t>
+          <t>2026-03-22T04:16:38.321161</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791377</t>
+          <t>2026-03-22T04:16:38.321164</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791380</t>
+          <t>2026-03-22T04:16:38.321167</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791382</t>
+          <t>2026-03-22T04:16:38.321170</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791387</t>
+          <t>2026-03-22T04:16:38.321175</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791390</t>
+          <t>2026-03-22T04:16:38.321178</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791393</t>
+          <t>2026-03-22T04:16:38.321180</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791396</t>
+          <t>2026-03-22T04:16:38.321183</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791399</t>
+          <t>2026-03-22T04:16:38.321186</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791402</t>
+          <t>2026-03-22T04:16:38.321191</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791405</t>
+          <t>2026-03-22T04:16:38.321194</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791407</t>
+          <t>2026-03-22T04:16:38.321197</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791410</t>
+          <t>2026-03-22T04:16:38.321199</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791413</t>
+          <t>2026-03-22T04:16:38.321202</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321038</t>
+          <t>2026-03-23T04:26:07.613509</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321052</t>
+          <t>2026-03-23T04:26:07.613524</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1269</v>
+        <v>1200</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321056</t>
+          <t>2026-03-23T04:26:07.613528</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321060</t>
+          <t>2026-03-23T04:26:07.613532</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321063</t>
+          <t>2026-03-23T04:26:07.613535</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321066</t>
+          <t>2026-03-23T04:26:07.613538</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321069</t>
+          <t>2026-03-23T04:26:07.613541</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321073</t>
+          <t>2026-03-23T04:26:07.613545</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321076</t>
+          <t>2026-03-23T04:26:07.613551</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321079</t>
+          <t>2026-03-23T04:26:07.613555</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321085</t>
+          <t>2026-03-23T04:26:07.613560</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321088</t>
+          <t>2026-03-23T04:26:07.613563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321091</t>
+          <t>2026-03-23T04:26:07.613566</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321094</t>
+          <t>2026-03-23T04:26:07.613569</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321097</t>
+          <t>2026-03-23T04:26:07.613572</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321099</t>
+          <t>2026-03-23T04:26:07.613575</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321102</t>
+          <t>2026-03-23T04:26:07.613578</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321105</t>
+          <t>2026-03-23T04:26:07.613581</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321108</t>
+          <t>2026-03-23T04:26:07.613584</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321111</t>
+          <t>2026-03-23T04:26:07.613586</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321116</t>
+          <t>2026-03-23T04:26:07.613591</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321119</t>
+          <t>2026-03-23T04:26:07.613594</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321122</t>
+          <t>2026-03-23T04:26:07.613597</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321124</t>
+          <t>2026-03-23T04:26:07.613600</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321127</t>
+          <t>2026-03-23T04:26:07.613603</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321130</t>
+          <t>2026-03-23T04:26:07.613606</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321133</t>
+          <t>2026-03-23T04:26:07.613609</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321136</t>
+          <t>2026-03-23T04:26:07.613611</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321139</t>
+          <t>2026-03-23T04:26:07.613614</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321142</t>
+          <t>2026-03-23T04:26:07.613617</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321144</t>
+          <t>2026-03-23T04:26:07.613620</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321147</t>
+          <t>2026-03-23T04:26:07.613623</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321150</t>
+          <t>2026-03-23T04:26:07.613626</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321153</t>
+          <t>2026-03-23T04:26:07.613628</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321156</t>
+          <t>2026-03-23T04:26:07.613631</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321158</t>
+          <t>2026-03-23T04:26:07.613634</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321161</t>
+          <t>2026-03-23T04:26:07.613637</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321164</t>
+          <t>2026-03-23T04:26:07.613640</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321167</t>
+          <t>2026-03-23T04:26:07.613643</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1452</v>
+        <v>1401</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321170</t>
+          <t>2026-03-23T04:26:07.613645</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321175</t>
+          <t>2026-03-23T04:26:07.613650</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321178</t>
+          <t>2026-03-23T04:26:07.613653</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321180</t>
+          <t>2026-03-23T04:26:07.613656</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321183</t>
+          <t>2026-03-23T04:26:07.613659</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321186</t>
+          <t>2026-03-23T04:26:07.613662</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321191</t>
+          <t>2026-03-23T04:26:07.613665</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1386</v>
+        <v>1428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321194</t>
+          <t>2026-03-23T04:26:07.613668</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321197</t>
+          <t>2026-03-23T04:26:07.613670</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321199</t>
+          <t>2026-03-23T04:26:07.613673</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321202</t>
+          <t>2026-03-23T04:26:07.613676</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613509</t>
+          <t>2026-03-24T04:15:01.558151</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613524</t>
+          <t>2026-03-24T04:15:01.558164</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1200</v>
+        <v>1178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613528</t>
+          <t>2026-03-24T04:15:01.558169</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613532</t>
+          <t>2026-03-24T04:15:01.558172</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1269</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613535</t>
+          <t>2026-03-24T04:15:01.558175</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1267</v>
+        <v>1206</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613538</t>
+          <t>2026-03-24T04:15:01.558179</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1310</v>
+        <v>1267</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613541</t>
+          <t>2026-03-24T04:15:01.558182</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613545</t>
+          <t>2026-03-24T04:15:01.558185</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1318</v>
+        <v>1268</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613551</t>
+          <t>2026-03-24T04:15:01.558188</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613555</t>
+          <t>2026-03-24T04:15:01.558192</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613560</t>
+          <t>2026-03-24T04:15:01.558198</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613563</t>
+          <t>2026-03-24T04:15:01.558201</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613566</t>
+          <t>2026-03-24T04:15:01.558204</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613569</t>
+          <t>2026-03-24T04:15:01.558207</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613572</t>
+          <t>2026-03-24T04:15:01.558209</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613575</t>
+          <t>2026-03-24T04:15:01.558212</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613578</t>
+          <t>2026-03-24T04:15:01.558215</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613581</t>
+          <t>2026-03-24T04:15:01.558218</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613584</t>
+          <t>2026-03-24T04:15:01.558221</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613586</t>
+          <t>2026-03-24T04:15:01.558224</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613591</t>
+          <t>2026-03-24T04:15:01.558229</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613594</t>
+          <t>2026-03-24T04:15:01.558232</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613597</t>
+          <t>2026-03-24T04:15:01.558234</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613600</t>
+          <t>2026-03-24T04:15:01.558237</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613603</t>
+          <t>2026-03-24T04:15:01.558240</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613606</t>
+          <t>2026-03-24T04:15:01.558243</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613609</t>
+          <t>2026-03-24T04:15:01.558246</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613611</t>
+          <t>2026-03-24T04:15:01.558248</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613614</t>
+          <t>2026-03-24T04:15:01.558251</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613617</t>
+          <t>2026-03-24T04:15:01.558254</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613620</t>
+          <t>2026-03-24T04:15:01.558257</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613623</t>
+          <t>2026-03-24T04:15:01.558260</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613626</t>
+          <t>2026-03-24T04:15:01.558263</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613628</t>
+          <t>2026-03-24T04:15:01.558265</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613631</t>
+          <t>2026-03-24T04:15:01.558268</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613634</t>
+          <t>2026-03-24T04:15:01.558271</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613637</t>
+          <t>2026-03-24T04:15:01.558274</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613640</t>
+          <t>2026-03-24T04:15:01.558277</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613643</t>
+          <t>2026-03-24T04:15:01.558279</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613645</t>
+          <t>2026-03-24T04:15:01.558282</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613650</t>
+          <t>2026-03-24T04:15:01.558287</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613653</t>
+          <t>2026-03-24T04:15:01.558290</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613656</t>
+          <t>2026-03-24T04:15:01.558293</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1452</v>
+        <v>1401</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613659</t>
+          <t>2026-03-24T04:15:01.558296</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613662</t>
+          <t>2026-03-24T04:15:01.558299</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613665</t>
+          <t>2026-03-24T04:15:01.558301</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613668</t>
+          <t>2026-03-24T04:15:01.558304</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613670</t>
+          <t>2026-03-24T04:15:01.558307</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613673</t>
+          <t>2026-03-24T04:15:01.558310</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:07.613676</t>
+          <t>2026-03-24T04:15:01.558313</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1180</v>
+        <v>1237</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558151</t>
+          <t>2026-03-25T04:17:40.816886</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1185</v>
+        <v>1239</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558164</t>
+          <t>2026-03-25T04:17:40.816901</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558169</t>
+          <t>2026-03-25T04:17:40.816906</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558172</t>
+          <t>2026-03-25T04:17:40.816909</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558175</t>
+          <t>2026-03-25T04:17:40.816913</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558179</t>
+          <t>2026-03-25T04:17:40.816916</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558182</t>
+          <t>2026-03-25T04:17:40.816922</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558185</t>
+          <t>2026-03-25T04:17:40.816926</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1268</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558188</t>
+          <t>2026-03-25T04:17:40.816929</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558192</t>
+          <t>2026-03-25T04:17:40.816933</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1310</v>
+        <v>1267</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558198</t>
+          <t>2026-03-25T04:17:40.816938</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1316</v>
+        <v>1268</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558201</t>
+          <t>2026-03-25T04:17:40.816941</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558204</t>
+          <t>2026-03-25T04:17:40.816944</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558207</t>
+          <t>2026-03-25T04:17:40.816947</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558209</t>
+          <t>2026-03-25T04:17:40.816950</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558212</t>
+          <t>2026-03-25T04:17:40.816953</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558215</t>
+          <t>2026-03-25T04:17:40.816956</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558218</t>
+          <t>2026-03-25T04:17:40.816959</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558221</t>
+          <t>2026-03-25T04:17:40.816961</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558224</t>
+          <t>2026-03-25T04:17:40.816964</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558229</t>
+          <t>2026-03-25T04:17:40.816969</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558232</t>
+          <t>2026-03-25T04:17:40.816972</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1383</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558234</t>
+          <t>2026-03-25T04:17:40.816977</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558237</t>
+          <t>2026-03-25T04:17:40.816988</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558240</t>
+          <t>2026-03-25T04:17:40.816995</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558243</t>
+          <t>2026-03-25T04:17:40.817001</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558246</t>
+          <t>2026-03-25T04:17:40.817007</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558248</t>
+          <t>2026-03-25T04:17:40.817013</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558251</t>
+          <t>2026-03-25T04:17:40.817019</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558254</t>
+          <t>2026-03-25T04:17:40.817024</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558257</t>
+          <t>2026-03-25T04:17:40.817030</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558260</t>
+          <t>2026-03-25T04:17:40.817036</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558263</t>
+          <t>2026-03-25T04:17:40.817043</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558265</t>
+          <t>2026-03-25T04:17:40.817049</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558268</t>
+          <t>2026-03-25T04:17:40.817051</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558271</t>
+          <t>2026-03-25T04:17:40.817054</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558274</t>
+          <t>2026-03-25T04:17:40.817057</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558277</t>
+          <t>2026-03-25T04:17:40.817060</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558279</t>
+          <t>2026-03-25T04:17:40.817063</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558282</t>
+          <t>2026-03-25T04:17:40.817066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558287</t>
+          <t>2026-03-25T04:17:40.817072</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558290</t>
+          <t>2026-03-25T04:17:40.817075</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558293</t>
+          <t>2026-03-25T04:17:40.817078</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558296</t>
+          <t>2026-03-25T04:17:40.817081</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558299</t>
+          <t>2026-03-25T04:17:40.817084</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1452</v>
+        <v>1401</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558301</t>
+          <t>2026-03-25T04:17:40.817087</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558304</t>
+          <t>2026-03-25T04:17:40.817090</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558307</t>
+          <t>2026-03-25T04:17:40.817092</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558310</t>
+          <t>2026-03-25T04:17:40.817095</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:01.558313</t>
+          <t>2026-03-25T04:17:40.817098</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816886</t>
+          <t>2026-03-26T04:30:34.415005</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816901</t>
+          <t>2026-03-26T04:30:34.415021</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816906</t>
+          <t>2026-03-26T04:30:34.415025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816909</t>
+          <t>2026-03-26T04:30:34.415029</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816913</t>
+          <t>2026-03-26T04:30:34.415032</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816916</t>
+          <t>2026-03-26T04:30:34.415035</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816922</t>
+          <t>2026-03-26T04:30:34.415038</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816926</t>
+          <t>2026-03-26T04:30:34.415042</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816929</t>
+          <t>2026-03-26T04:30:34.415046</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816933</t>
+          <t>2026-03-26T04:30:34.415049</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816938</t>
+          <t>2026-03-26T04:30:34.415057</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816941</t>
+          <t>2026-03-26T04:30:34.415061</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816944</t>
+          <t>2026-03-26T04:30:34.415064</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816947</t>
+          <t>2026-03-26T04:30:34.415067</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816950</t>
+          <t>2026-03-26T04:30:34.415070</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816953</t>
+          <t>2026-03-26T04:30:34.415073</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816956</t>
+          <t>2026-03-26T04:30:34.415076</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816959</t>
+          <t>2026-03-26T04:30:34.415078</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816961</t>
+          <t>2026-03-26T04:30:34.415081</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816964</t>
+          <t>2026-03-26T04:30:34.415084</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816969</t>
+          <t>2026-03-26T04:30:34.415089</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816972</t>
+          <t>2026-03-26T04:30:34.415092</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816977</t>
+          <t>2026-03-26T04:30:34.415095</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816988</t>
+          <t>2026-03-26T04:30:34.415098</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.816995</t>
+          <t>2026-03-26T04:30:34.415101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817001</t>
+          <t>2026-03-26T04:30:34.415104</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817007</t>
+          <t>2026-03-26T04:30:34.415107</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817013</t>
+          <t>2026-03-26T04:30:34.415110</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817019</t>
+          <t>2026-03-26T04:30:34.415112</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817024</t>
+          <t>2026-03-26T04:30:34.415115</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817030</t>
+          <t>2026-03-26T04:30:34.415118</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817036</t>
+          <t>2026-03-26T04:30:34.415121</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817043</t>
+          <t>2026-03-26T04:30:34.415124</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817049</t>
+          <t>2026-03-26T04:30:34.415127</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817051</t>
+          <t>2026-03-26T04:30:34.415130</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817054</t>
+          <t>2026-03-26T04:30:34.415132</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817057</t>
+          <t>2026-03-26T04:30:34.415135</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817060</t>
+          <t>2026-03-26T04:30:34.415138</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817063</t>
+          <t>2026-03-26T04:30:34.415141</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817066</t>
+          <t>2026-03-26T04:30:34.415144</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817072</t>
+          <t>2026-03-26T04:30:34.415149</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817075</t>
+          <t>2026-03-26T04:30:34.415152</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817078</t>
+          <t>2026-03-26T04:30:34.415155</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817081</t>
+          <t>2026-03-26T04:30:34.415158</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817084</t>
+          <t>2026-03-26T04:30:34.415161</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817087</t>
+          <t>2026-03-26T04:30:34.415163</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817090</t>
+          <t>2026-03-26T04:30:34.415166</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817092</t>
+          <t>2026-03-26T04:30:34.415169</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817095</t>
+          <t>2026-03-26T04:30:34.415172</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:40.817098</t>
+          <t>2026-03-26T04:30:34.415175</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415005</t>
+          <t>2026-03-27T04:31:21.602003</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415021</t>
+          <t>2026-03-27T04:31:21.602017</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415025</t>
+          <t>2026-03-27T04:31:21.602022</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415029</t>
+          <t>2026-03-27T04:31:21.602025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415032</t>
+          <t>2026-03-27T04:31:21.602028</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415035</t>
+          <t>2026-03-27T04:31:21.602032</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415038</t>
+          <t>2026-03-27T04:31:21.602035</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415042</t>
+          <t>2026-03-27T04:31:21.602038</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415046</t>
+          <t>2026-03-27T04:31:21.602042</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415049</t>
+          <t>2026-03-27T04:31:21.602045</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415057</t>
+          <t>2026-03-27T04:31:21.602050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415061</t>
+          <t>2026-03-27T04:31:21.602054</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415064</t>
+          <t>2026-03-27T04:31:21.602057</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415067</t>
+          <t>2026-03-27T04:31:21.602060</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415070</t>
+          <t>2026-03-27T04:31:21.602063</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415073</t>
+          <t>2026-03-27T04:31:21.602065</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415076</t>
+          <t>2026-03-27T04:31:21.602068</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415078</t>
+          <t>2026-03-27T04:31:21.602071</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415081</t>
+          <t>2026-03-27T04:31:21.602074</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415084</t>
+          <t>2026-03-27T04:31:21.602077</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415089</t>
+          <t>2026-03-27T04:31:21.602081</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415092</t>
+          <t>2026-03-27T04:31:21.602084</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415095</t>
+          <t>2026-03-27T04:31:21.602087</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415098</t>
+          <t>2026-03-27T04:31:21.602090</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415101</t>
+          <t>2026-03-27T04:31:21.602093</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415104</t>
+          <t>2026-03-27T04:31:21.602096</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415107</t>
+          <t>2026-03-27T04:31:21.602099</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415110</t>
+          <t>2026-03-27T04:31:21.602102</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415112</t>
+          <t>2026-03-27T04:31:21.602104</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415115</t>
+          <t>2026-03-27T04:31:21.602107</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415118</t>
+          <t>2026-03-27T04:31:21.602110</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415121</t>
+          <t>2026-03-27T04:31:21.602113</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415124</t>
+          <t>2026-03-27T04:31:21.602115</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415127</t>
+          <t>2026-03-27T04:31:21.602118</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415130</t>
+          <t>2026-03-27T04:31:21.602121</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415132</t>
+          <t>2026-03-27T04:31:21.602124</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415135</t>
+          <t>2026-03-27T04:31:21.602127</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415138</t>
+          <t>2026-03-27T04:31:21.602130</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415141</t>
+          <t>2026-03-27T04:31:21.602132</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415144</t>
+          <t>2026-03-27T04:31:21.602135</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415149</t>
+          <t>2026-03-27T04:31:21.602140</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415152</t>
+          <t>2026-03-27T04:31:21.602143</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415155</t>
+          <t>2026-03-27T04:31:21.602146</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415158</t>
+          <t>2026-03-27T04:31:21.602148</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415161</t>
+          <t>2026-03-27T04:31:21.602151</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415163</t>
+          <t>2026-03-27T04:31:21.602154</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415166</t>
+          <t>2026-03-27T04:31:21.602159</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415169</t>
+          <t>2026-03-27T04:31:21.602162</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415172</t>
+          <t>2026-03-27T04:31:21.602164</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:34.415175</t>
+          <t>2026-03-27T04:31:21.602167</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602003</t>
+          <t>2026-03-28T04:16:56.720966</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602017</t>
+          <t>2026-03-28T04:16:56.720981</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602022</t>
+          <t>2026-03-28T04:16:56.720986</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602025</t>
+          <t>2026-03-28T04:16:56.720989</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602028</t>
+          <t>2026-03-28T04:16:56.720992</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602032</t>
+          <t>2026-03-28T04:16:56.720996</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602035</t>
+          <t>2026-03-28T04:16:56.720999</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602038</t>
+          <t>2026-03-28T04:16:56.721003</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1237</v>
+        <v>1246</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602042</t>
+          <t>2026-03-28T04:16:56.721006</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602045</t>
+          <t>2026-03-28T04:16:56.721009</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602050</t>
+          <t>2026-03-28T04:16:56.721015</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602054</t>
+          <t>2026-03-28T04:16:56.721018</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602057</t>
+          <t>2026-03-28T04:16:56.721022</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602060</t>
+          <t>2026-03-28T04:16:56.721024</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602063</t>
+          <t>2026-03-28T04:16:56.721027</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602065</t>
+          <t>2026-03-28T04:16:56.721030</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602068</t>
+          <t>2026-03-28T04:16:56.721033</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602071</t>
+          <t>2026-03-28T04:16:56.721036</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602074</t>
+          <t>2026-03-28T04:16:56.721039</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602077</t>
+          <t>2026-03-28T04:16:56.721042</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602081</t>
+          <t>2026-03-28T04:16:56.721047</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602084</t>
+          <t>2026-03-28T04:16:56.721049</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602087</t>
+          <t>2026-03-28T04:16:56.721052</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602090</t>
+          <t>2026-03-28T04:16:56.721055</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602093</t>
+          <t>2026-03-28T04:16:56.721058</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602096</t>
+          <t>2026-03-28T04:16:56.721061</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602099</t>
+          <t>2026-03-28T04:16:56.721064</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602102</t>
+          <t>2026-03-28T04:16:56.721067</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602104</t>
+          <t>2026-03-28T04:16:56.721070</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602107</t>
+          <t>2026-03-28T04:16:56.721073</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602110</t>
+          <t>2026-03-28T04:16:56.721075</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602113</t>
+          <t>2026-03-28T04:16:56.721078</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602115</t>
+          <t>2026-03-28T04:16:56.721081</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602118</t>
+          <t>2026-03-28T04:16:56.721084</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602121</t>
+          <t>2026-03-28T04:16:56.721087</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602124</t>
+          <t>2026-03-28T04:16:56.721090</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602127</t>
+          <t>2026-03-28T04:16:56.721092</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602130</t>
+          <t>2026-03-28T04:16:56.721095</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602132</t>
+          <t>2026-03-28T04:16:56.721098</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602135</t>
+          <t>2026-03-28T04:16:56.721101</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602140</t>
+          <t>2026-03-28T04:16:56.721105</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602143</t>
+          <t>2026-03-28T04:16:56.721108</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1378</v>
+        <v>1371</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602146</t>
+          <t>2026-03-28T04:16:56.721111</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602148</t>
+          <t>2026-03-28T04:16:56.721114</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602151</t>
+          <t>2026-03-28T04:16:56.721117</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602154</t>
+          <t>2026-03-28T04:16:56.721120</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602159</t>
+          <t>2026-03-28T04:16:56.721123</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602162</t>
+          <t>2026-03-28T04:16:56.721125</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602164</t>
+          <t>2026-03-28T04:16:56.721128</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:21.602167</t>
+          <t>2026-03-28T04:16:56.721133</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.720966</t>
+          <t>2026-03-29T04:34:51.560814</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.720981</t>
+          <t>2026-03-29T04:34:51.560830</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.720986</t>
+          <t>2026-03-29T04:34:51.560835</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.720989</t>
+          <t>2026-03-29T04:34:51.560838</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.720992</t>
+          <t>2026-03-29T04:34:51.560841</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.720996</t>
+          <t>2026-03-29T04:34:51.560845</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.720999</t>
+          <t>2026-03-29T04:34:51.560848</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721003</t>
+          <t>2026-03-29T04:34:51.560851</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721006</t>
+          <t>2026-03-29T04:34:51.560855</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721009</t>
+          <t>2026-03-29T04:34:51.560858</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721015</t>
+          <t>2026-03-29T04:34:51.560864</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721018</t>
+          <t>2026-03-29T04:34:51.560867</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721022</t>
+          <t>2026-03-29T04:34:51.560870</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721024</t>
+          <t>2026-03-29T04:34:51.560873</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721027</t>
+          <t>2026-03-29T04:34:51.560876</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721030</t>
+          <t>2026-03-29T04:34:51.560878</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721033</t>
+          <t>2026-03-29T04:34:51.560881</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721036</t>
+          <t>2026-03-29T04:34:51.560884</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721039</t>
+          <t>2026-03-29T04:34:51.560887</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721042</t>
+          <t>2026-03-29T04:34:51.560890</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721047</t>
+          <t>2026-03-29T04:34:51.560894</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721049</t>
+          <t>2026-03-29T04:34:51.560897</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721052</t>
+          <t>2026-03-29T04:34:51.560900</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721055</t>
+          <t>2026-03-29T04:34:51.560920</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721058</t>
+          <t>2026-03-29T04:34:51.560924</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721061</t>
+          <t>2026-03-29T04:34:51.560927</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721064</t>
+          <t>2026-03-29T04:34:51.560930</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721067</t>
+          <t>2026-03-29T04:34:51.560933</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721070</t>
+          <t>2026-03-29T04:34:51.560936</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721073</t>
+          <t>2026-03-29T04:34:51.560939</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721075</t>
+          <t>2026-03-29T04:34:51.560942</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721078</t>
+          <t>2026-03-29T04:34:51.560944</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721081</t>
+          <t>2026-03-29T04:34:51.560949</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721084</t>
+          <t>2026-03-29T04:34:51.560952</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721087</t>
+          <t>2026-03-29T04:34:51.560955</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721090</t>
+          <t>2026-03-29T04:34:51.560958</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721092</t>
+          <t>2026-03-29T04:34:51.560961</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721095</t>
+          <t>2026-03-29T04:34:51.560964</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721098</t>
+          <t>2026-03-29T04:34:51.560967</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721101</t>
+          <t>2026-03-29T04:34:51.560969</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721105</t>
+          <t>2026-03-29T04:34:51.560974</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721108</t>
+          <t>2026-03-29T04:34:51.560977</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721111</t>
+          <t>2026-03-29T04:34:51.560980</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721114</t>
+          <t>2026-03-29T04:34:51.560983</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721117</t>
+          <t>2026-03-29T04:34:51.560985</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721120</t>
+          <t>2026-03-29T04:34:51.560988</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721123</t>
+          <t>2026-03-29T04:34:51.560991</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721125</t>
+          <t>2026-03-29T04:34:51.560994</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721128</t>
+          <t>2026-03-29T04:34:51.560997</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:56.721133</t>
+          <t>2026-03-29T04:34:51.560999</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560814</t>
+          <t>2026-03-30T04:42:12.666581</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560830</t>
+          <t>2026-03-30T04:42:12.666598</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560835</t>
+          <t>2026-03-30T04:42:12.666603</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560838</t>
+          <t>2026-03-30T04:42:12.666607</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560841</t>
+          <t>2026-03-30T04:42:12.666611</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560845</t>
+          <t>2026-03-30T04:42:12.666614</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560848</t>
+          <t>2026-03-30T04:42:12.666618</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560851</t>
+          <t>2026-03-30T04:42:12.666621</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560855</t>
+          <t>2026-03-30T04:42:12.666624</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560858</t>
+          <t>2026-03-30T04:42:12.666630</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1185</v>
+        <v>1237</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560864</t>
+          <t>2026-03-30T04:42:12.666635</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560867</t>
+          <t>2026-03-30T04:42:12.666639</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560870</t>
+          <t>2026-03-30T04:42:12.666642</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560873</t>
+          <t>2026-03-30T04:42:12.666644</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560876</t>
+          <t>2026-03-30T04:42:12.666647</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560878</t>
+          <t>2026-03-30T04:42:12.666650</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1268</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560881</t>
+          <t>2026-03-30T04:42:12.666653</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560884</t>
+          <t>2026-03-30T04:42:12.666656</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560887</t>
+          <t>2026-03-30T04:42:12.666659</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560890</t>
+          <t>2026-03-30T04:42:12.666662</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560894</t>
+          <t>2026-03-30T04:42:12.666666</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560897</t>
+          <t>2026-03-30T04:42:12.666669</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1359</v>
+        <v>1318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560900</t>
+          <t>2026-03-30T04:42:12.666672</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560920</t>
+          <t>2026-03-30T04:42:12.666675</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560924</t>
+          <t>2026-03-30T04:42:12.666678</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560927</t>
+          <t>2026-03-30T04:42:12.666681</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560930</t>
+          <t>2026-03-30T04:42:12.666684</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560933</t>
+          <t>2026-03-30T04:42:12.666686</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560936</t>
+          <t>2026-03-30T04:42:12.666689</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560939</t>
+          <t>2026-03-30T04:42:12.666692</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560942</t>
+          <t>2026-03-30T04:42:12.666695</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560944</t>
+          <t>2026-03-30T04:42:12.666698</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560949</t>
+          <t>2026-03-30T04:42:12.666700</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560952</t>
+          <t>2026-03-30T04:42:12.666703</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560955</t>
+          <t>2026-03-30T04:42:12.666706</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560958</t>
+          <t>2026-03-30T04:42:12.666709</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560961</t>
+          <t>2026-03-30T04:42:12.666712</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560964</t>
+          <t>2026-03-30T04:42:12.666715</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1401</v>
+        <v>1386</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560967</t>
+          <t>2026-03-30T04:42:12.666718</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560969</t>
+          <t>2026-03-30T04:42:12.666720</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560974</t>
+          <t>2026-03-30T04:42:12.666725</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560977</t>
+          <t>2026-03-30T04:42:12.666728</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560980</t>
+          <t>2026-03-30T04:42:12.666731</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560983</t>
+          <t>2026-03-30T04:42:12.666734</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560985</t>
+          <t>2026-03-30T04:42:12.666737</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560988</t>
+          <t>2026-03-30T04:42:12.666740</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560991</t>
+          <t>2026-03-30T04:42:12.666743</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560994</t>
+          <t>2026-03-30T04:42:12.666745</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560997</t>
+          <t>2026-03-30T04:42:12.666748</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:51.560999</t>
+          <t>2026-03-30T04:42:12.666751</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666581</t>
+          <t>2026-03-31T04:33:40.326397</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666598</t>
+          <t>2026-03-31T04:33:40.326412</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666603</t>
+          <t>2026-03-31T04:33:40.326417</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666607</t>
+          <t>2026-03-31T04:33:40.326420</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666611</t>
+          <t>2026-03-31T04:33:40.326423</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666614</t>
+          <t>2026-03-31T04:33:40.326427</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666618</t>
+          <t>2026-03-31T04:33:40.326430</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666621</t>
+          <t>2026-03-31T04:33:40.326433</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666624</t>
+          <t>2026-03-31T04:33:40.326436</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666630</t>
+          <t>2026-03-31T04:33:40.326440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666635</t>
+          <t>2026-03-31T04:33:40.326446</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666639</t>
+          <t>2026-03-31T04:33:40.326449</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666642</t>
+          <t>2026-03-31T04:33:40.326452</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666644</t>
+          <t>2026-03-31T04:33:40.326454</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666647</t>
+          <t>2026-03-31T04:33:40.326457</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666650</t>
+          <t>2026-03-31T04:33:40.326460</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666653</t>
+          <t>2026-03-31T04:33:40.326463</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666656</t>
+          <t>2026-03-31T04:33:40.326466</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666659</t>
+          <t>2026-03-31T04:33:40.326469</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666662</t>
+          <t>2026-03-31T04:33:40.326471</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666666</t>
+          <t>2026-03-31T04:33:40.326476</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666669</t>
+          <t>2026-03-31T04:33:40.326479</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666672</t>
+          <t>2026-03-31T04:33:40.326482</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666675</t>
+          <t>2026-03-31T04:33:40.326484</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666678</t>
+          <t>2026-03-31T04:33:40.326487</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666681</t>
+          <t>2026-03-31T04:33:40.326490</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666684</t>
+          <t>2026-03-31T04:33:40.326493</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666686</t>
+          <t>2026-03-31T04:33:40.326496</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666689</t>
+          <t>2026-03-31T04:33:40.326499</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666692</t>
+          <t>2026-03-31T04:33:40.326501</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666695</t>
+          <t>2026-03-31T04:33:40.326504</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666698</t>
+          <t>2026-03-31T04:33:40.326507</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666700</t>
+          <t>2026-03-31T04:33:40.326510</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666703</t>
+          <t>2026-03-31T04:33:40.326513</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666706</t>
+          <t>2026-03-31T04:33:40.326515</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666709</t>
+          <t>2026-03-31T04:33:40.326518</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666712</t>
+          <t>2026-03-31T04:33:40.326521</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666715</t>
+          <t>2026-03-31T04:33:40.326526</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666718</t>
+          <t>2026-03-31T04:33:40.326528</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666720</t>
+          <t>2026-03-31T04:33:40.326531</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666725</t>
+          <t>2026-03-31T04:33:40.326536</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666728</t>
+          <t>2026-03-31T04:33:40.326539</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666731</t>
+          <t>2026-03-31T04:33:40.326541</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666734</t>
+          <t>2026-03-31T04:33:40.326544</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666737</t>
+          <t>2026-03-31T04:33:40.326547</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666740</t>
+          <t>2026-03-31T04:33:40.326550</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666743</t>
+          <t>2026-03-31T04:33:40.326553</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666745</t>
+          <t>2026-03-31T04:33:40.326555</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666748</t>
+          <t>2026-03-31T04:33:40.326558</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:12.666751</t>
+          <t>2026-03-31T04:33:40.326561</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326397</t>
+          <t>2026-04-01T04:44:32.741687</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326412</t>
+          <t>2026-04-01T04:44:32.741703</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326417</t>
+          <t>2026-04-01T04:44:32.741708</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326420</t>
+          <t>2026-04-01T04:44:32.741711</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326423</t>
+          <t>2026-04-01T04:44:32.741714</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326427</t>
+          <t>2026-04-01T04:44:32.741718</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326430</t>
+          <t>2026-04-01T04:44:32.741721</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326433</t>
+          <t>2026-04-01T04:44:32.741725</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326436</t>
+          <t>2026-04-01T04:44:32.741728</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326440</t>
+          <t>2026-04-01T04:44:32.741731</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326446</t>
+          <t>2026-04-01T04:44:32.741734</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326449</t>
+          <t>2026-04-01T04:44:32.741740</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326452</t>
+          <t>2026-04-01T04:44:32.741743</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326454</t>
+          <t>2026-04-01T04:44:32.741746</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326457</t>
+          <t>2026-04-01T04:44:32.741749</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1180</v>
+        <v>1237</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326460</t>
+          <t>2026-04-01T04:44:32.741751</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326463</t>
+          <t>2026-04-01T04:44:32.741754</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1185</v>
+        <v>1239</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326466</t>
+          <t>2026-04-01T04:44:32.741757</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326469</t>
+          <t>2026-04-01T04:44:32.741760</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1206</v>
+        <v>1185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326471</t>
+          <t>2026-04-01T04:44:32.741763</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1200</v>
+        <v>1178</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326476</t>
+          <t>2026-04-01T04:44:32.741766</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326479</t>
+          <t>2026-04-01T04:44:32.741771</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1269</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326482</t>
+          <t>2026-04-01T04:44:32.741774</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326484</t>
+          <t>2026-04-01T04:44:32.741777</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326487</t>
+          <t>2026-04-01T04:44:32.741780</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326490</t>
+          <t>2026-04-01T04:44:32.741782</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326493</t>
+          <t>2026-04-01T04:44:32.741785</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326496</t>
+          <t>2026-04-01T04:44:32.741788</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326499</t>
+          <t>2026-04-01T04:44:32.741791</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326501</t>
+          <t>2026-04-01T04:44:32.741794</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326504</t>
+          <t>2026-04-01T04:44:32.741797</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326507</t>
+          <t>2026-04-01T04:44:32.741803</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326510</t>
+          <t>2026-04-01T04:44:32.741806</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326513</t>
+          <t>2026-04-01T04:44:32.741809</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326515</t>
+          <t>2026-04-01T04:44:32.741812</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326518</t>
+          <t>2026-04-01T04:44:32.741815</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326521</t>
+          <t>2026-04-01T04:44:32.741818</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326526</t>
+          <t>2026-04-01T04:44:32.741821</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326528</t>
+          <t>2026-04-01T04:44:32.741823</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326531</t>
+          <t>2026-04-01T04:44:32.741826</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326536</t>
+          <t>2026-04-01T04:44:32.741829</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326539</t>
+          <t>2026-04-01T04:44:32.741834</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326541</t>
+          <t>2026-04-01T04:44:32.741837</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326544</t>
+          <t>2026-04-01T04:44:32.741840</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326547</t>
+          <t>2026-04-01T04:44:32.741842</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326550</t>
+          <t>2026-04-01T04:44:32.741845</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326553</t>
+          <t>2026-04-01T04:44:32.741848</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326555</t>
+          <t>2026-04-01T04:44:32.741851</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326558</t>
+          <t>2026-04-01T04:44:32.741854</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:40.326561</t>
+          <t>2026-04-01T04:44:32.741857</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741687</t>
+          <t>2026-04-02T04:27:07.125116</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741703</t>
+          <t>2026-04-02T04:27:07.125132</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741708</t>
+          <t>2026-04-02T04:27:07.125136</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1228</v>
+        <v>1266</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741711</t>
+          <t>2026-04-02T04:27:07.125139</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741714</t>
+          <t>2026-04-02T04:27:07.125143</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1223</v>
+        <v>1268</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741718</t>
+          <t>2026-04-02T04:27:07.125146</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741721</t>
+          <t>2026-04-02T04:27:07.125149</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741725</t>
+          <t>2026-04-02T04:27:07.125153</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741728</t>
+          <t>2026-04-02T04:27:07.125156</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741731</t>
+          <t>2026-04-02T04:27:07.125159</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741734</t>
+          <t>2026-04-02T04:27:07.125162</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741740</t>
+          <t>2026-04-02T04:27:07.125169</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741743</t>
+          <t>2026-04-02T04:27:07.125172</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741746</t>
+          <t>2026-04-02T04:27:07.125175</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741749</t>
+          <t>2026-04-02T04:27:07.125178</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741751</t>
+          <t>2026-04-02T04:27:07.125181</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741754</t>
+          <t>2026-04-02T04:27:07.125184</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741757</t>
+          <t>2026-04-02T04:27:07.125187</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1180</v>
+        <v>1246</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741760</t>
+          <t>2026-04-02T04:27:07.125189</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1185</v>
+        <v>1237</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741763</t>
+          <t>2026-04-02T04:27:07.125192</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1178</v>
+        <v>1239</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741766</t>
+          <t>2026-04-02T04:27:07.125195</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1206</v>
+        <v>1178</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741771</t>
+          <t>2026-04-02T04:27:07.125200</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741774</t>
+          <t>2026-04-02T04:27:07.125202</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741777</t>
+          <t>2026-04-02T04:27:07.125205</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741780</t>
+          <t>2026-04-02T04:27:07.125208</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741782</t>
+          <t>2026-04-02T04:27:07.125211</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1269</v>
+        <v>1200</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741785</t>
+          <t>2026-04-02T04:27:07.125214</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1310</v>
+        <v>1267</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741788</t>
+          <t>2026-04-02T04:27:07.125217</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741791</t>
+          <t>2026-04-02T04:27:07.125220</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1318</v>
+        <v>1268</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741794</t>
+          <t>2026-04-02T04:27:07.125222</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741797</t>
+          <t>2026-04-02T04:27:07.125225</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741803</t>
+          <t>2026-04-02T04:27:07.125230</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741806</t>
+          <t>2026-04-02T04:27:07.125233</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741809</t>
+          <t>2026-04-02T04:27:07.125236</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741812</t>
+          <t>2026-04-02T04:27:07.125240</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741815</t>
+          <t>2026-04-02T04:27:07.125243</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741818</t>
+          <t>2026-04-02T04:27:07.125246</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741821</t>
+          <t>2026-04-02T04:27:07.125249</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741823</t>
+          <t>2026-04-02T04:27:07.125252</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741826</t>
+          <t>2026-04-02T04:27:07.125254</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741829</t>
+          <t>2026-04-02T04:27:07.125257</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741834</t>
+          <t>2026-04-02T04:27:07.125262</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741837</t>
+          <t>2026-04-02T04:27:07.125265</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741840</t>
+          <t>2026-04-02T04:27:07.125267</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741842</t>
+          <t>2026-04-02T04:27:07.125270</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741845</t>
+          <t>2026-04-02T04:27:07.125273</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1401</v>
+        <v>1386</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741848</t>
+          <t>2026-04-02T04:27:07.125276</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741851</t>
+          <t>2026-04-02T04:27:07.125280</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741854</t>
+          <t>2026-04-02T04:27:07.125282</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:32.741857</t>
+          <t>2026-04-02T04:27:07.125285</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125116</t>
+          <t>2026-04-03T04:27:18.994739</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125132</t>
+          <t>2026-04-03T04:27:18.994754</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125136</t>
+          <t>2026-04-03T04:27:18.994759</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125139</t>
+          <t>2026-04-03T04:27:18.994763</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125143</t>
+          <t>2026-04-03T04:27:18.994766</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125146</t>
+          <t>2026-04-03T04:27:18.994769</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125149</t>
+          <t>2026-04-03T04:27:18.994772</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125153</t>
+          <t>2026-04-03T04:27:18.994795</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125156</t>
+          <t>2026-04-03T04:27:18.994798</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125159</t>
+          <t>2026-04-03T04:27:18.994802</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125162</t>
+          <t>2026-04-03T04:27:18.994805</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125169</t>
+          <t>2026-04-03T04:27:18.994811</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125172</t>
+          <t>2026-04-03T04:27:18.994814</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125175</t>
+          <t>2026-04-03T04:27:18.994817</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125178</t>
+          <t>2026-04-03T04:27:18.994820</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125181</t>
+          <t>2026-04-03T04:27:18.994823</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125184</t>
+          <t>2026-04-03T04:27:18.994825</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125187</t>
+          <t>2026-04-03T04:27:18.994828</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125189</t>
+          <t>2026-04-03T04:27:18.994831</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125192</t>
+          <t>2026-04-03T04:27:18.994834</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125195</t>
+          <t>2026-04-03T04:27:18.994837</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125200</t>
+          <t>2026-04-03T04:27:18.994841</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125202</t>
+          <t>2026-04-03T04:27:18.994844</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125205</t>
+          <t>2026-04-03T04:27:18.994847</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125208</t>
+          <t>2026-04-03T04:27:18.994850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125211</t>
+          <t>2026-04-03T04:27:18.994853</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125214</t>
+          <t>2026-04-03T04:27:18.994856</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125217</t>
+          <t>2026-04-03T04:27:18.994859</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125220</t>
+          <t>2026-04-03T04:27:18.994861</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125222</t>
+          <t>2026-04-03T04:27:18.994867</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125225</t>
+          <t>2026-04-03T04:27:18.994871</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125230</t>
+          <t>2026-04-03T04:27:18.994878</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125233</t>
+          <t>2026-04-03T04:27:18.994881</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125236</t>
+          <t>2026-04-03T04:27:18.994884</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125240</t>
+          <t>2026-04-03T04:27:18.994887</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125243</t>
+          <t>2026-04-03T04:27:18.994890</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125246</t>
+          <t>2026-04-03T04:27:18.994893</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125249</t>
+          <t>2026-04-03T04:27:18.994895</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125252</t>
+          <t>2026-04-03T04:27:18.994898</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125254</t>
+          <t>2026-04-03T04:27:18.994901</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125257</t>
+          <t>2026-04-03T04:27:18.994904</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125262</t>
+          <t>2026-04-03T04:27:18.994908</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125265</t>
+          <t>2026-04-03T04:27:18.994911</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125267</t>
+          <t>2026-04-03T04:27:18.994914</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125270</t>
+          <t>2026-04-03T04:27:18.994917</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125273</t>
+          <t>2026-04-03T04:27:18.994920</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125276</t>
+          <t>2026-04-03T04:27:18.994923</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125280</t>
+          <t>2026-04-03T04:27:18.994925</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125282</t>
+          <t>2026-04-03T04:27:18.994928</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:07.125285</t>
+          <t>2026-04-03T04:27:18.994931</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994739</t>
+          <t>2026-04-04T04:13:37.180291</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994754</t>
+          <t>2026-04-04T04:13:37.180308</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994759</t>
+          <t>2026-04-04T04:13:37.180313</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994763</t>
+          <t>2026-04-04T04:13:37.180316</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994766</t>
+          <t>2026-04-04T04:13:37.180320</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994769</t>
+          <t>2026-04-04T04:13:37.180323</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994772</t>
+          <t>2026-04-04T04:13:37.180326</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994795</t>
+          <t>2026-04-04T04:13:37.180330</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994798</t>
+          <t>2026-04-04T04:13:37.180333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994802</t>
+          <t>2026-04-04T04:13:37.180336</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994805</t>
+          <t>2026-04-04T04:13:37.180339</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994811</t>
+          <t>2026-04-04T04:13:37.180345</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994814</t>
+          <t>2026-04-04T04:13:37.180348</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994817</t>
+          <t>2026-04-04T04:13:37.180351</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994820</t>
+          <t>2026-04-04T04:13:37.180354</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994823</t>
+          <t>2026-04-04T04:13:37.180356</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994825</t>
+          <t>2026-04-04T04:13:37.180359</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994828</t>
+          <t>2026-04-04T04:13:37.180362</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994831</t>
+          <t>2026-04-04T04:13:37.180365</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994834</t>
+          <t>2026-04-04T04:13:37.180368</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994837</t>
+          <t>2026-04-04T04:13:37.180371</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994841</t>
+          <t>2026-04-04T04:13:37.180376</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994844</t>
+          <t>2026-04-04T04:13:37.180379</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994847</t>
+          <t>2026-04-04T04:13:37.180382</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994850</t>
+          <t>2026-04-04T04:13:37.180385</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994853</t>
+          <t>2026-04-04T04:13:37.180387</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994856</t>
+          <t>2026-04-04T04:13:37.180390</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994859</t>
+          <t>2026-04-04T04:13:37.180393</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994861</t>
+          <t>2026-04-04T04:13:37.180396</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994867</t>
+          <t>2026-04-04T04:13:37.180399</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994871</t>
+          <t>2026-04-04T04:13:37.180402</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994878</t>
+          <t>2026-04-04T04:13:37.180406</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994881</t>
+          <t>2026-04-04T04:13:37.180409</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994884</t>
+          <t>2026-04-04T04:13:37.180412</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994887</t>
+          <t>2026-04-04T04:13:37.180415</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994890</t>
+          <t>2026-04-04T04:13:37.180420</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994893</t>
+          <t>2026-04-04T04:13:37.180423</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994895</t>
+          <t>2026-04-04T04:13:37.180426</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994898</t>
+          <t>2026-04-04T04:13:37.180429</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994901</t>
+          <t>2026-04-04T04:13:37.180431</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994904</t>
+          <t>2026-04-04T04:13:37.180434</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994908</t>
+          <t>2026-04-04T04:13:37.180439</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994911</t>
+          <t>2026-04-04T04:13:37.180442</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994914</t>
+          <t>2026-04-04T04:13:37.180445</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994917</t>
+          <t>2026-04-04T04:13:37.180448</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994920</t>
+          <t>2026-04-04T04:13:37.180450</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994923</t>
+          <t>2026-04-04T04:13:37.180453</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994925</t>
+          <t>2026-04-04T04:13:37.180456</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994928</t>
+          <t>2026-04-04T04:13:37.180459</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:18.994931</t>
+          <t>2026-04-04T04:13:37.180462</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180291</t>
+          <t>2026-04-05T04:34:34.001128</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180308</t>
+          <t>2026-04-05T04:34:34.001145</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180313</t>
+          <t>2026-04-05T04:34:34.001149</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180316</t>
+          <t>2026-04-05T04:34:34.001153</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180320</t>
+          <t>2026-04-05T04:34:34.001156</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180323</t>
+          <t>2026-04-05T04:34:34.001160</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180326</t>
+          <t>2026-04-05T04:34:34.001163</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180330</t>
+          <t>2026-04-05T04:34:34.001166</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180333</t>
+          <t>2026-04-05T04:34:34.001170</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180336</t>
+          <t>2026-04-05T04:34:34.001173</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180339</t>
+          <t>2026-04-05T04:34:34.001176</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180345</t>
+          <t>2026-04-05T04:34:34.001182</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180348</t>
+          <t>2026-04-05T04:34:34.001185</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180351</t>
+          <t>2026-04-05T04:34:34.001188</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180354</t>
+          <t>2026-04-05T04:34:34.001190</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180356</t>
+          <t>2026-04-05T04:34:34.001193</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180359</t>
+          <t>2026-04-05T04:34:34.001196</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180362</t>
+          <t>2026-04-05T04:34:34.001200</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180365</t>
+          <t>2026-04-05T04:34:34.001202</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180368</t>
+          <t>2026-04-05T04:34:34.001205</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180371</t>
+          <t>2026-04-05T04:34:34.001208</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180376</t>
+          <t>2026-04-05T04:34:34.001213</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180379</t>
+          <t>2026-04-05T04:34:34.001215</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180382</t>
+          <t>2026-04-05T04:34:34.001218</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180385</t>
+          <t>2026-04-05T04:34:34.001221</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180387</t>
+          <t>2026-04-05T04:34:34.001224</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180390</t>
+          <t>2026-04-05T04:34:34.001227</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180393</t>
+          <t>2026-04-05T04:34:34.001230</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180396</t>
+          <t>2026-04-05T04:34:34.001232</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180399</t>
+          <t>2026-04-05T04:34:34.001235</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180402</t>
+          <t>2026-04-05T04:34:34.001238</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180406</t>
+          <t>2026-04-05T04:34:34.001242</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180409</t>
+          <t>2026-04-05T04:34:34.001247</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180412</t>
+          <t>2026-04-05T04:34:34.001250</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180415</t>
+          <t>2026-04-05T04:34:34.001253</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180420</t>
+          <t>2026-04-05T04:34:34.001255</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180423</t>
+          <t>2026-04-05T04:34:34.001258</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180426</t>
+          <t>2026-04-05T04:34:34.001261</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180429</t>
+          <t>2026-04-05T04:34:34.001264</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180431</t>
+          <t>2026-04-05T04:34:34.001267</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180434</t>
+          <t>2026-04-05T04:34:34.001269</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180439</t>
+          <t>2026-04-05T04:34:34.001274</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180442</t>
+          <t>2026-04-05T04:34:34.001277</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180445</t>
+          <t>2026-04-05T04:34:34.001280</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180448</t>
+          <t>2026-04-05T04:34:34.001282</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180450</t>
+          <t>2026-04-05T04:34:34.001285</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180453</t>
+          <t>2026-04-05T04:34:34.001288</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180456</t>
+          <t>2026-04-05T04:34:34.001291</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180459</t>
+          <t>2026-04-05T04:34:34.001293</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:37.180462</t>
+          <t>2026-04-05T04:34:34.001296</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001128</t>
+          <t>2026-04-06T04:41:44.944321</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001145</t>
+          <t>2026-04-06T04:41:44.944332</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001149</t>
+          <t>2026-04-06T04:41:44.944336</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001153</t>
+          <t>2026-04-06T04:41:44.944340</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001156</t>
+          <t>2026-04-06T04:41:44.944343</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001160</t>
+          <t>2026-04-06T04:41:44.944346</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001163</t>
+          <t>2026-04-06T04:41:44.944349</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001166</t>
+          <t>2026-04-06T04:41:44.944352</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001170</t>
+          <t>2026-04-06T04:41:44.944355</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001173</t>
+          <t>2026-04-06T04:41:44.944359</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001176</t>
+          <t>2026-04-06T04:41:44.944362</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001182</t>
+          <t>2026-04-06T04:41:44.944367</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001185</t>
+          <t>2026-04-06T04:41:44.944370</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001188</t>
+          <t>2026-04-06T04:41:44.944373</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001190</t>
+          <t>2026-04-06T04:41:44.944376</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001193</t>
+          <t>2026-04-06T04:41:44.944379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001196</t>
+          <t>2026-04-06T04:41:44.944382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001200</t>
+          <t>2026-04-06T04:41:44.944384</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001202</t>
+          <t>2026-04-06T04:41:44.944387</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001205</t>
+          <t>2026-04-06T04:41:44.944390</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001208</t>
+          <t>2026-04-06T04:41:44.944393</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001213</t>
+          <t>2026-04-06T04:41:44.944398</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001215</t>
+          <t>2026-04-06T04:41:44.944400</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001218</t>
+          <t>2026-04-06T04:41:44.944403</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001221</t>
+          <t>2026-04-06T04:41:44.944406</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001224</t>
+          <t>2026-04-06T04:41:44.944410</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001227</t>
+          <t>2026-04-06T04:41:44.944413</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001230</t>
+          <t>2026-04-06T04:41:44.944416</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001232</t>
+          <t>2026-04-06T04:41:44.944419</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001235</t>
+          <t>2026-04-06T04:41:44.944422</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001238</t>
+          <t>2026-04-06T04:41:44.944424</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001242</t>
+          <t>2026-04-06T04:41:44.944427</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001247</t>
+          <t>2026-04-06T04:41:44.944430</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001250</t>
+          <t>2026-04-06T04:41:44.944433</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001253</t>
+          <t>2026-04-06T04:41:44.944436</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001255</t>
+          <t>2026-04-06T04:41:44.944438</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001258</t>
+          <t>2026-04-06T04:41:44.944441</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001261</t>
+          <t>2026-04-06T04:41:44.944444</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001264</t>
+          <t>2026-04-06T04:41:44.944447</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001267</t>
+          <t>2026-04-06T04:41:44.944450</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001269</t>
+          <t>2026-04-06T04:41:44.944452</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001274</t>
+          <t>2026-04-06T04:41:44.944457</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001277</t>
+          <t>2026-04-06T04:41:44.944460</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001280</t>
+          <t>2026-04-06T04:41:44.944462</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001282</t>
+          <t>2026-04-06T04:41:44.944465</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001285</t>
+          <t>2026-04-06T04:41:44.944468</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001288</t>
+          <t>2026-04-06T04:41:44.944471</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001291</t>
+          <t>2026-04-06T04:41:44.944473</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001293</t>
+          <t>2026-04-06T04:41:44.944476</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:34.001296</t>
+          <t>2026-04-06T04:41:44.944479</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944321</t>
+          <t>2026-04-07T04:30:28.066229</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944332</t>
+          <t>2026-04-07T04:30:28.066240</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944336</t>
+          <t>2026-04-07T04:30:28.066245</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944340</t>
+          <t>2026-04-07T04:30:28.066248</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944343</t>
+          <t>2026-04-07T04:30:28.066251</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944346</t>
+          <t>2026-04-07T04:30:28.066255</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944349</t>
+          <t>2026-04-07T04:30:28.066258</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944352</t>
+          <t>2026-04-07T04:30:28.066262</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944355</t>
+          <t>2026-04-07T04:30:28.066265</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944359</t>
+          <t>2026-04-07T04:30:28.066268</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944362</t>
+          <t>2026-04-07T04:30:28.066271</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944367</t>
+          <t>2026-04-07T04:30:28.066277</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944370</t>
+          <t>2026-04-07T04:30:28.066280</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944373</t>
+          <t>2026-04-07T04:30:28.066283</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944376</t>
+          <t>2026-04-07T04:30:28.066286</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944379</t>
+          <t>2026-04-07T04:30:28.066288</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944382</t>
+          <t>2026-04-07T04:30:28.066291</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944384</t>
+          <t>2026-04-07T04:30:28.066294</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944387</t>
+          <t>2026-04-07T04:30:28.066297</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944390</t>
+          <t>2026-04-07T04:30:28.066300</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944393</t>
+          <t>2026-04-07T04:30:28.066302</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944398</t>
+          <t>2026-04-07T04:30:28.066307</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944400</t>
+          <t>2026-04-07T04:30:28.066310</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944403</t>
+          <t>2026-04-07T04:30:28.066313</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944406</t>
+          <t>2026-04-07T04:30:28.066318</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944410</t>
+          <t>2026-04-07T04:30:28.066321</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944413</t>
+          <t>2026-04-07T04:30:28.066324</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944416</t>
+          <t>2026-04-07T04:30:28.066326</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944419</t>
+          <t>2026-04-07T04:30:28.066329</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944422</t>
+          <t>2026-04-07T04:30:28.066332</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944424</t>
+          <t>2026-04-07T04:30:28.066335</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944427</t>
+          <t>2026-04-07T04:30:28.066339</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944430</t>
+          <t>2026-04-07T04:30:28.066342</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944433</t>
+          <t>2026-04-07T04:30:28.066345</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944436</t>
+          <t>2026-04-07T04:30:28.066348</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944438</t>
+          <t>2026-04-07T04:30:28.066350</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944441</t>
+          <t>2026-04-07T04:30:28.066353</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944444</t>
+          <t>2026-04-07T04:30:28.066356</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944447</t>
+          <t>2026-04-07T04:30:28.066359</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944450</t>
+          <t>2026-04-07T04:30:28.066362</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944452</t>
+          <t>2026-04-07T04:30:28.066364</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944457</t>
+          <t>2026-04-07T04:30:28.066369</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944460</t>
+          <t>2026-04-07T04:30:28.066372</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944462</t>
+          <t>2026-04-07T04:30:28.066375</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1358</v>
+        <v>1310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944465</t>
+          <t>2026-04-07T04:30:28.066378</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944468</t>
+          <t>2026-04-07T04:30:28.066380</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944471</t>
+          <t>2026-04-07T04:30:28.066383</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944473</t>
+          <t>2026-04-07T04:30:28.066386</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944476</t>
+          <t>2026-04-07T04:30:28.066389</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:44.944479</t>
+          <t>2026-04-07T04:30:28.066391</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066229</t>
+          <t>2026-04-08T04:34:14.127277</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066240</t>
+          <t>2026-04-08T04:34:14.127292</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066245</t>
+          <t>2026-04-08T04:34:14.127296</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066248</t>
+          <t>2026-04-08T04:34:14.127300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066251</t>
+          <t>2026-04-08T04:34:14.127303</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066255</t>
+          <t>2026-04-08T04:34:14.127307</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066258</t>
+          <t>2026-04-08T04:34:14.127310</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066262</t>
+          <t>2026-04-08T04:34:14.127313</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066265</t>
+          <t>2026-04-08T04:34:14.127317</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066268</t>
+          <t>2026-04-08T04:34:14.127320</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066271</t>
+          <t>2026-04-08T04:34:14.127323</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066277</t>
+          <t>2026-04-08T04:34:14.127329</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066280</t>
+          <t>2026-04-08T04:34:14.127332</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066283</t>
+          <t>2026-04-08T04:34:14.127335</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066286</t>
+          <t>2026-04-08T04:34:14.127338</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066288</t>
+          <t>2026-04-08T04:34:14.127341</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066291</t>
+          <t>2026-04-08T04:34:14.127343</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066294</t>
+          <t>2026-04-08T04:34:14.127346</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1223</v>
+        <v>1268</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066297</t>
+          <t>2026-04-08T04:34:14.127349</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1228</v>
+        <v>1264</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066300</t>
+          <t>2026-04-08T04:34:14.127352</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1221</v>
+        <v>1266</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066302</t>
+          <t>2026-04-08T04:34:14.127355</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066307</t>
+          <t>2026-04-08T04:34:14.127360</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066310</t>
+          <t>2026-04-08T04:34:14.127362</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066313</t>
+          <t>2026-04-08T04:34:14.127365</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066318</t>
+          <t>2026-04-08T04:34:14.127368</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066321</t>
+          <t>2026-04-08T04:34:14.127371</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066324</t>
+          <t>2026-04-08T04:34:14.127375</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1233</v>
+        <v>1196</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066326</t>
+          <t>2026-04-08T04:34:14.127378</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1237</v>
+        <v>1198</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066329</t>
+          <t>2026-04-08T04:34:14.127381</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066332</t>
+          <t>2026-04-08T04:34:14.127384</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066335</t>
+          <t>2026-04-08T04:34:14.127387</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066339</t>
+          <t>2026-04-08T04:34:14.127391</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066342</t>
+          <t>2026-04-08T04:34:14.127394</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1185</v>
+        <v>1239</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066345</t>
+          <t>2026-04-08T04:34:14.127397</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1180</v>
+        <v>1237</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066348</t>
+          <t>2026-04-08T04:34:14.127400</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066350</t>
+          <t>2026-04-08T04:34:14.127403</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066353</t>
+          <t>2026-04-08T04:34:14.127405</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066356</t>
+          <t>2026-04-08T04:34:14.127408</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1206</v>
+        <v>1185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066359</t>
+          <t>2026-04-08T04:34:14.127411</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066362</t>
+          <t>2026-04-08T04:34:14.127414</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066364</t>
+          <t>2026-04-08T04:34:14.127416</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066369</t>
+          <t>2026-04-08T04:34:14.127421</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066372</t>
+          <t>2026-04-08T04:34:14.127424</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066375</t>
+          <t>2026-04-08T04:34:14.127427</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066378</t>
+          <t>2026-04-08T04:34:14.127430</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1359</v>
+        <v>1318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066380</t>
+          <t>2026-04-08T04:34:14.127433</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066383</t>
+          <t>2026-04-08T04:34:14.127436</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1358</v>
+        <v>1316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066386</t>
+          <t>2026-04-08T04:34:14.127439</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066389</t>
+          <t>2026-04-08T04:34:14.127442</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:28.066391</t>
+          <t>2026-04-08T04:34:14.127445</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1293</v>
+        <v>1272</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127277</t>
+          <t>2026-04-09T04:31:09.255285</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127292</t>
+          <t>2026-04-09T04:31:09.255304</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127296</t>
+          <t>2026-04-09T04:31:09.255309</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127300</t>
+          <t>2026-04-09T04:31:09.255312</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127303</t>
+          <t>2026-04-09T04:31:09.255315</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1259</v>
+        <v>1295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127307</t>
+          <t>2026-04-09T04:31:09.255318</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127310</t>
+          <t>2026-04-09T04:31:09.255321</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127313</t>
+          <t>2026-04-09T04:31:09.255325</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127317</t>
+          <t>2026-04-09T04:31:09.255328</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127320</t>
+          <t>2026-04-09T04:31:09.255331</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127323</t>
+          <t>2026-04-09T04:31:09.255334</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127329</t>
+          <t>2026-04-09T04:31:09.255339</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127332</t>
+          <t>2026-04-09T04:31:09.255342</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127335</t>
+          <t>2026-04-09T04:31:09.255345</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127338</t>
+          <t>2026-04-09T04:31:09.255348</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127341</t>
+          <t>2026-04-09T04:31:09.255351</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127343</t>
+          <t>2026-04-09T04:31:09.255354</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127346</t>
+          <t>2026-04-09T04:31:09.255356</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127349</t>
+          <t>2026-04-09T04:31:09.255359</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127352</t>
+          <t>2026-04-09T04:31:09.255362</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127355</t>
+          <t>2026-04-09T04:31:09.255365</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1221</v>
+        <v>1266</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127360</t>
+          <t>2026-04-09T04:31:09.255370</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1223</v>
+        <v>1264</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127362</t>
+          <t>2026-04-09T04:31:09.255373</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127365</t>
+          <t>2026-04-09T04:31:09.255376</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127368</t>
+          <t>2026-04-09T04:31:09.255378</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127371</t>
+          <t>2026-04-09T04:31:09.255381</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127375</t>
+          <t>2026-04-09T04:31:09.255384</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127378</t>
+          <t>2026-04-09T04:31:09.255389</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127381</t>
+          <t>2026-04-09T04:31:09.255392</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127384</t>
+          <t>2026-04-09T04:31:09.255395</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127387</t>
+          <t>2026-04-09T04:31:09.255398</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127391</t>
+          <t>2026-04-09T04:31:09.255403</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127394</t>
+          <t>2026-04-09T04:31:09.255405</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127397</t>
+          <t>2026-04-09T04:31:09.255408</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127400</t>
+          <t>2026-04-09T04:31:09.255411</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127403</t>
+          <t>2026-04-09T04:31:09.255414</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127405</t>
+          <t>2026-04-09T04:31:09.255417</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127408</t>
+          <t>2026-04-09T04:31:09.255419</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1185</v>
+        <v>1237</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127411</t>
+          <t>2026-04-09T04:31:09.255422</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127414</t>
+          <t>2026-04-09T04:31:09.255425</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127416</t>
+          <t>2026-04-09T04:31:09.255428</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127421</t>
+          <t>2026-04-09T04:31:09.255433</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1269</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127424</t>
+          <t>2026-04-09T04:31:09.255436</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1267</v>
+        <v>1206</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127427</t>
+          <t>2026-04-09T04:31:09.255439</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127430</t>
+          <t>2026-04-09T04:31:09.255442</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127433</t>
+          <t>2026-04-09T04:31:09.255444</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127436</t>
+          <t>2026-04-09T04:31:09.255447</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127439</t>
+          <t>2026-04-09T04:31:09.255450</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1359</v>
+        <v>1318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127442</t>
+          <t>2026-04-09T04:31:09.255453</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:14.127445</t>
+          <t>2026-04-09T04:31:09.255455</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255285</t>
+          <t>2026-04-10T04:43:48.425165</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255304</t>
+          <t>2026-04-10T04:43:48.425183</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255309</t>
+          <t>2026-04-10T04:43:48.425187</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255312</t>
+          <t>2026-04-10T04:43:48.425191</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255315</t>
+          <t>2026-04-10T04:43:48.425194</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255318</t>
+          <t>2026-04-10T04:43:48.425197</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255321</t>
+          <t>2026-04-10T04:43:48.425200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255325</t>
+          <t>2026-04-10T04:43:48.425208</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255328</t>
+          <t>2026-04-10T04:43:48.425211</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255331</t>
+          <t>2026-04-10T04:43:48.425215</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255334</t>
+          <t>2026-04-10T04:43:48.425217</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255339</t>
+          <t>2026-04-10T04:43:48.425223</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255342</t>
+          <t>2026-04-10T04:43:48.425226</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255345</t>
+          <t>2026-04-10T04:43:48.425229</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255348</t>
+          <t>2026-04-10T04:43:48.425232</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255351</t>
+          <t>2026-04-10T04:43:48.425234</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255354</t>
+          <t>2026-04-10T04:43:48.425237</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255356</t>
+          <t>2026-04-10T04:43:48.425240</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255359</t>
+          <t>2026-04-10T04:43:48.425243</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255362</t>
+          <t>2026-04-10T04:43:48.425248</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255365</t>
+          <t>2026-04-10T04:43:48.425251</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255370</t>
+          <t>2026-04-10T04:43:48.425256</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255373</t>
+          <t>2026-04-10T04:43:48.425258</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255376</t>
+          <t>2026-04-10T04:43:48.425261</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255378</t>
+          <t>2026-04-10T04:43:48.425264</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255381</t>
+          <t>2026-04-10T04:43:48.425267</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255384</t>
+          <t>2026-04-10T04:43:48.425270</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255389</t>
+          <t>2026-04-10T04:43:48.425272</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255392</t>
+          <t>2026-04-10T04:43:48.425275</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255395</t>
+          <t>2026-04-10T04:43:48.425278</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255398</t>
+          <t>2026-04-10T04:43:48.425281</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255403</t>
+          <t>2026-04-10T04:43:48.425286</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255405</t>
+          <t>2026-04-10T04:43:48.425288</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255408</t>
+          <t>2026-04-10T04:43:48.425291</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255411</t>
+          <t>2026-04-10T04:43:48.425294</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255414</t>
+          <t>2026-04-10T04:43:48.425297</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255417</t>
+          <t>2026-04-10T04:43:48.425300</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255419</t>
+          <t>2026-04-10T04:43:48.425302</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255422</t>
+          <t>2026-04-10T04:43:48.425305</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255425</t>
+          <t>2026-04-10T04:43:48.425308</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255428</t>
+          <t>2026-04-10T04:43:48.425311</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255433</t>
+          <t>2026-04-10T04:43:48.425316</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255436</t>
+          <t>2026-04-10T04:43:48.425318</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255439</t>
+          <t>2026-04-10T04:43:48.425321</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255442</t>
+          <t>2026-04-10T04:43:48.425324</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1269</v>
+        <v>1206</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255444</t>
+          <t>2026-04-10T04:43:48.425327</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255447</t>
+          <t>2026-04-10T04:43:48.425330</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255450</t>
+          <t>2026-04-10T04:43:48.425333</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255453</t>
+          <t>2026-04-10T04:43:48.425335</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1316</v>
+        <v>1267</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:09.255455</t>
+          <t>2026-04-10T04:43:48.425338</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425165</t>
+          <t>2026-04-11T04:19:26.336892</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425183</t>
+          <t>2026-04-11T04:19:26.336908</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425187</t>
+          <t>2026-04-11T04:19:26.336913</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425191</t>
+          <t>2026-04-11T04:19:26.336916</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425194</t>
+          <t>2026-04-11T04:19:26.336919</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425197</t>
+          <t>2026-04-11T04:19:26.336923</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425200</t>
+          <t>2026-04-11T04:19:26.336926</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425208</t>
+          <t>2026-04-11T04:19:26.336929</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425211</t>
+          <t>2026-04-11T04:19:26.336932</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425215</t>
+          <t>2026-04-11T04:19:26.336936</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425217</t>
+          <t>2026-04-11T04:19:26.336938</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425223</t>
+          <t>2026-04-11T04:19:26.336944</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425226</t>
+          <t>2026-04-11T04:19:26.336947</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425229</t>
+          <t>2026-04-11T04:19:26.336950</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425232</t>
+          <t>2026-04-11T04:19:26.336952</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425234</t>
+          <t>2026-04-11T04:19:26.336955</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425237</t>
+          <t>2026-04-11T04:19:26.336958</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425240</t>
+          <t>2026-04-11T04:19:26.336961</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425243</t>
+          <t>2026-04-11T04:19:26.336964</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425248</t>
+          <t>2026-04-11T04:19:26.336969</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425251</t>
+          <t>2026-04-11T04:19:26.336972</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425256</t>
+          <t>2026-04-11T04:19:26.336977</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425258</t>
+          <t>2026-04-11T04:19:26.336980</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425261</t>
+          <t>2026-04-11T04:19:26.336983</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425264</t>
+          <t>2026-04-11T04:19:26.336985</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425267</t>
+          <t>2026-04-11T04:19:26.336988</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425270</t>
+          <t>2026-04-11T04:19:26.336991</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425272</t>
+          <t>2026-04-11T04:19:26.336994</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425275</t>
+          <t>2026-04-11T04:19:26.336997</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425278</t>
+          <t>2026-04-11T04:19:26.336999</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425281</t>
+          <t>2026-04-11T04:19:26.337002</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425286</t>
+          <t>2026-04-11T04:19:26.337007</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425288</t>
+          <t>2026-04-11T04:19:26.337010</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425291</t>
+          <t>2026-04-11T04:19:26.337013</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425294</t>
+          <t>2026-04-11T04:19:26.337016</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425297</t>
+          <t>2026-04-11T04:19:26.337018</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425300</t>
+          <t>2026-04-11T04:19:26.337021</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425302</t>
+          <t>2026-04-11T04:19:26.337024</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425305</t>
+          <t>2026-04-11T04:19:26.337027</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425308</t>
+          <t>2026-04-11T04:19:26.337030</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425311</t>
+          <t>2026-04-11T04:19:26.337032</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425316</t>
+          <t>2026-04-11T04:19:26.337038</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425318</t>
+          <t>2026-04-11T04:19:26.337041</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425321</t>
+          <t>2026-04-11T04:19:26.337044</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425324</t>
+          <t>2026-04-11T04:19:26.337047</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425327</t>
+          <t>2026-04-11T04:19:26.337050</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425330</t>
+          <t>2026-04-11T04:19:26.337053</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425333</t>
+          <t>2026-04-11T04:19:26.337055</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425335</t>
+          <t>2026-04-11T04:19:26.337058</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:48.425338</t>
+          <t>2026-04-11T04:19:26.337061</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336892</t>
+          <t>2026-04-12T04:43:50.468668</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336908</t>
+          <t>2026-04-12T04:43:50.468685</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336913</t>
+          <t>2026-04-12T04:43:50.468690</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336916</t>
+          <t>2026-04-12T04:43:50.468693</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336919</t>
+          <t>2026-04-12T04:43:50.468696</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336923</t>
+          <t>2026-04-12T04:43:50.468700</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336926</t>
+          <t>2026-04-12T04:43:50.468703</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336929</t>
+          <t>2026-04-12T04:43:50.468707</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336932</t>
+          <t>2026-04-12T04:43:50.468710</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336936</t>
+          <t>2026-04-12T04:43:50.468713</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336938</t>
+          <t>2026-04-12T04:43:50.468716</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336944</t>
+          <t>2026-04-12T04:43:50.468722</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336947</t>
+          <t>2026-04-12T04:43:50.468725</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336950</t>
+          <t>2026-04-12T04:43:50.468727</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336952</t>
+          <t>2026-04-12T04:43:50.468730</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336955</t>
+          <t>2026-04-12T04:43:50.468733</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336958</t>
+          <t>2026-04-12T04:43:50.468736</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336961</t>
+          <t>2026-04-12T04:43:50.468739</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336964</t>
+          <t>2026-04-12T04:43:50.468742</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336969</t>
+          <t>2026-04-12T04:43:50.468746</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336972</t>
+          <t>2026-04-12T04:43:50.468749</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336977</t>
+          <t>2026-04-12T04:43:50.468754</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336980</t>
+          <t>2026-04-12T04:43:50.468757</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336983</t>
+          <t>2026-04-12T04:43:50.468760</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336985</t>
+          <t>2026-04-12T04:43:50.468762</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336988</t>
+          <t>2026-04-12T04:43:50.468765</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336991</t>
+          <t>2026-04-12T04:43:50.468768</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336994</t>
+          <t>2026-04-12T04:43:50.468771</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336997</t>
+          <t>2026-04-12T04:43:50.468774</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.336999</t>
+          <t>2026-04-12T04:43:50.468777</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337002</t>
+          <t>2026-04-12T04:43:50.468780</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337007</t>
+          <t>2026-04-12T04:43:50.468784</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337010</t>
+          <t>2026-04-12T04:43:50.468787</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337013</t>
+          <t>2026-04-12T04:43:50.468791</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337016</t>
+          <t>2026-04-12T04:43:50.468794</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337018</t>
+          <t>2026-04-12T04:43:50.468797</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337021</t>
+          <t>2026-04-12T04:43:50.468800</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337024</t>
+          <t>2026-04-12T04:43:50.468803</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337027</t>
+          <t>2026-04-12T04:43:50.468805</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337030</t>
+          <t>2026-04-12T04:43:50.468808</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337032</t>
+          <t>2026-04-12T04:43:50.468811</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337038</t>
+          <t>2026-04-12T04:43:50.468816</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337041</t>
+          <t>2026-04-12T04:43:50.468820</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337044</t>
+          <t>2026-04-12T04:43:50.468823</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337047</t>
+          <t>2026-04-12T04:43:50.468827</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337050</t>
+          <t>2026-04-12T04:43:50.468830</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337053</t>
+          <t>2026-04-12T04:43:50.468833</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337055</t>
+          <t>2026-04-12T04:43:50.468836</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337058</t>
+          <t>2026-04-12T04:43:50.468838</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:26.337061</t>
+          <t>2026-04-12T04:43:50.468841</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468668</t>
+          <t>2026-04-13T04:55:08.229916</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468685</t>
+          <t>2026-04-13T04:55:08.229931</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468690</t>
+          <t>2026-04-13T04:55:08.229936</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468693</t>
+          <t>2026-04-13T04:55:08.229939</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468696</t>
+          <t>2026-04-13T04:55:08.229942</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468700</t>
+          <t>2026-04-13T04:55:08.229946</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468703</t>
+          <t>2026-04-13T04:55:08.229949</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468707</t>
+          <t>2026-04-13T04:55:08.229952</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468710</t>
+          <t>2026-04-13T04:55:08.229955</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468713</t>
+          <t>2026-04-13T04:55:08.229959</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468716</t>
+          <t>2026-04-13T04:55:08.229962</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468722</t>
+          <t>2026-04-13T04:55:08.229968</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468725</t>
+          <t>2026-04-13T04:55:08.229971</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468727</t>
+          <t>2026-04-13T04:55:08.229974</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468730</t>
+          <t>2026-04-13T04:55:08.229976</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468733</t>
+          <t>2026-04-13T04:55:08.229979</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468736</t>
+          <t>2026-04-13T04:55:08.229982</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468739</t>
+          <t>2026-04-13T04:55:08.229985</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468742</t>
+          <t>2026-04-13T04:55:08.229988</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468746</t>
+          <t>2026-04-13T04:55:08.229992</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468749</t>
+          <t>2026-04-13T04:55:08.229995</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468754</t>
+          <t>2026-04-13T04:55:08.230000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468757</t>
+          <t>2026-04-13T04:55:08.230002</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468760</t>
+          <t>2026-04-13T04:55:08.230005</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468762</t>
+          <t>2026-04-13T04:55:08.230008</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468765</t>
+          <t>2026-04-13T04:55:08.230011</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468768</t>
+          <t>2026-04-13T04:55:08.230014</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468771</t>
+          <t>2026-04-13T04:55:08.230017</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468774</t>
+          <t>2026-04-13T04:55:08.230019</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468777</t>
+          <t>2026-04-13T04:55:08.230022</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468780</t>
+          <t>2026-04-13T04:55:08.230025</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468784</t>
+          <t>2026-04-13T04:55:08.230029</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468787</t>
+          <t>2026-04-13T04:55:08.230032</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468791</t>
+          <t>2026-04-13T04:55:08.230035</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468794</t>
+          <t>2026-04-13T04:55:08.230038</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468797</t>
+          <t>2026-04-13T04:55:08.230041</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468800</t>
+          <t>2026-04-13T04:55:08.230044</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468803</t>
+          <t>2026-04-13T04:55:08.230047</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468805</t>
+          <t>2026-04-13T04:55:08.230049</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468808</t>
+          <t>2026-04-13T04:55:08.230052</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468811</t>
+          <t>2026-04-13T04:55:08.230055</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468816</t>
+          <t>2026-04-13T04:55:08.230060</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468820</t>
+          <t>2026-04-13T04:55:08.230062</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468823</t>
+          <t>2026-04-13T04:55:08.230065</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468827</t>
+          <t>2026-04-13T04:55:08.230068</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468830</t>
+          <t>2026-04-13T04:55:08.230071</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1206.00</t>
+          <t>1180.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468833</t>
+          <t>2026-04-13T04:55:08.230074</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468836</t>
+          <t>2026-04-13T04:55:08.230076</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468838</t>
+          <t>2026-04-13T04:55:08.230079</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1268</v>
+        <v>1200</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:50.468841</t>
+          <t>2026-04-13T04:55:08.230082</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229916</t>
+          <t>2026-04-14T04:42:39.406429</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229931</t>
+          <t>2026-04-14T04:42:39.406445</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229936</t>
+          <t>2026-04-14T04:42:39.406450</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229939</t>
+          <t>2026-04-14T04:42:39.406453</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229942</t>
+          <t>2026-04-14T04:42:39.406457</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229946</t>
+          <t>2026-04-14T04:42:39.406460</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229949</t>
+          <t>2026-04-14T04:42:39.406463</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229952</t>
+          <t>2026-04-14T04:42:39.406467</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229955</t>
+          <t>2026-04-14T04:42:39.406470</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229959</t>
+          <t>2026-04-14T04:42:39.406474</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229962</t>
+          <t>2026-04-14T04:42:39.406477</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229968</t>
+          <t>2026-04-14T04:42:39.406482</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229971</t>
+          <t>2026-04-14T04:42:39.406485</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229974</t>
+          <t>2026-04-14T04:42:39.406488</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229976</t>
+          <t>2026-04-14T04:42:39.406492</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229979</t>
+          <t>2026-04-14T04:42:39.406505</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229982</t>
+          <t>2026-04-14T04:42:39.406509</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229985</t>
+          <t>2026-04-14T04:42:39.406512</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229988</t>
+          <t>2026-04-14T04:42:39.406515</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229992</t>
+          <t>2026-04-14T04:42:39.406518</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.229995</t>
+          <t>2026-04-14T04:42:39.406521</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230000</t>
+          <t>2026-04-14T04:42:39.406527</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230002</t>
+          <t>2026-04-14T04:42:39.406530</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230005</t>
+          <t>2026-04-14T04:42:39.406534</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230008</t>
+          <t>2026-04-14T04:42:39.406537</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230011</t>
+          <t>2026-04-14T04:42:39.406540</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230014</t>
+          <t>2026-04-14T04:42:39.406543</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230017</t>
+          <t>2026-04-14T04:42:39.406546</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230019</t>
+          <t>2026-04-14T04:42:39.406549</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230022</t>
+          <t>2026-04-14T04:42:39.406552</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230025</t>
+          <t>2026-04-14T04:42:39.406556</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230029</t>
+          <t>2026-04-14T04:42:39.406560</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230032</t>
+          <t>2026-04-14T04:42:39.406564</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230035</t>
+          <t>2026-04-14T04:42:39.406567</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230038</t>
+          <t>2026-04-14T04:42:39.406570</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230041</t>
+          <t>2026-04-14T04:42:39.406573</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230044</t>
+          <t>2026-04-14T04:42:39.406576</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230047</t>
+          <t>2026-04-14T04:42:39.406579</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230049</t>
+          <t>2026-04-14T04:42:39.406582</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230052</t>
+          <t>2026-04-14T04:42:39.406585</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230055</t>
+          <t>2026-04-14T04:42:39.406588</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230060</t>
+          <t>2026-04-14T04:42:39.406593</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230062</t>
+          <t>2026-04-14T04:42:39.406596</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230065</t>
+          <t>2026-04-14T04:42:39.406599</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230068</t>
+          <t>2026-04-14T04:42:39.406603</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230071</t>
+          <t>2026-04-14T04:42:39.406606</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1180.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230074</t>
+          <t>2026-04-14T04:42:39.406609</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1246.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1185</v>
+        <v>1246</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230076</t>
+          <t>2026-04-14T04:42:39.406612</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1204.00</t>
+          <t>1178.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230079</t>
+          <t>2026-04-14T04:42:39.406615</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t>1185.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.230082</t>
+          <t>2026-04-14T04:42:39.406618</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406429</t>
+          <t>2026-04-15T04:42:56.000211</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406445</t>
+          <t>2026-04-15T04:42:56.000227</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406450</t>
+          <t>2026-04-15T04:42:56.000232</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406453</t>
+          <t>2026-04-15T04:42:56.000235</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406457</t>
+          <t>2026-04-15T04:42:56.000239</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406460</t>
+          <t>2026-04-15T04:42:56.000242</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406463</t>
+          <t>2026-04-15T04:42:56.000245</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406467</t>
+          <t>2026-04-15T04:42:56.000249</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406470</t>
+          <t>2026-04-15T04:42:56.000252</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406474</t>
+          <t>2026-04-15T04:42:56.000255</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406477</t>
+          <t>2026-04-15T04:42:56.000258</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406482</t>
+          <t>2026-04-15T04:42:56.000264</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406485</t>
+          <t>2026-04-15T04:42:56.000267</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1292</v>
+        <v>1272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406488</t>
+          <t>2026-04-15T04:42:56.000270</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406492</t>
+          <t>2026-04-15T04:42:56.000273</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1255</v>
+        <v>1295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406505</t>
+          <t>2026-04-15T04:42:56.000276</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406509</t>
+          <t>2026-04-15T04:42:56.000279</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406512</t>
+          <t>2026-04-15T04:42:56.000282</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406515</t>
+          <t>2026-04-15T04:42:56.000284</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406518</t>
+          <t>2026-04-15T04:42:56.000287</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406521</t>
+          <t>2026-04-15T04:42:56.000290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406527</t>
+          <t>2026-04-15T04:42:56.000295</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1264</v>
+        <v>1257</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406530</t>
+          <t>2026-04-15T04:42:56.000298</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406534</t>
+          <t>2026-04-15T04:42:56.000301</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406537</t>
+          <t>2026-04-15T04:42:56.000303</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406540</t>
+          <t>2026-04-15T04:42:56.000306</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406543</t>
+          <t>2026-04-15T04:42:56.000309</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406546</t>
+          <t>2026-04-15T04:42:56.000312</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406549</t>
+          <t>2026-04-15T04:42:56.000315</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406552</t>
+          <t>2026-04-15T04:42:56.000317</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406556</t>
+          <t>2026-04-15T04:42:56.000322</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406560</t>
+          <t>2026-04-15T04:42:56.000327</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406564</t>
+          <t>2026-04-15T04:42:56.000330</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1228</v>
+        <v>1266</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406567</t>
+          <t>2026-04-15T04:42:56.000333</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1223</v>
+        <v>1264</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406570</t>
+          <t>2026-04-15T04:42:56.000335</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1221</v>
+        <v>1268</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406573</t>
+          <t>2026-04-15T04:42:56.000338</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406576</t>
+          <t>2026-04-15T04:42:56.000341</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406579</t>
+          <t>2026-04-15T04:42:56.000344</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406582</t>
+          <t>2026-04-15T04:42:56.000346</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406585</t>
+          <t>2026-04-15T04:42:56.000349</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406588</t>
+          <t>2026-04-15T04:42:56.000352</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406593</t>
+          <t>2026-04-15T04:42:56.000357</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406596</t>
+          <t>2026-04-15T04:42:56.000360</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406599</t>
+          <t>2026-04-15T04:42:56.000363</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406603</t>
+          <t>2026-04-15T04:42:56.000365</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406606</t>
+          <t>2026-04-15T04:42:56.000368</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1233.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406609</t>
+          <t>2026-04-15T04:42:56.000371</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1246.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406612</t>
+          <t>2026-04-15T04:42:56.000374</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1178.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1178</v>
+        <v>1237</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406615</t>
+          <t>2026-04-15T04:42:56.000377</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1185</v>
+        <v>1239</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:39.406618</t>
+          <t>2026-04-15T04:42:56.000379</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000211</t>
+          <t>2026-04-16T04:48:27.493137</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000227</t>
+          <t>2026-04-16T04:48:27.493155</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000232</t>
+          <t>2026-04-16T04:48:27.493160</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1272</v>
+        <v>1300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000235</t>
+          <t>2026-04-16T04:48:27.493164</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000239</t>
+          <t>2026-04-16T04:48:27.493167</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1277</v>
+        <v>1296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000242</t>
+          <t>2026-04-16T04:48:27.493170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000245</t>
+          <t>2026-04-16T04:48:27.493173</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000249</t>
+          <t>2026-04-16T04:48:27.493177</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000252</t>
+          <t>2026-04-16T04:48:27.493180</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000255</t>
+          <t>2026-04-16T04:48:27.493183</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000258</t>
+          <t>2026-04-16T04:48:27.493186</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000264</t>
+          <t>2026-04-16T04:48:27.493191</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000267</t>
+          <t>2026-04-16T04:48:27.493194</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000270</t>
+          <t>2026-04-16T04:48:27.493197</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000273</t>
+          <t>2026-04-16T04:48:27.493200</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000276</t>
+          <t>2026-04-16T04:48:27.493203</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1292</v>
+        <v>1272</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000279</t>
+          <t>2026-04-16T04:48:27.493205</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000282</t>
+          <t>2026-04-16T04:48:27.493208</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1259</v>
+        <v>1295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000284</t>
+          <t>2026-04-16T04:48:27.493211</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000287</t>
+          <t>2026-04-16T04:48:27.493214</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000290</t>
+          <t>2026-04-16T04:48:27.493217</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000295</t>
+          <t>2026-04-16T04:48:27.493222</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000298</t>
+          <t>2026-04-16T04:48:27.493224</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000301</t>
+          <t>2026-04-16T04:48:27.493227</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000303</t>
+          <t>2026-04-16T04:48:27.493230</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000306</t>
+          <t>2026-04-16T04:48:27.493233</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000309</t>
+          <t>2026-04-16T04:48:27.493236</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000312</t>
+          <t>2026-04-16T04:48:27.493239</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000315</t>
+          <t>2026-04-16T04:48:27.493241</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000317</t>
+          <t>2026-04-16T04:48:27.493244</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000322</t>
+          <t>2026-04-16T04:48:27.493247</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000327</t>
+          <t>2026-04-16T04:48:27.493252</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000330</t>
+          <t>2026-04-16T04:48:27.493255</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000333</t>
+          <t>2026-04-16T04:48:27.493258</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000335</t>
+          <t>2026-04-16T04:48:27.493263</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000338</t>
+          <t>2026-04-16T04:48:27.493266</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000341</t>
+          <t>2026-04-16T04:48:27.493269</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1221</v>
+        <v>1268</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000344</t>
+          <t>2026-04-16T04:48:27.493271</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1228</v>
+        <v>1264</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000346</t>
+          <t>2026-04-16T04:48:27.493274</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000349</t>
+          <t>2026-04-16T04:48:27.493277</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000352</t>
+          <t>2026-04-16T04:48:27.493280</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000357</t>
+          <t>2026-04-16T04:48:27.493285</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000360</t>
+          <t>2026-04-16T04:48:27.493288</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1196</v>
+        <v>1223</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000363</t>
+          <t>2026-04-16T04:48:27.493291</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000365</t>
+          <t>2026-04-16T04:48:27.493294</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000368</t>
+          <t>2026-04-16T04:48:27.493296</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1233.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1233</v>
+        <v>1198</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000371</t>
+          <t>2026-04-16T04:48:27.493299</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000374</t>
+          <t>2026-04-16T04:48:27.493302</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1239.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000377</t>
+          <t>2026-04-16T04:48:27.493305</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1237.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.000379</t>
+          <t>2026-04-16T04:48:27.493308</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493137</t>
+          <t>2026-04-17T04:46:14.124090</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493155</t>
+          <t>2026-04-17T04:46:14.124103</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493160</t>
+          <t>2026-04-17T04:46:14.124108</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493164</t>
+          <t>2026-04-17T04:46:14.124111</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493167</t>
+          <t>2026-04-17T04:46:14.124114</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493170</t>
+          <t>2026-04-17T04:46:14.124118</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493173</t>
+          <t>2026-04-17T04:46:14.124121</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493177</t>
+          <t>2026-04-17T04:46:14.124124</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493180</t>
+          <t>2026-04-17T04:46:14.124127</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493183</t>
+          <t>2026-04-17T04:46:14.124130</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493186</t>
+          <t>2026-04-17T04:46:14.124133</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493191</t>
+          <t>2026-04-17T04:46:14.124139</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493194</t>
+          <t>2026-04-17T04:46:14.124142</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493197</t>
+          <t>2026-04-17T04:46:14.124145</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493200</t>
+          <t>2026-04-17T04:46:14.124148</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493203</t>
+          <t>2026-04-17T04:46:14.124151</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493205</t>
+          <t>2026-04-17T04:46:14.124154</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493208</t>
+          <t>2026-04-17T04:46:14.124157</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493211</t>
+          <t>2026-04-17T04:46:14.124160</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493214</t>
+          <t>2026-04-17T04:46:14.124163</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493217</t>
+          <t>2026-04-17T04:46:14.124165</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493222</t>
+          <t>2026-04-17T04:46:14.124170</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493224</t>
+          <t>2026-04-17T04:46:14.124173</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493227</t>
+          <t>2026-04-17T04:46:14.124178</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493230</t>
+          <t>2026-04-17T04:46:14.124180</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493233</t>
+          <t>2026-04-17T04:46:14.124183</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493236</t>
+          <t>2026-04-17T04:46:14.124186</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493239</t>
+          <t>2026-04-17T04:46:14.124189</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493241</t>
+          <t>2026-04-17T04:46:14.124192</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493244</t>
+          <t>2026-04-17T04:46:14.124195</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493247</t>
+          <t>2026-04-17T04:46:14.124198</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493252</t>
+          <t>2026-04-17T04:46:14.124202</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493255</t>
+          <t>2026-04-17T04:46:14.124205</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493258</t>
+          <t>2026-04-17T04:46:14.124208</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493263</t>
+          <t>2026-04-17T04:46:14.124211</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493266</t>
+          <t>2026-04-17T04:46:14.124214</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493269</t>
+          <t>2026-04-17T04:46:14.124217</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493271</t>
+          <t>2026-04-17T04:46:14.124220</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493274</t>
+          <t>2026-04-17T04:46:14.124222</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493277</t>
+          <t>2026-04-17T04:46:14.124225</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493280</t>
+          <t>2026-04-17T04:46:14.124228</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493285</t>
+          <t>2026-04-17T04:46:14.124233</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493288</t>
+          <t>2026-04-17T04:46:14.124236</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493291</t>
+          <t>2026-04-17T04:46:14.124239</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493294</t>
+          <t>2026-04-17T04:46:14.124242</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493296</t>
+          <t>2026-04-17T04:46:14.124244</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493299</t>
+          <t>2026-04-17T04:46:14.124247</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493302</t>
+          <t>2026-04-17T04:46:14.124250</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1239.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493305</t>
+          <t>2026-04-17T04:46:14.124253</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:27.493308</t>
+          <t>2026-04-17T04:46:14.124256</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124090</t>
+          <t>2026-04-18T04:29:40.553718</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124103</t>
+          <t>2026-04-18T04:29:40.553735</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124108</t>
+          <t>2026-04-18T04:29:40.553740</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124111</t>
+          <t>2026-04-18T04:29:40.553744</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124114</t>
+          <t>2026-04-18T04:29:40.553747</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124118</t>
+          <t>2026-04-18T04:29:40.553751</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124121</t>
+          <t>2026-04-18T04:29:40.553754</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124124</t>
+          <t>2026-04-18T04:29:40.553757</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124127</t>
+          <t>2026-04-18T04:29:40.553761</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124130</t>
+          <t>2026-04-18T04:29:40.553764</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124133</t>
+          <t>2026-04-18T04:29:40.553767</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124139</t>
+          <t>2026-04-18T04:29:40.553773</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124142</t>
+          <t>2026-04-18T04:29:40.553776</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124145</t>
+          <t>2026-04-18T04:29:40.553779</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124148</t>
+          <t>2026-04-18T04:29:40.553781</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124151</t>
+          <t>2026-04-18T04:29:40.553784</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124154</t>
+          <t>2026-04-18T04:29:40.553787</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124157</t>
+          <t>2026-04-18T04:29:40.553790</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124160</t>
+          <t>2026-04-18T04:29:40.553793</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124163</t>
+          <t>2026-04-18T04:29:40.553795</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124165</t>
+          <t>2026-04-18T04:29:40.553798</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124170</t>
+          <t>2026-04-18T04:29:40.553803</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124173</t>
+          <t>2026-04-18T04:29:40.553806</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124178</t>
+          <t>2026-04-18T04:29:40.553809</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124180</t>
+          <t>2026-04-18T04:29:40.553812</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124183</t>
+          <t>2026-04-18T04:29:40.553815</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124186</t>
+          <t>2026-04-18T04:29:40.553818</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124189</t>
+          <t>2026-04-18T04:29:40.553823</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124192</t>
+          <t>2026-04-18T04:29:40.553826</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124195</t>
+          <t>2026-04-18T04:29:40.553829</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124198</t>
+          <t>2026-04-18T04:29:40.553831</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124202</t>
+          <t>2026-04-18T04:29:40.553836</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124205</t>
+          <t>2026-04-18T04:29:40.553839</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124208</t>
+          <t>2026-04-18T04:29:40.553842</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124211</t>
+          <t>2026-04-18T04:29:40.553845</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124214</t>
+          <t>2026-04-18T04:29:40.553848</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124217</t>
+          <t>2026-04-18T04:29:40.553850</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124220</t>
+          <t>2026-04-18T04:29:40.553853</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124222</t>
+          <t>2026-04-18T04:29:40.553856</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124225</t>
+          <t>2026-04-18T04:29:40.553859</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124228</t>
+          <t>2026-04-18T04:29:40.553862</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124233</t>
+          <t>2026-04-18T04:29:40.553867</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124236</t>
+          <t>2026-04-18T04:29:40.553870</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124239</t>
+          <t>2026-04-18T04:29:40.553873</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124242</t>
+          <t>2026-04-18T04:29:40.553875</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124244</t>
+          <t>2026-04-18T04:29:40.553878</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124247</t>
+          <t>2026-04-18T04:29:40.553881</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124250</t>
+          <t>2026-04-18T04:29:40.553884</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1196.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124253</t>
+          <t>2026-04-18T04:29:40.553887</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1198.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.124256</t>
+          <t>2026-04-18T04:29:40.553889</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553718</t>
+          <t>2026-04-19T04:47:50.863036</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553735</t>
+          <t>2026-04-19T04:47:50.863051</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553740</t>
+          <t>2026-04-19T04:47:50.863055</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553744</t>
+          <t>2026-04-19T04:47:50.863059</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553747</t>
+          <t>2026-04-19T04:47:50.863062</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553751</t>
+          <t>2026-04-19T04:47:50.863065</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553754</t>
+          <t>2026-04-19T04:47:50.863068</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553757</t>
+          <t>2026-04-19T04:47:50.863072</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553761</t>
+          <t>2026-04-19T04:47:50.863076</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553764</t>
+          <t>2026-04-19T04:47:50.863079</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553767</t>
+          <t>2026-04-19T04:47:50.863082</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553773</t>
+          <t>2026-04-19T04:47:50.863088</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553776</t>
+          <t>2026-04-19T04:47:50.863091</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553779</t>
+          <t>2026-04-19T04:47:50.863094</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553781</t>
+          <t>2026-04-19T04:47:50.863097</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553784</t>
+          <t>2026-04-19T04:47:50.863099</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553787</t>
+          <t>2026-04-19T04:47:50.863102</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553790</t>
+          <t>2026-04-19T04:47:50.863105</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553793</t>
+          <t>2026-04-19T04:47:50.863108</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553795</t>
+          <t>2026-04-19T04:47:50.863111</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553798</t>
+          <t>2026-04-19T04:47:50.863116</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553803</t>
+          <t>2026-04-19T04:47:50.863120</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553806</t>
+          <t>2026-04-19T04:47:50.863123</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553809</t>
+          <t>2026-04-19T04:47:50.863126</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553812</t>
+          <t>2026-04-19T04:47:50.863129</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553815</t>
+          <t>2026-04-19T04:47:50.863131</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553818</t>
+          <t>2026-04-19T04:47:50.863134</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553823</t>
+          <t>2026-04-19T04:47:50.863137</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553826</t>
+          <t>2026-04-19T04:47:50.863140</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553829</t>
+          <t>2026-04-19T04:47:50.863143</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553831</t>
+          <t>2026-04-19T04:47:50.863146</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553836</t>
+          <t>2026-04-19T04:47:50.863150</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553839</t>
+          <t>2026-04-19T04:47:50.863153</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553842</t>
+          <t>2026-04-19T04:47:50.863156</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553845</t>
+          <t>2026-04-19T04:47:50.863159</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553848</t>
+          <t>2026-04-19T04:47:50.863162</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553850</t>
+          <t>2026-04-19T04:47:50.863164</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553853</t>
+          <t>2026-04-19T04:47:50.863167</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553856</t>
+          <t>2026-04-19T04:47:50.863170</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553859</t>
+          <t>2026-04-19T04:47:50.863173</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553862</t>
+          <t>2026-04-19T04:47:50.863176</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553867</t>
+          <t>2026-04-19T04:47:50.863180</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553870</t>
+          <t>2026-04-19T04:47:50.863183</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553873</t>
+          <t>2026-04-19T04:47:50.863186</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553875</t>
+          <t>2026-04-19T04:47:50.863189</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553878</t>
+          <t>2026-04-19T04:47:50.863192</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553881</t>
+          <t>2026-04-19T04:47:50.863195</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553884</t>
+          <t>2026-04-19T04:47:50.863197</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553887</t>
+          <t>2026-04-19T04:47:50.863200</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:40.553889</t>
+          <t>2026-04-19T04:47:50.863203</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863036</t>
+          <t>2026-04-20T04:54:54.180822</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863051</t>
+          <t>2026-04-20T04:54:54.180839</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863055</t>
+          <t>2026-04-20T04:54:54.180844</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863059</t>
+          <t>2026-04-20T04:54:54.180847</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863062</t>
+          <t>2026-04-20T04:54:54.180851</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863065</t>
+          <t>2026-04-20T04:54:54.180857</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863068</t>
+          <t>2026-04-20T04:54:54.180860</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863072</t>
+          <t>2026-04-20T04:54:54.180863</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863076</t>
+          <t>2026-04-20T04:54:54.180867</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863079</t>
+          <t>2026-04-20T04:54:54.180870</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863082</t>
+          <t>2026-04-20T04:54:54.180873</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863088</t>
+          <t>2026-04-20T04:54:54.180878</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863091</t>
+          <t>2026-04-20T04:54:54.180881</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863094</t>
+          <t>2026-04-20T04:54:54.180884</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863097</t>
+          <t>2026-04-20T04:54:54.180887</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863099</t>
+          <t>2026-04-20T04:54:54.180890</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863102</t>
+          <t>2026-04-20T04:54:54.180892</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863105</t>
+          <t>2026-04-20T04:54:54.180895</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863108</t>
+          <t>2026-04-20T04:54:54.180898</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863111</t>
+          <t>2026-04-20T04:54:54.180901</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863116</t>
+          <t>2026-04-20T04:54:54.180904</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863120</t>
+          <t>2026-04-20T04:54:54.180909</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863123</t>
+          <t>2026-04-20T04:54:54.180912</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863126</t>
+          <t>2026-04-20T04:54:54.180914</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863129</t>
+          <t>2026-04-20T04:54:54.180917</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863131</t>
+          <t>2026-04-20T04:54:54.180920</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863134</t>
+          <t>2026-04-20T04:54:54.180923</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863137</t>
+          <t>2026-04-20T04:54:54.180926</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863140</t>
+          <t>2026-04-20T04:54:54.180928</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863143</t>
+          <t>2026-04-20T04:54:54.180931</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863146</t>
+          <t>2026-04-20T04:54:54.180934</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863150</t>
+          <t>2026-04-20T04:54:54.180939</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863153</t>
+          <t>2026-04-20T04:54:54.180942</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863156</t>
+          <t>2026-04-20T04:54:54.180945</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863159</t>
+          <t>2026-04-20T04:54:54.180947</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863162</t>
+          <t>2026-04-20T04:54:54.180950</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863164</t>
+          <t>2026-04-20T04:54:54.180953</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863167</t>
+          <t>2026-04-20T04:54:54.180956</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863170</t>
+          <t>2026-04-20T04:54:54.180958</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863173</t>
+          <t>2026-04-20T04:54:54.180961</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863176</t>
+          <t>2026-04-20T04:54:54.180964</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863180</t>
+          <t>2026-04-20T04:54:54.180969</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863183</t>
+          <t>2026-04-20T04:54:54.180972</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863186</t>
+          <t>2026-04-20T04:54:54.180975</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863189</t>
+          <t>2026-04-20T04:54:54.180978</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863192</t>
+          <t>2026-04-20T04:54:54.180980</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863195</t>
+          <t>2026-04-20T04:54:54.180983</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863197</t>
+          <t>2026-04-20T04:54:54.180986</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1196.00</t>
+          <t>1221.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863200</t>
+          <t>2026-04-20T04:54:54.180989</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1198.00</t>
+          <t>1220.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1198</v>
+        <v>1220</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:50.863203</t>
+          <t>2026-04-20T04:54:54.180991</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180822</t>
+          <t>2026-04-21T04:45:44.059408</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180839</t>
+          <t>2026-04-21T04:45:44.059425</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180844</t>
+          <t>2026-04-21T04:45:44.059429</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180847</t>
+          <t>2026-04-21T04:45:44.059432</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180851</t>
+          <t>2026-04-21T04:45:44.059435</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180857</t>
+          <t>2026-04-21T04:45:44.059438</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180860</t>
+          <t>2026-04-21T04:45:44.059441</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180863</t>
+          <t>2026-04-21T04:45:44.059444</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180867</t>
+          <t>2026-04-21T04:45:44.059447</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180870</t>
+          <t>2026-04-21T04:45:44.059450</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180873</t>
+          <t>2026-04-21T04:45:44.059453</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180878</t>
+          <t>2026-04-21T04:45:44.059458</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180881</t>
+          <t>2026-04-21T04:45:44.059461</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180884</t>
+          <t>2026-04-21T04:45:44.059464</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180887</t>
+          <t>2026-04-21T04:45:44.059467</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180890</t>
+          <t>2026-04-21T04:45:44.059469</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180892</t>
+          <t>2026-04-21T04:45:44.059472</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180895</t>
+          <t>2026-04-21T04:45:44.059475</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180898</t>
+          <t>2026-04-21T04:45:44.059478</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180901</t>
+          <t>2026-04-21T04:45:44.059482</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180904</t>
+          <t>2026-04-21T04:45:44.059485</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180909</t>
+          <t>2026-04-21T04:45:44.059490</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180912</t>
+          <t>2026-04-21T04:45:44.059493</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180914</t>
+          <t>2026-04-21T04:45:44.059495</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180917</t>
+          <t>2026-04-21T04:45:44.059498</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180920</t>
+          <t>2026-04-21T04:45:44.059501</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180923</t>
+          <t>2026-04-21T04:45:44.059504</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180926</t>
+          <t>2026-04-21T04:45:44.059507</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180928</t>
+          <t>2026-04-21T04:45:44.059510</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180931</t>
+          <t>2026-04-21T04:45:44.059512</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180934</t>
+          <t>2026-04-21T04:45:44.059515</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180939</t>
+          <t>2026-04-21T04:45:44.059519</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180942</t>
+          <t>2026-04-21T04:45:44.059522</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180945</t>
+          <t>2026-04-21T04:45:44.059525</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180947</t>
+          <t>2026-04-21T04:45:44.059528</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180950</t>
+          <t>2026-04-21T04:45:44.059531</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180953</t>
+          <t>2026-04-21T04:45:44.059534</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180956</t>
+          <t>2026-04-21T04:45:44.059536</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180958</t>
+          <t>2026-04-21T04:45:44.059539</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180961</t>
+          <t>2026-04-21T04:45:44.059542</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180964</t>
+          <t>2026-04-21T04:45:44.059545</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180969</t>
+          <t>2026-04-21T04:45:44.059549</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180972</t>
+          <t>2026-04-21T04:45:44.059552</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180975</t>
+          <t>2026-04-21T04:45:44.059555</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180978</t>
+          <t>2026-04-21T04:45:44.059557</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180980</t>
+          <t>2026-04-21T04:45:44.059560</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1223.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1223</v>
+        <v>1266</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180983</t>
+          <t>2026-04-21T04:45:44.059563</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180986</t>
+          <t>2026-04-21T04:45:44.059567</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180989</t>
+          <t>2026-04-21T04:45:44.059569</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1228.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:54.180991</t>
+          <t>2026-04-21T04:45:44.059572</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059408</t>
+          <t>2026-04-22T04:43:35.477703</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059425</t>
+          <t>2026-04-22T04:43:35.477721</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059429</t>
+          <t>2026-04-22T04:43:35.477726</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059432</t>
+          <t>2026-04-22T04:43:35.477729</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059435</t>
+          <t>2026-04-22T04:43:35.477732</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059438</t>
+          <t>2026-04-22T04:43:35.477735</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059441</t>
+          <t>2026-04-22T04:43:35.477739</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059444</t>
+          <t>2026-04-22T04:43:35.477742</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059447</t>
+          <t>2026-04-22T04:43:35.477746</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059450</t>
+          <t>2026-04-22T04:43:35.477749</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1294</v>
+        <v>1277</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059453</t>
+          <t>2026-04-22T04:43:35.477754</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1291</v>
+        <v>1283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059458</t>
+          <t>2026-04-22T04:43:35.477757</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059461</t>
+          <t>2026-04-22T04:43:35.477760</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059464</t>
+          <t>2026-04-22T04:43:35.477763</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059467</t>
+          <t>2026-04-22T04:43:35.477766</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1270</v>
+        <v>1296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059469</t>
+          <t>2026-04-22T04:43:35.477769</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059472</t>
+          <t>2026-04-22T04:43:35.477772</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059475</t>
+          <t>2026-04-22T04:43:35.477777</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059478</t>
+          <t>2026-04-22T04:43:35.477780</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059482</t>
+          <t>2026-04-22T04:43:35.477783</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059485</t>
+          <t>2026-04-22T04:43:35.477788</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059490</t>
+          <t>2026-04-22T04:43:35.477791</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059493</t>
+          <t>2026-04-22T04:43:35.477794</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059495</t>
+          <t>2026-04-22T04:43:35.477797</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059498</t>
+          <t>2026-04-22T04:43:35.477799</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059501</t>
+          <t>2026-04-22T04:43:35.477803</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059504</t>
+          <t>2026-04-22T04:43:35.477806</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059507</t>
+          <t>2026-04-22T04:43:35.477808</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1293</v>
+        <v>1272</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059510</t>
+          <t>2026-04-22T04:43:35.477811</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059512</t>
+          <t>2026-04-22T04:43:35.477814</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059515</t>
+          <t>2026-04-22T04:43:35.477819</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1259</v>
+        <v>1295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059519</t>
+          <t>2026-04-22T04:43:35.477822</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059522</t>
+          <t>2026-04-22T04:43:35.477825</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059525</t>
+          <t>2026-04-22T04:43:35.477828</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059528</t>
+          <t>2026-04-22T04:43:35.477831</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059531</t>
+          <t>2026-04-22T04:43:35.477833</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059534</t>
+          <t>2026-04-22T04:43:35.477836</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059536</t>
+          <t>2026-04-22T04:43:35.477839</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059539</t>
+          <t>2026-04-22T04:43:35.477842</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059542</t>
+          <t>2026-04-22T04:43:35.477845</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059545</t>
+          <t>2026-04-22T04:43:35.477850</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059549</t>
+          <t>2026-04-22T04:43:35.477853</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059552</t>
+          <t>2026-04-22T04:43:35.477856</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059555</t>
+          <t>2026-04-22T04:43:35.477859</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059557</t>
+          <t>2026-04-22T04:43:35.477861</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059560</t>
+          <t>2026-04-22T04:43:35.477864</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059563</t>
+          <t>2026-04-22T04:43:35.477867</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059567</t>
+          <t>2026-04-22T04:43:35.477870</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1221.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1221</v>
+        <v>1264</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059569</t>
+          <t>2026-04-22T04:43:35.477873</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1228.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1228</v>
+        <v>1266</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:44.059572</t>
+          <t>2026-04-22T04:43:35.477875</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477703</t>
+          <t>2026-04-23T04:47:37.369757</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477721</t>
+          <t>2026-04-23T04:47:37.369773</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477726</t>
+          <t>2026-04-23T04:47:37.369778</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1285</v>
+        <v>1271</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477729</t>
+          <t>2026-04-23T04:47:37.369781</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477732</t>
+          <t>2026-04-23T04:47:37.369784</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477735</t>
+          <t>2026-04-23T04:47:37.369791</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477739</t>
+          <t>2026-04-23T04:47:37.369794</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477742</t>
+          <t>2026-04-23T04:47:37.369797</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477746</t>
+          <t>2026-04-23T04:47:37.369801</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477749</t>
+          <t>2026-04-23T04:47:37.369804</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477754</t>
+          <t>2026-04-23T04:47:37.369809</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477757</t>
+          <t>2026-04-23T04:47:37.369812</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1294</v>
+        <v>1285</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477760</t>
+          <t>2026-04-23T04:47:37.369815</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1296</v>
+        <v>1283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477763</t>
+          <t>2026-04-23T04:47:37.369818</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477766</t>
+          <t>2026-04-23T04:47:37.369821</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477769</t>
+          <t>2026-04-23T04:47:37.369823</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477772</t>
+          <t>2026-04-23T04:47:37.369826</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477777</t>
+          <t>2026-04-23T04:47:37.369829</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1277</v>
+        <v>1296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477780</t>
+          <t>2026-04-23T04:47:37.369832</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477783</t>
+          <t>2026-04-23T04:47:37.369835</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1272</v>
+        <v>1300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477788</t>
+          <t>2026-04-23T04:47:37.369840</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477791</t>
+          <t>2026-04-23T04:47:37.369843</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477794</t>
+          <t>2026-04-23T04:47:37.369846</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477797</t>
+          <t>2026-04-23T04:47:37.369848</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477799</t>
+          <t>2026-04-23T04:47:37.369851</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477803</t>
+          <t>2026-04-23T04:47:37.369854</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477806</t>
+          <t>2026-04-23T04:47:37.369857</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477808</t>
+          <t>2026-04-23T04:47:37.369860</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477811</t>
+          <t>2026-04-23T04:47:37.369863</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477814</t>
+          <t>2026-04-23T04:47:37.369866</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477819</t>
+          <t>2026-04-23T04:47:37.369870</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477822</t>
+          <t>2026-04-23T04:47:37.369873</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477825</t>
+          <t>2026-04-23T04:47:37.369876</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477828</t>
+          <t>2026-04-23T04:47:37.369879</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1255</v>
+        <v>1292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477831</t>
+          <t>2026-04-23T04:47:37.369882</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1259</v>
+        <v>1293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477833</t>
+          <t>2026-04-23T04:47:37.369885</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477836</t>
+          <t>2026-04-23T04:47:37.369888</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477839</t>
+          <t>2026-04-23T04:47:37.369890</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477842</t>
+          <t>2026-04-23T04:47:37.369893</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477845</t>
+          <t>2026-04-23T04:47:37.369896</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477850</t>
+          <t>2026-04-23T04:47:37.369901</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477853</t>
+          <t>2026-04-23T04:47:37.369904</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477856</t>
+          <t>2026-04-23T04:47:37.369907</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477859</t>
+          <t>2026-04-23T04:47:37.369909</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477861</t>
+          <t>2026-04-23T04:47:37.369912</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477864</t>
+          <t>2026-04-23T04:47:37.369915</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477867</t>
+          <t>2026-04-23T04:47:37.369918</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477870</t>
+          <t>2026-04-23T04:47:37.369921</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477873</t>
+          <t>2026-04-23T04:47:37.369924</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:35.477875</t>
+          <t>2026-04-23T04:47:37.369926</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1276</v>
+        <v>1265</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369757</t>
+          <t>2026-04-24T04:51:33.201748</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369773</t>
+          <t>2026-04-24T04:51:33.201763</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1274</v>
+        <v>1263</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369778</t>
+          <t>2026-04-24T04:51:33.201767</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369781</t>
+          <t>2026-04-24T04:51:33.201771</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369784</t>
+          <t>2026-04-24T04:51:33.201774</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369791</t>
+          <t>2026-04-24T04:51:33.201778</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369794</t>
+          <t>2026-04-24T04:51:33.201781</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369797</t>
+          <t>2026-04-24T04:51:33.201784</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369801</t>
+          <t>2026-04-24T04:51:33.201787</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369804</t>
+          <t>2026-04-24T04:51:33.201791</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369809</t>
+          <t>2026-04-24T04:51:33.201796</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369812</t>
+          <t>2026-04-24T04:51:33.201799</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369815</t>
+          <t>2026-04-24T04:51:33.201804</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369818</t>
+          <t>2026-04-24T04:51:33.201807</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369821</t>
+          <t>2026-04-24T04:51:33.201810</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369823</t>
+          <t>2026-04-24T04:51:33.201812</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369826</t>
+          <t>2026-04-24T04:51:33.201815</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369829</t>
+          <t>2026-04-24T04:51:33.201818</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369832</t>
+          <t>2026-04-24T04:51:33.201821</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369835</t>
+          <t>2026-04-24T04:51:33.201824</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369840</t>
+          <t>2026-04-24T04:51:33.201829</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369843</t>
+          <t>2026-04-24T04:51:33.201831</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369846</t>
+          <t>2026-04-24T04:51:33.201834</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369848</t>
+          <t>2026-04-24T04:51:33.201837</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369851</t>
+          <t>2026-04-24T04:51:33.201840</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369854</t>
+          <t>2026-04-24T04:51:33.201843</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369857</t>
+          <t>2026-04-24T04:51:33.201846</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369860</t>
+          <t>2026-04-24T04:51:33.201848</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369863</t>
+          <t>2026-04-24T04:51:33.201851</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369866</t>
+          <t>2026-04-24T04:51:33.201854</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369870</t>
+          <t>2026-04-24T04:51:33.201859</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369873</t>
+          <t>2026-04-24T04:51:33.201862</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369876</t>
+          <t>2026-04-24T04:51:33.201864</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369879</t>
+          <t>2026-04-24T04:51:33.201867</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369882</t>
+          <t>2026-04-24T04:51:33.201870</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369885</t>
+          <t>2026-04-24T04:51:33.201873</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369888</t>
+          <t>2026-04-24T04:51:33.201876</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369890</t>
+          <t>2026-04-24T04:51:33.201878</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369893</t>
+          <t>2026-04-24T04:51:33.201881</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369896</t>
+          <t>2026-04-24T04:51:33.201884</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369901</t>
+          <t>2026-04-24T04:51:33.201889</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369904</t>
+          <t>2026-04-24T04:51:33.201892</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369907</t>
+          <t>2026-04-24T04:51:33.201894</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369909</t>
+          <t>2026-04-24T04:51:33.201897</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369912</t>
+          <t>2026-04-24T04:51:33.201900</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369915</t>
+          <t>2026-04-24T04:51:33.201903</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369918</t>
+          <t>2026-04-24T04:51:33.201905</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369921</t>
+          <t>2026-04-24T04:51:33.201908</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369924</t>
+          <t>2026-04-24T04:51:33.201911</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:37.369926</t>
+          <t>2026-04-24T04:51:33.201914</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201748</t>
+          <t>2026-04-25T04:33:36.822646</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201763</t>
+          <t>2026-04-25T04:33:36.822664</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201767</t>
+          <t>2026-04-25T04:33:36.822668</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201771</t>
+          <t>2026-04-25T04:33:36.822672</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201774</t>
+          <t>2026-04-25T04:33:36.822675</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201778</t>
+          <t>2026-04-25T04:33:36.822679</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201781</t>
+          <t>2026-04-25T04:33:36.822682</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201784</t>
+          <t>2026-04-25T04:33:36.822685</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201787</t>
+          <t>2026-04-25T04:33:36.822688</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201791</t>
+          <t>2026-04-25T04:33:36.822691</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201796</t>
+          <t>2026-04-25T04:33:36.822698</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201799</t>
+          <t>2026-04-25T04:33:36.822701</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201804</t>
+          <t>2026-04-25T04:33:36.822704</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201807</t>
+          <t>2026-04-25T04:33:36.822707</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201810</t>
+          <t>2026-04-25T04:33:36.822710</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201812</t>
+          <t>2026-04-25T04:33:36.822713</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201815</t>
+          <t>2026-04-25T04:33:36.822716</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201818</t>
+          <t>2026-04-25T04:33:36.822719</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201821</t>
+          <t>2026-04-25T04:33:36.822721</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201824</t>
+          <t>2026-04-25T04:33:36.822724</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201829</t>
+          <t>2026-04-25T04:33:36.822729</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201831</t>
+          <t>2026-04-25T04:33:36.822732</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201834</t>
+          <t>2026-04-25T04:33:36.822735</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201837</t>
+          <t>2026-04-25T04:33:36.822738</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201840</t>
+          <t>2026-04-25T04:33:36.822741</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201843</t>
+          <t>2026-04-25T04:33:36.822744</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201846</t>
+          <t>2026-04-25T04:33:36.822746</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201848</t>
+          <t>2026-04-25T04:33:36.822749</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201851</t>
+          <t>2026-04-25T04:33:36.822752</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201854</t>
+          <t>2026-04-25T04:33:36.822755</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201859</t>
+          <t>2026-04-25T04:33:36.822760</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201862</t>
+          <t>2026-04-25T04:33:36.822763</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201864</t>
+          <t>2026-04-25T04:33:36.822765</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201867</t>
+          <t>2026-04-25T04:33:36.822768</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201870</t>
+          <t>2026-04-25T04:33:36.822771</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201873</t>
+          <t>2026-04-25T04:33:36.822774</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201876</t>
+          <t>2026-04-25T04:33:36.822777</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201878</t>
+          <t>2026-04-25T04:33:36.822780</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201881</t>
+          <t>2026-04-25T04:33:36.822783</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201884</t>
+          <t>2026-04-25T04:33:36.822785</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201889</t>
+          <t>2026-04-25T04:33:36.822790</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201892</t>
+          <t>2026-04-25T04:33:36.822794</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201894</t>
+          <t>2026-04-25T04:33:36.822796</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201897</t>
+          <t>2026-04-25T04:33:36.822799</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201900</t>
+          <t>2026-04-25T04:33:36.822802</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201903</t>
+          <t>2026-04-25T04:33:36.822805</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201905</t>
+          <t>2026-04-25T04:33:36.822808</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201908</t>
+          <t>2026-04-25T04:33:36.822811</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201911</t>
+          <t>2026-04-25T04:33:36.822813</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-24T04:51:33.201914</t>
+          <t>2026-04-25T04:33:36.822816</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822646</t>
+          <t>2026-04-26T04:56:09.766705</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822664</t>
+          <t>2026-04-26T04:56:09.766721</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822668</t>
+          <t>2026-04-26T04:56:09.766725</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822672</t>
+          <t>2026-04-26T04:56:09.766729</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822675</t>
+          <t>2026-04-26T04:56:09.766732</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822679</t>
+          <t>2026-04-26T04:56:09.766735</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822682</t>
+          <t>2026-04-26T04:56:09.766738</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822685</t>
+          <t>2026-04-26T04:56:09.766742</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822688</t>
+          <t>2026-04-26T04:56:09.766745</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822691</t>
+          <t>2026-04-26T04:56:09.766749</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822698</t>
+          <t>2026-04-26T04:56:09.766754</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822701</t>
+          <t>2026-04-26T04:56:09.766757</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822704</t>
+          <t>2026-04-26T04:56:09.766760</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822707</t>
+          <t>2026-04-26T04:56:09.766763</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822710</t>
+          <t>2026-04-26T04:56:09.766766</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822713</t>
+          <t>2026-04-26T04:56:09.766769</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822716</t>
+          <t>2026-04-26T04:56:09.766772</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822719</t>
+          <t>2026-04-26T04:56:09.766774</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822721</t>
+          <t>2026-04-26T04:56:09.766777</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822724</t>
+          <t>2026-04-26T04:56:09.766781</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822729</t>
+          <t>2026-04-26T04:56:09.766786</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822732</t>
+          <t>2026-04-26T04:56:09.766788</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822735</t>
+          <t>2026-04-26T04:56:09.766791</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822738</t>
+          <t>2026-04-26T04:56:09.766794</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822741</t>
+          <t>2026-04-26T04:56:09.766797</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822744</t>
+          <t>2026-04-26T04:56:09.766800</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822746</t>
+          <t>2026-04-26T04:56:09.766803</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822749</t>
+          <t>2026-04-26T04:56:09.766806</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822752</t>
+          <t>2026-04-26T04:56:09.766808</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822755</t>
+          <t>2026-04-26T04:56:09.766811</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822760</t>
+          <t>2026-04-26T04:56:09.766816</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822763</t>
+          <t>2026-04-26T04:56:09.766819</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822765</t>
+          <t>2026-04-26T04:56:09.766822</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822768</t>
+          <t>2026-04-26T04:56:09.766825</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822771</t>
+          <t>2026-04-26T04:56:09.766827</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822774</t>
+          <t>2026-04-26T04:56:09.766830</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822777</t>
+          <t>2026-04-26T04:56:09.766833</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822780</t>
+          <t>2026-04-26T04:56:09.766836</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822783</t>
+          <t>2026-04-26T04:56:09.766839</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822785</t>
+          <t>2026-04-26T04:56:09.766842</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822790</t>
+          <t>2026-04-26T04:56:09.766846</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822794</t>
+          <t>2026-04-26T04:56:09.766849</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822796</t>
+          <t>2026-04-26T04:56:09.766852</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822799</t>
+          <t>2026-04-26T04:56:09.766855</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822802</t>
+          <t>2026-04-26T04:56:09.766858</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1264.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822805</t>
+          <t>2026-04-26T04:56:09.766861</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1266.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822808</t>
+          <t>2026-04-26T04:56:09.766863</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822811</t>
+          <t>2026-04-26T04:56:09.766866</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822813</t>
+          <t>2026-04-26T04:56:09.766869</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-25T04:33:36.822816</t>
+          <t>2026-04-26T04:56:09.766872</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766705</t>
+          <t>2026-04-27T05:19:50.741793</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766721</t>
+          <t>2026-04-27T05:19:50.741807</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766725</t>
+          <t>2026-04-27T05:19:50.741812</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766729</t>
+          <t>2026-04-27T05:19:50.741815</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1274</v>
+        <v>1263</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766732</t>
+          <t>2026-04-27T05:19:50.741818</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1276</v>
+        <v>1265</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766735</t>
+          <t>2026-04-27T05:19:50.741821</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766738</t>
+          <t>2026-04-27T05:19:50.741824</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766742</t>
+          <t>2026-04-27T05:19:50.741828</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766745</t>
+          <t>2026-04-27T05:19:50.741831</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766749</t>
+          <t>2026-04-27T05:19:50.741835</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766754</t>
+          <t>2026-04-27T05:19:50.741840</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766757</t>
+          <t>2026-04-27T05:19:50.741843</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766760</t>
+          <t>2026-04-27T05:19:50.741846</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766763</t>
+          <t>2026-04-27T05:19:50.741849</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766766</t>
+          <t>2026-04-27T05:19:50.741852</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766769</t>
+          <t>2026-04-27T05:19:50.741856</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766772</t>
+          <t>2026-04-27T05:19:50.741859</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766774</t>
+          <t>2026-04-27T05:19:50.741862</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766777</t>
+          <t>2026-04-27T05:19:50.741865</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766781</t>
+          <t>2026-04-27T05:19:50.741868</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766786</t>
+          <t>2026-04-27T05:19:50.741873</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766788</t>
+          <t>2026-04-27T05:19:50.741875</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766791</t>
+          <t>2026-04-27T05:19:50.741878</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766794</t>
+          <t>2026-04-27T05:19:50.741881</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766797</t>
+          <t>2026-04-27T05:19:50.741884</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766800</t>
+          <t>2026-04-27T05:19:50.741887</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766803</t>
+          <t>2026-04-27T05:19:50.741890</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766806</t>
+          <t>2026-04-27T05:19:50.741893</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766808</t>
+          <t>2026-04-27T05:19:50.741895</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766811</t>
+          <t>2026-04-27T05:19:50.741898</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766816</t>
+          <t>2026-04-27T05:19:50.741903</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766819</t>
+          <t>2026-04-27T05:19:50.741906</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766822</t>
+          <t>2026-04-27T05:19:50.741909</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766825</t>
+          <t>2026-04-27T05:19:50.741912</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766827</t>
+          <t>2026-04-27T05:19:50.741914</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766830</t>
+          <t>2026-04-27T05:19:50.741917</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766833</t>
+          <t>2026-04-27T05:19:50.741920</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766836</t>
+          <t>2026-04-27T05:19:50.741923</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766839</t>
+          <t>2026-04-27T05:19:50.741926</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766842</t>
+          <t>2026-04-27T05:19:50.741929</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766846</t>
+          <t>2026-04-27T05:19:50.741933</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766849</t>
+          <t>2026-04-27T05:19:50.741936</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766852</t>
+          <t>2026-04-27T05:19:50.741939</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766855</t>
+          <t>2026-04-27T05:19:50.741942</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766858</t>
+          <t>2026-04-27T05:19:50.741945</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766861</t>
+          <t>2026-04-27T05:19:50.741947</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766863</t>
+          <t>2026-04-27T05:19:50.741950</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766866</t>
+          <t>2026-04-27T05:19:50.741953</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766869</t>
+          <t>2026-04-27T05:19:50.741956</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1266.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-26T04:56:09.766872</t>
+          <t>2026-04-27T05:19:50.741958</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741793</t>
+          <t>2026-04-28T05:27:37.796961</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741807</t>
+          <t>2026-04-28T05:27:37.796976</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741812</t>
+          <t>2026-04-28T05:27:37.796980</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741815</t>
+          <t>2026-04-28T05:27:37.796984</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741818</t>
+          <t>2026-04-28T05:27:37.796987</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741821</t>
+          <t>2026-04-28T05:27:37.796990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1276</v>
+        <v>1265</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741824</t>
+          <t>2026-04-28T05:27:37.796993</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741828</t>
+          <t>2026-04-28T05:27:37.796997</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1274</v>
+        <v>1263</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741831</t>
+          <t>2026-04-28T05:27:37.797001</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741835</t>
+          <t>2026-04-28T05:27:37.797004</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741840</t>
+          <t>2026-04-28T05:27:37.797009</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741843</t>
+          <t>2026-04-28T05:27:37.797012</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741846</t>
+          <t>2026-04-28T05:27:37.797017</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741849</t>
+          <t>2026-04-28T05:27:37.797020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741852</t>
+          <t>2026-04-28T05:27:37.797023</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741856</t>
+          <t>2026-04-28T05:27:37.797026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741859</t>
+          <t>2026-04-28T05:27:37.797028</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741862</t>
+          <t>2026-04-28T05:27:37.797031</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741865</t>
+          <t>2026-04-28T05:27:37.797034</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741868</t>
+          <t>2026-04-28T05:27:37.797037</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741873</t>
+          <t>2026-04-28T05:27:37.797042</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741875</t>
+          <t>2026-04-28T05:27:37.797045</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741878</t>
+          <t>2026-04-28T05:27:37.797047</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741881</t>
+          <t>2026-04-28T05:27:37.797050</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741884</t>
+          <t>2026-04-28T05:27:37.797053</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741887</t>
+          <t>2026-04-28T05:27:37.797056</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741890</t>
+          <t>2026-04-28T05:27:37.797059</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741893</t>
+          <t>2026-04-28T05:27:37.797062</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741895</t>
+          <t>2026-04-28T05:27:37.797065</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741898</t>
+          <t>2026-04-28T05:27:37.797068</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741903</t>
+          <t>2026-04-28T05:27:37.797072</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741906</t>
+          <t>2026-04-28T05:27:37.797075</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741909</t>
+          <t>2026-04-28T05:27:37.797078</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741912</t>
+          <t>2026-04-28T05:27:37.797081</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741914</t>
+          <t>2026-04-28T05:27:37.797084</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741917</t>
+          <t>2026-04-28T05:27:37.797087</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741920</t>
+          <t>2026-04-28T05:27:37.797089</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741923</t>
+          <t>2026-04-28T05:27:37.797092</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741926</t>
+          <t>2026-04-28T05:27:37.797095</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741929</t>
+          <t>2026-04-28T05:27:37.797098</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741933</t>
+          <t>2026-04-28T05:27:37.797103</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741936</t>
+          <t>2026-04-28T05:27:37.797106</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741939</t>
+          <t>2026-04-28T05:27:37.797108</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741942</t>
+          <t>2026-04-28T05:27:37.797111</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741945</t>
+          <t>2026-04-28T05:27:37.797114</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741947</t>
+          <t>2026-04-28T05:27:37.797117</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741950</t>
+          <t>2026-04-28T05:27:37.797120</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1259.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741953</t>
+          <t>2026-04-28T05:27:37.797123</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741956</t>
+          <t>2026-04-28T05:27:37.797125</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1255.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-27T05:19:50.741958</t>
+          <t>2026-04-28T05:27:37.797128</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1263</v>
+        <v>1234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.796961</t>
+          <t>2026-04-29T05:23:07.300645</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1265</v>
+        <v>1236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.796976</t>
+          <t>2026-04-29T05:23:07.300660</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1232.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1262</v>
+        <v>1232</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.796980</t>
+          <t>2026-04-29T05:23:07.300664</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.796984</t>
+          <t>2026-04-29T05:23:07.300667</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.796987</t>
+          <t>2026-04-29T05:23:07.300671</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.796990</t>
+          <t>2026-04-29T05:23:07.300674</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.796993</t>
+          <t>2026-04-29T05:23:07.300677</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.796997</t>
+          <t>2026-04-29T05:23:07.300681</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797001</t>
+          <t>2026-04-29T05:23:07.300684</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1276</v>
+        <v>1265</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797004</t>
+          <t>2026-04-29T05:23:07.300690</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1274</v>
+        <v>1260</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797009</t>
+          <t>2026-04-29T05:23:07.300695</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797012</t>
+          <t>2026-04-29T05:23:07.300698</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797017</t>
+          <t>2026-04-29T05:23:07.300701</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797020</t>
+          <t>2026-04-29T05:23:07.300704</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797023</t>
+          <t>2026-04-29T05:23:07.300707</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797026</t>
+          <t>2026-04-29T05:23:07.300709</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797028</t>
+          <t>2026-04-29T05:23:07.300713</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1285</v>
+        <v>1274</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797031</t>
+          <t>2026-04-29T05:23:07.300715</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797034</t>
+          <t>2026-04-29T05:23:07.300718</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797037</t>
+          <t>2026-04-29T05:23:07.300721</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797042</t>
+          <t>2026-04-29T05:23:07.300726</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797045</t>
+          <t>2026-04-29T05:23:07.300729</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797047</t>
+          <t>2026-04-29T05:23:07.300731</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797050</t>
+          <t>2026-04-29T05:23:07.300734</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797053</t>
+          <t>2026-04-29T05:23:07.300737</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797056</t>
+          <t>2026-04-29T05:23:07.300740</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1296</v>
+        <v>1277</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797059</t>
+          <t>2026-04-29T05:23:07.300743</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797062</t>
+          <t>2026-04-29T05:23:07.300746</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797065</t>
+          <t>2026-04-29T05:23:07.300749</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797068</t>
+          <t>2026-04-29T05:23:07.300751</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1272</v>
+        <v>1300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797072</t>
+          <t>2026-04-29T05:23:07.300756</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1277</v>
+        <v>1296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797075</t>
+          <t>2026-04-29T05:23:07.300759</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797078</t>
+          <t>2026-04-29T05:23:07.300762</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797081</t>
+          <t>2026-04-29T05:23:07.300765</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797084</t>
+          <t>2026-04-29T05:23:07.300767</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797087</t>
+          <t>2026-04-29T05:23:07.300770</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797089</t>
+          <t>2026-04-29T05:23:07.300773</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797092</t>
+          <t>2026-04-29T05:23:07.300776</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797095</t>
+          <t>2026-04-29T05:23:07.300778</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797098</t>
+          <t>2026-04-29T05:23:07.300781</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797103</t>
+          <t>2026-04-29T05:23:07.300786</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797106</t>
+          <t>2026-04-29T05:23:07.300789</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797108</t>
+          <t>2026-04-29T05:23:07.300791</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797111</t>
+          <t>2026-04-29T05:23:07.300794</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797114</t>
+          <t>2026-04-29T05:23:07.300797</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1255</v>
+        <v>1295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797117</t>
+          <t>2026-04-29T05:23:07.300800</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797120</t>
+          <t>2026-04-29T05:23:07.300803</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1259.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1259</v>
+        <v>1293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797123</t>
+          <t>2026-04-29T05:23:07.300805</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797125</t>
+          <t>2026-04-29T05:23:07.300808</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1257.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-28T05:27:37.797128</t>
+          <t>2026-04-29T05:23:07.300811</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300645</t>
+          <t>2026-04-30T05:27:17.441636</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1235.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300660</t>
+          <t>2026-04-30T05:27:17.441650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1232.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300664</t>
+          <t>2026-04-30T05:27:17.441654</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1232.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1265</v>
+        <v>1232</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300667</t>
+          <t>2026-04-30T05:27:17.441658</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1263</v>
+        <v>1234</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300671</t>
+          <t>2026-04-30T05:27:17.441661</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1262</v>
+        <v>1236</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300674</t>
+          <t>2026-04-30T05:27:17.441664</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300677</t>
+          <t>2026-04-30T05:27:17.441667</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300681</t>
+          <t>2026-04-30T05:27:17.441670</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300684</t>
+          <t>2026-04-30T05:27:17.441673</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300690</t>
+          <t>2026-04-30T05:27:17.441676</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300695</t>
+          <t>2026-04-30T05:27:17.441680</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300698</t>
+          <t>2026-04-30T05:27:17.441685</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1274</v>
+        <v>1265</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300701</t>
+          <t>2026-04-30T05:27:17.441688</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1276</v>
+        <v>1263</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300704</t>
+          <t>2026-04-30T05:27:17.441690</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300707</t>
+          <t>2026-04-30T05:27:17.441693</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300709</t>
+          <t>2026-04-30T05:27:17.441696</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300713</t>
+          <t>2026-04-30T05:27:17.441699</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300715</t>
+          <t>2026-04-30T05:27:17.441702</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300718</t>
+          <t>2026-04-30T05:27:17.441705</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300721</t>
+          <t>2026-04-30T05:27:17.441707</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1285</v>
+        <v>1271</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300726</t>
+          <t>2026-04-30T05:27:17.441712</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300729</t>
+          <t>2026-04-30T05:27:17.441714</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300731</t>
+          <t>2026-04-30T05:27:17.441717</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300734</t>
+          <t>2026-04-30T05:27:17.441720</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300737</t>
+          <t>2026-04-30T05:27:17.441723</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300740</t>
+          <t>2026-04-30T05:27:17.441726</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300743</t>
+          <t>2026-04-30T05:27:17.441728</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1294</v>
+        <v>1277</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300746</t>
+          <t>2026-04-30T05:27:17.441731</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1296</v>
+        <v>1283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300749</t>
+          <t>2026-04-30T05:27:17.441734</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300751</t>
+          <t>2026-04-30T05:27:17.441737</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300756</t>
+          <t>2026-04-30T05:27:17.441741</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300759</t>
+          <t>2026-04-30T05:27:17.441744</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300762</t>
+          <t>2026-04-30T05:27:17.441747</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300765</t>
+          <t>2026-04-30T05:27:17.441750</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300767</t>
+          <t>2026-04-30T05:27:17.441753</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1277</v>
+        <v>1294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300770</t>
+          <t>2026-04-30T05:27:17.441755</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300773</t>
+          <t>2026-04-30T05:27:17.441758</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300776</t>
+          <t>2026-04-30T05:27:17.441761</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300778</t>
+          <t>2026-04-30T05:27:17.441764</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300781</t>
+          <t>2026-04-30T05:27:17.441767</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300786</t>
+          <t>2026-04-30T05:27:17.441771</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300789</t>
+          <t>2026-04-30T05:27:17.441774</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300791</t>
+          <t>2026-04-30T05:27:17.441777</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300794</t>
+          <t>2026-04-30T05:27:17.441780</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300797</t>
+          <t>2026-04-30T05:27:17.441783</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300800</t>
+          <t>2026-04-30T05:27:17.441785</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1292</v>
+        <v>1270</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300803</t>
+          <t>2026-04-30T05:27:17.441788</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1293</v>
+        <v>1270</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300805</t>
+          <t>2026-04-30T05:27:17.441791</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1255.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1255</v>
+        <v>1295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300808</t>
+          <t>2026-04-30T05:27:17.441794</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1257.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-29T05:23:07.300811</t>
+          <t>2026-04-30T05:27:17.441796</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441636</t>
+          <t>2026-05-01T05:38:31.565289</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1235.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441650</t>
+          <t>2026-05-01T05:38:31.565307</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1235.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441654</t>
+          <t>2026-05-01T05:38:31.565311</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441658</t>
+          <t>2026-05-01T05:38:31.565314</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441661</t>
+          <t>2026-05-01T05:38:31.565318</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441664</t>
+          <t>2026-05-01T05:38:31.565321</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441667</t>
+          <t>2026-05-01T05:38:31.565325</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441670</t>
+          <t>2026-05-01T05:38:31.565328</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441673</t>
+          <t>2026-05-01T05:38:31.565331</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441676</t>
+          <t>2026-05-01T05:38:31.565334</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441680</t>
+          <t>2026-05-01T05:38:31.565340</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441685</t>
+          <t>2026-05-01T05:38:31.565343</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441688</t>
+          <t>2026-05-01T05:38:31.565345</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441690</t>
+          <t>2026-05-01T05:38:31.565348</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441693</t>
+          <t>2026-05-01T05:38:31.565351</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441696</t>
+          <t>2026-05-01T05:38:31.565354</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441699</t>
+          <t>2026-05-01T05:38:31.565357</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441702</t>
+          <t>2026-05-01T05:38:31.565360</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441705</t>
+          <t>2026-05-01T05:38:31.565363</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441707</t>
+          <t>2026-05-01T05:38:31.565366</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441712</t>
+          <t>2026-05-01T05:38:31.565371</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441714</t>
+          <t>2026-05-01T05:38:31.565374</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441717</t>
+          <t>2026-05-01T05:38:31.565376</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441720</t>
+          <t>2026-05-01T05:38:31.565379</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441723</t>
+          <t>2026-05-01T05:38:31.565382</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441726</t>
+          <t>2026-05-01T05:38:31.565385</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441728</t>
+          <t>2026-05-01T05:38:31.565388</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441731</t>
+          <t>2026-05-01T05:38:31.565391</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441734</t>
+          <t>2026-05-01T05:38:31.565393</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441737</t>
+          <t>2026-05-01T05:38:31.565396</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1291.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441741</t>
+          <t>2026-05-01T05:38:31.565401</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1291.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441744</t>
+          <t>2026-05-01T05:38:31.565404</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441747</t>
+          <t>2026-05-01T05:38:31.565407</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441750</t>
+          <t>2026-05-01T05:38:31.565410</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441753</t>
+          <t>2026-05-01T05:38:31.565412</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441755</t>
+          <t>2026-05-01T05:38:31.565415</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1277.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441758</t>
+          <t>2026-05-01T05:38:31.565418</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1277.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441761</t>
+          <t>2026-05-01T05:38:31.565421</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441764</t>
+          <t>2026-05-01T05:38:31.565423</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441767</t>
+          <t>2026-05-01T05:38:31.565426</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441771</t>
+          <t>2026-05-01T05:38:31.565432</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441774</t>
+          <t>2026-05-01T05:38:31.565434</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441777</t>
+          <t>2026-05-01T05:38:31.565437</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441780</t>
+          <t>2026-05-01T05:38:31.565440</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441783</t>
+          <t>2026-05-01T05:38:31.565443</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441785</t>
+          <t>2026-05-01T05:38:31.565446</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441788</t>
+          <t>2026-05-01T05:38:31.565448</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441791</t>
+          <t>2026-05-01T05:38:31.565451</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1295.00</t>
+          <t>1293.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441794</t>
+          <t>2026-05-01T05:38:31.565454</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-30T05:27:17.441796</t>
+          <t>2026-05-01T05:38:31.565457</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1235.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565289</t>
+          <t>2026-05-02T04:55:46.466018</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565307</t>
+          <t>2026-05-02T04:55:46.466032</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1235.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565311</t>
+          <t>2026-05-02T04:55:46.466036</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1232.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565314</t>
+          <t>2026-05-02T04:55:46.466040</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565318</t>
+          <t>2026-05-02T04:55:46.466043</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1232.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565321</t>
+          <t>2026-05-02T04:55:46.466046</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1265.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565325</t>
+          <t>2026-05-02T04:55:46.466049</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1265.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565328</t>
+          <t>2026-05-02T04:55:46.466053</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565331</t>
+          <t>2026-05-02T04:55:46.466056</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565334</t>
+          <t>2026-05-02T04:55:46.466059</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565340</t>
+          <t>2026-05-02T04:55:46.466065</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565343</t>
+          <t>2026-05-02T04:55:46.466068</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565345</t>
+          <t>2026-05-02T04:55:46.466071</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565348</t>
+          <t>2026-05-02T04:55:46.466074</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565351</t>
+          <t>2026-05-02T04:55:46.466077</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565354</t>
+          <t>2026-05-02T04:55:46.466079</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565357</t>
+          <t>2026-05-02T04:55:46.466082</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565360</t>
+          <t>2026-05-02T04:55:46.466085</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565363</t>
+          <t>2026-05-02T04:55:46.466088</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565366</t>
+          <t>2026-05-02T04:55:46.466091</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565371</t>
+          <t>2026-05-02T04:55:46.466096</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565374</t>
+          <t>2026-05-02T04:55:46.466098</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565376</t>
+          <t>2026-05-02T04:55:46.466101</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565379</t>
+          <t>2026-05-02T04:55:46.466104</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565382</t>
+          <t>2026-05-02T04:55:46.466107</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565385</t>
+          <t>2026-05-02T04:55:46.466110</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565388</t>
+          <t>2026-05-02T04:55:46.466113</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565391</t>
+          <t>2026-05-02T04:55:46.466116</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565393</t>
+          <t>2026-05-02T04:55:46.466118</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565396</t>
+          <t>2026-05-02T04:55:46.466121</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565401</t>
+          <t>2026-05-02T04:55:46.466126</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565404</t>
+          <t>2026-05-02T04:55:46.466129</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565407</t>
+          <t>2026-05-02T04:55:46.466132</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1296.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565410</t>
+          <t>2026-05-02T04:55:46.466135</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1296.00</t>
+          <t>1294.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565412</t>
+          <t>2026-05-02T04:55:46.466137</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1294.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565415</t>
+          <t>2026-05-02T04:55:46.466140</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565418</t>
+          <t>2026-05-02T04:55:46.466143</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565421</t>
+          <t>2026-05-02T04:55:46.466146</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565423</t>
+          <t>2026-05-02T04:55:46.466149</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565426</t>
+          <t>2026-05-02T04:55:46.466152</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565432</t>
+          <t>2026-05-02T04:55:46.466156</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565434</t>
+          <t>2026-05-02T04:55:46.466159</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565437</t>
+          <t>2026-05-02T04:55:46.466162</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565440</t>
+          <t>2026-05-02T04:55:46.466165</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565443</t>
+          <t>2026-05-02T04:55:46.466168</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1270.00</t>
+          <t>1272.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565446</t>
+          <t>2026-05-02T04:55:46.466171</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1272.00</t>
+          <t>1270.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565448</t>
+          <t>2026-05-02T04:55:46.466174</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565451</t>
+          <t>2026-05-02T04:55:46.466176</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1293.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565454</t>
+          <t>2026-05-02T04:55:46.466179</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1295.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-05-01T05:38:31.565457</t>
+          <t>2026-05-02T04:55:46.466182</t>
         </is>
       </c>
     </row>

--- a/jewelry_gold_latest.xlsx
+++ b/jewelry_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1235.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466018</t>
+          <t>2026-05-03T05:27:15.707546</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466032</t>
+          <t>2026-05-03T05:27:15.707560</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1235.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466036</t>
+          <t>2026-05-03T05:27:15.707565</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1234.00</t>
+          <t>1232.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466040</t>
+          <t>2026-05-03T05:27:15.707568</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1236.00</t>
+          <t>1234.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466043</t>
+          <t>2026-05-03T05:27:15.707571</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1232.00</t>
+          <t>1236.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466046</t>
+          <t>2026-05-03T05:27:15.707575</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1262.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466049</t>
+          <t>2026-05-03T05:27:15.707578</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466053</t>
+          <t>2026-05-03T05:27:15.707582</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466056</t>
+          <t>2026-05-03T05:27:15.707585</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466059</t>
+          <t>2026-05-03T05:27:15.707588</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1261.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466065</t>
+          <t>2026-05-03T05:27:15.707594</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1261.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466068</t>
+          <t>2026-05-03T05:27:15.707597</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466071</t>
+          <t>2026-05-03T05:27:15.707600</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466074</t>
+          <t>2026-05-03T05:27:15.707603</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466077</t>
+          <t>2026-05-03T05:27:15.707606</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466079</t>
+          <t>2026-05-03T05:27:15.707609</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466082</t>
+          <t>2026-05-03T05:27:15.707612</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466085</t>
+          <t>2026-05-03T05:27:15.707614</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1276.00</t>
+          <t>1274.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466088</t>
+          <t>2026-05-03T05:27:15.707617</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1271.00</t>
+          <t>1276.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466091</t>
+          <t>2026-05-03T05:27:15.707620</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1274.00</t>
+          <t>1271.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466096</t>
+          <t>2026-05-03T05:27:15.707625</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1285.00</t>
+          <t>1289.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466098</t>
+          <t>2026-05-03T05:27:15.707628</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466101</t>
+          <t>2026-05-03T05:27:15.707631</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1289.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466104</t>
+          <t>2026-05-03T05:27:15.707634</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1286.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-05-02T04:55:46.466107</t>
+          <t>2026-05-03T05:27:15.707637</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1285.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
   